--- a/research/traditional_assets/database/data/hong_kong/hong_kong_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ42"/>
+  <dimension ref="A1:AQ43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.032415</v>
+        <v>-0.0121</v>
       </c>
       <c r="E2">
-        <v>0.0998</v>
+        <v>0.00163</v>
       </c>
       <c r="F2">
-        <v>0.164</v>
+        <v>0.12</v>
       </c>
       <c r="G2">
-        <v>0.2153334955857041</v>
+        <v>0.242276691368887</v>
       </c>
       <c r="H2">
-        <v>0.2137200851039855</v>
+        <v>0.2407482494618995</v>
       </c>
       <c r="I2">
-        <v>0.2396521408750406</v>
+        <v>0.1326584464573266</v>
       </c>
       <c r="J2">
-        <v>0.2137309301261106</v>
+        <v>0.1173742045708487</v>
       </c>
       <c r="K2">
-        <v>4911.489</v>
+        <v>1703.829</v>
       </c>
       <c r="L2">
-        <v>0.4536436817864634</v>
+        <v>0.1672362988659475</v>
       </c>
       <c r="M2">
-        <v>3103.279</v>
+        <v>2754.767</v>
       </c>
       <c r="N2">
-        <v>0.03463118481569676</v>
+        <v>0.03829479524710135</v>
       </c>
       <c r="O2">
-        <v>0.631840771708946</v>
+        <v>1.616809550723693</v>
       </c>
       <c r="P2">
-        <v>2304.148</v>
+        <v>1936.358</v>
       </c>
       <c r="Q2">
-        <v>0.02571324564459659</v>
+        <v>0.02691786025282235</v>
       </c>
       <c r="R2">
-        <v>0.4691343093713535</v>
+        <v>1.136474376243156</v>
       </c>
       <c r="S2">
-        <v>799.131</v>
+        <v>818.4089999999999</v>
       </c>
       <c r="T2">
-        <v>0.2575118125054177</v>
+        <v>0.2970882836915064</v>
       </c>
       <c r="U2">
-        <v>30046.844</v>
+        <v>31333.244</v>
       </c>
       <c r="V2">
-        <v>0.3353091383960028</v>
+        <v>0.4355722873867252</v>
       </c>
       <c r="W2">
-        <v>0.0406939918471995</v>
+        <v>0.01712913553895411</v>
       </c>
       <c r="X2">
-        <v>0.02897887819944255</v>
+        <v>0.0551134216040054</v>
       </c>
       <c r="Y2">
-        <v>0.01171511364775695</v>
+        <v>-0.03798428606505129</v>
       </c>
       <c r="Z2">
-        <v>0.2081745401424061</v>
+        <v>0.1306666163132563</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02905451297684478</v>
+        <v>0.05369565510106083</v>
       </c>
       <c r="AC2">
-        <v>-0.02902364244083503</v>
+        <v>-0.05515345331111729</v>
       </c>
       <c r="AD2">
-        <v>54612.176</v>
+        <v>63662.881</v>
       </c>
       <c r="AE2">
-        <v>0.5799276022495059</v>
+        <v>1.142253752244955</v>
       </c>
       <c r="AF2">
-        <v>54612.75592760225</v>
+        <v>63664.02325375225</v>
       </c>
       <c r="AG2">
-        <v>24565.91192760225</v>
+        <v>32330.77925375225</v>
       </c>
       <c r="AH2">
-        <v>0.3786711074298413</v>
+        <v>0.4694992842883045</v>
       </c>
       <c r="AI2">
-        <v>0.5763591838753093</v>
+        <v>0.6034420134617593</v>
       </c>
       <c r="AJ2">
-        <v>0.2151596156476598</v>
+        <v>0.3100780452816327</v>
       </c>
       <c r="AK2">
-        <v>0.3796432764517134</v>
+        <v>0.4359114174804483</v>
       </c>
       <c r="AL2">
-        <v>234.731</v>
+        <v>237.811</v>
       </c>
       <c r="AM2">
-        <v>222.792</v>
+        <v>228.575</v>
       </c>
       <c r="AN2">
-        <v>20.55829914615499</v>
+        <v>44.41315409815937</v>
       </c>
       <c r="AO2">
-        <v>11.05168469439486</v>
+        <v>5.679855010912027</v>
       </c>
       <c r="AP2">
-        <v>9.247633095699097</v>
+        <v>22.55493088838491</v>
       </c>
       <c r="AQ2">
-        <v>11.64392348019678</v>
+        <v>5.909360166247402</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital Finance Holdings Limited (SEHK:8239)</t>
+          <t>Hong Kong Exchanges and Clearing Limited (SEHK:388)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,100 +725,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.176</v>
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.07629999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.14</v>
       </c>
       <c r="G3">
-        <v>-0.6749174917491749</v>
+        <v>0.8688596684110999</v>
       </c>
       <c r="H3">
-        <v>-0.6749174917491749</v>
+        <v>0.8688596684110999</v>
       </c>
       <c r="I3">
-        <v>0.07904290429042904</v>
+        <v>0.6508641540964862</v>
       </c>
       <c r="J3">
-        <v>0.07904290429042904</v>
+        <v>0.5581078264366741</v>
       </c>
       <c r="K3">
-        <v>-5.32</v>
+        <v>1245</v>
       </c>
       <c r="L3">
-        <v>-0.877887788778878</v>
+        <v>0.5475174809798143</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1230.066</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02247545647395454</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.9880048192771085</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1230.066</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02247545647395454</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.9880048192771085</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0</v>
+        <v>22344.5</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.4082730822429667</v>
+      </c>
+      <c r="W3">
+        <v>0.205408259226873</v>
       </c>
       <c r="X3">
-        <v>0.03634950736421977</v>
+        <v>0.04981542152606089</v>
+      </c>
+      <c r="Y3">
+        <v>0.1555928377008121</v>
       </c>
       <c r="AB3">
-        <v>0.03095834716312973</v>
+        <v>0.04982697654309011</v>
       </c>
       <c r="AD3">
-        <v>46.2</v>
+        <v>284.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>46.2</v>
+        <v>284.6</v>
       </c>
       <c r="AG3">
-        <v>46.2</v>
+        <v>-22059.9</v>
       </c>
       <c r="AH3">
-        <v>0.6193029490616623</v>
+        <v>0.005173238036205396</v>
       </c>
       <c r="AI3">
-        <v>0.7924528301886793</v>
+        <v>0.04512661138154661</v>
       </c>
       <c r="AJ3">
-        <v>0.6193029490616623</v>
+        <v>-0.6752465610020386</v>
       </c>
       <c r="AK3">
-        <v>0.7924528301886793</v>
+        <v>1.375494145082243</v>
       </c>
       <c r="AL3">
-        <v>5.33</v>
+        <v>11.3</v>
       </c>
       <c r="AM3">
-        <v>5.054</v>
+        <v>11.3</v>
       </c>
       <c r="AN3">
-        <v>88</v>
+        <v>0.1854675790159661</v>
       </c>
       <c r="AO3">
-        <v>0.08986866791744839</v>
+        <v>130.9734513274336</v>
       </c>
       <c r="AP3">
-        <v>88</v>
+        <v>-14.37595307917889</v>
       </c>
       <c r="AQ3">
-        <v>0.09477641472101304</v>
+        <v>130.9734513274336</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Temir Corp. (OTCPK:TMRR)</t>
+          <t>Capital Finance Holdings Limited (SEHK:8239)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,23 +852,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.09849999999999999</v>
+      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.8015122873345936</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.8015122873345936</v>
       </c>
       <c r="I4">
-        <v>-0.9631706931185471</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="J4">
-        <v>-0.9631706931185471</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="K4">
-        <v>-0.267</v>
+        <v>-0.612</v>
       </c>
       <c r="L4">
-        <v>-1.213636363636364</v>
+        <v>-0.1156899810964083</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,67 +895,58 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.0001869158878504673</v>
-      </c>
-      <c r="W4">
-        <v>1.094262295081967</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.02412011895124758</v>
-      </c>
-      <c r="Y4">
-        <v>1.07014217613072</v>
-      </c>
-      <c r="Z4">
-        <v>-1.239351173823964</v>
-      </c>
-      <c r="AA4">
-        <v>1.193706729109312</v>
+        <v>0.1094305612606592</v>
       </c>
       <c r="AB4">
-        <v>0.0241279903215509</v>
-      </c>
-      <c r="AC4">
-        <v>1.169578738787761</v>
+        <v>0.07061555859359278</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="AE4">
-        <v>0.06948776243040171</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.06948776243040171</v>
+        <v>24.3</v>
       </c>
       <c r="AG4">
-        <v>0.05948776243040171</v>
+        <v>24.3</v>
       </c>
       <c r="AH4">
-        <v>0.001297151892483377</v>
+        <v>0.8669282911166607</v>
       </c>
       <c r="AI4">
-        <v>-0.1573858129344556</v>
+        <v>0.7126099706744868</v>
       </c>
       <c r="AJ4">
-        <v>0.001110685798457724</v>
+        <v>0.8669282911166607</v>
       </c>
       <c r="AK4">
-        <v>-0.1317522704381451</v>
+        <v>0.7126099706744868</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>3.566</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>12.65625</v>
+      </c>
+      <c r="AO4">
+        <v>0.4893617021276596</v>
       </c>
       <c r="AP4">
-        <v>0.8262189226444682</v>
+        <v>12.65625</v>
+      </c>
+      <c r="AQ4">
+        <v>0.5159842961301179</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TradeGo FinTech Limited (SEHK:8017)</t>
+          <t>AGM Group Holdings Inc. (NasdaqCM:AGMH)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -956,23 +965,29 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.6509999999999999</v>
+      </c>
+      <c r="E5">
+        <v>0.313</v>
+      </c>
       <c r="G5">
-        <v>0.4586466165413534</v>
+        <v>0.03331557922769641</v>
       </c>
       <c r="H5">
-        <v>0.2857142857142857</v>
+        <v>0.03322237017310253</v>
       </c>
       <c r="I5">
-        <v>0.3276047261009667</v>
+        <v>0.1693945242117651</v>
       </c>
       <c r="J5">
-        <v>0.3102301623524809</v>
+        <v>0.1254326119758546</v>
       </c>
       <c r="K5">
-        <v>2.96</v>
+        <v>18.6</v>
       </c>
       <c r="L5">
-        <v>0.317937701396348</v>
+        <v>0.1238348868175766</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,73 +1011,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>10.8</v>
+        <v>9.65</v>
       </c>
       <c r="V5">
-        <v>0.1824324324324324</v>
+        <v>0.24125</v>
       </c>
       <c r="W5">
-        <v>0.3410138248847926</v>
+        <v>6.019417475728156</v>
       </c>
       <c r="X5">
-        <v>0.02436452398962533</v>
+        <v>0.0518328863203748</v>
       </c>
       <c r="Y5">
-        <v>0.3166493008951673</v>
+        <v>5.967584589407782</v>
       </c>
       <c r="Z5">
-        <v>3.259803921568629</v>
+        <v>42.80772728895199</v>
       </c>
       <c r="AA5">
-        <v>1.01128949982549</v>
+        <v>5.369485046603319</v>
       </c>
       <c r="AB5">
-        <v>0.02447170623285945</v>
+        <v>0.05245649567281157</v>
       </c>
       <c r="AC5">
-        <v>0.9868177935926301</v>
+        <v>5.317028550930508</v>
       </c>
       <c r="AD5">
-        <v>2</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.04971231696442497</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>9.019712316964426</v>
       </c>
       <c r="AG5">
-        <v>-8.800000000000001</v>
+        <v>-0.6302876830355739</v>
       </c>
       <c r="AH5">
-        <v>0.03267973856209151</v>
+        <v>0.1840017391094101</v>
       </c>
       <c r="AI5">
-        <v>0.111731843575419</v>
+        <v>0.2030565225772453</v>
       </c>
       <c r="AJ5">
-        <v>-0.1746031746031746</v>
+        <v>-0.01600945615149905</v>
       </c>
       <c r="AK5">
-        <v>-1.23943661971831</v>
+        <v>-0.01812749203357807</v>
       </c>
       <c r="AL5">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.5988023952095809</v>
-      </c>
-      <c r="AO5">
-        <v>122</v>
+        <v>0.3496667056484621</v>
       </c>
       <c r="AP5">
-        <v>-2.634730538922156</v>
-      </c>
-      <c r="AQ5">
-        <v>-35.46511627906977</v>
+        <v>-0.02456974556720749</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DL Holdings Group Limited (SEHK:1709)</t>
+          <t>TradeGo FinTech Limited (SEHK:8017)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,122 +1090,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.228</v>
-      </c>
-      <c r="E6">
-        <v>0.7070000000000001</v>
-      </c>
       <c r="G6">
-        <v>0.3327067669172932</v>
+        <v>0.4532786885245902</v>
       </c>
       <c r="H6">
-        <v>0.3327067669172932</v>
+        <v>0.3057377049180328</v>
       </c>
       <c r="I6">
-        <v>0.4116541353383458</v>
+        <v>0.3868852459016394</v>
       </c>
       <c r="J6">
-        <v>0.3795482915783667</v>
+        <v>0.3767283540044603</v>
       </c>
       <c r="K6">
-        <v>23.9</v>
+        <v>4.19</v>
       </c>
       <c r="L6">
-        <v>0.4492481203007518</v>
+        <v>0.3434426229508197</v>
       </c>
       <c r="M6">
-        <v>21.57</v>
+        <v>4.42</v>
       </c>
       <c r="N6">
-        <v>0.04601109215017065</v>
+        <v>0.05573770491803279</v>
       </c>
       <c r="O6">
-        <v>0.9025104602510461</v>
+        <v>1.054892601431981</v>
       </c>
       <c r="P6">
-        <v>7.57</v>
+        <v>2.42</v>
       </c>
       <c r="Q6">
-        <v>0.01614761092150171</v>
+        <v>0.03051702395964691</v>
       </c>
       <c r="R6">
-        <v>0.3167364016736402</v>
+        <v>0.5775656324582338</v>
       </c>
       <c r="S6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="T6">
-        <v>0.6490496059341678</v>
+        <v>0.4524886877828054</v>
       </c>
       <c r="U6">
-        <v>9.529999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="V6">
-        <v>0.02032849829351535</v>
+        <v>0.2005044136191677</v>
       </c>
       <c r="W6">
-        <v>0.5584112149532711</v>
+        <v>0.2635220125786163</v>
       </c>
       <c r="X6">
-        <v>0.02452761368011341</v>
+        <v>0.04996528067209265</v>
       </c>
       <c r="Y6">
-        <v>0.5338836012731577</v>
+        <v>0.2135567319065237</v>
       </c>
       <c r="Z6">
-        <v>1.873107527638899</v>
+        <v>1.71830985915493</v>
       </c>
       <c r="AA6">
-        <v>0.7109347620579223</v>
+        <v>0.6473360449090727</v>
       </c>
       <c r="AB6">
-        <v>0.02469138461941086</v>
+        <v>0.05027541220945848</v>
       </c>
       <c r="AC6">
-        <v>0.6862433774385114</v>
+        <v>0.5970606326996142</v>
       </c>
       <c r="AD6">
-        <v>26</v>
+        <v>1.71</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>26</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>16.47</v>
+        <v>-14.19</v>
       </c>
       <c r="AH6">
-        <v>0.05254648342764753</v>
+        <v>0.02110850512282434</v>
       </c>
       <c r="AI6">
-        <v>0.2957906712172924</v>
+        <v>0.09238249594813613</v>
       </c>
       <c r="AJ6">
-        <v>0.03393986852679951</v>
+        <v>-0.2179388726770081</v>
       </c>
       <c r="AK6">
-        <v>0.2101569478116626</v>
+        <v>-5.436781609195404</v>
       </c>
       <c r="AL6">
-        <v>0.614</v>
+        <v>0.082</v>
       </c>
       <c r="AM6">
-        <v>0.433</v>
+        <v>-0.17</v>
       </c>
       <c r="AN6">
-        <v>1.181818181818182</v>
+        <v>0.3475609756097561</v>
       </c>
       <c r="AO6">
-        <v>35.66775244299674</v>
+        <v>57.56097560975609</v>
       </c>
       <c r="AP6">
-        <v>0.7486363636363635</v>
+        <v>-2.884146341463415</v>
       </c>
       <c r="AQ6">
-        <v>50.57736720554272</v>
+        <v>-27.76470588235294</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>China Everbright Limited (SEHK:165)</t>
+          <t>Dingyi Group Investment Limited (SEHK:508)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,121 +1219,118 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.17</v>
-      </c>
-      <c r="E7">
-        <v>0.00058</v>
+        <v>0.0522</v>
       </c>
       <c r="G7">
-        <v>0.6473082358987537</v>
+        <v>0.03991130820399113</v>
       </c>
       <c r="H7">
-        <v>0.6473082358987537</v>
+        <v>0.03991130820399113</v>
       </c>
       <c r="I7">
-        <v>0.8013619426956188</v>
+        <v>0.1382113821138211</v>
       </c>
       <c r="J7">
-        <v>0.624278761403058</v>
+        <v>0.06910569105691056</v>
       </c>
       <c r="K7">
-        <v>430</v>
+        <v>-0.264</v>
       </c>
       <c r="L7">
-        <v>0.5524861878453039</v>
+        <v>-0.001951219512195122</v>
       </c>
       <c r="M7">
-        <v>112</v>
+        <v>0.002</v>
       </c>
       <c r="N7">
-        <v>0.05560520305828617</v>
+        <v>4.329004329004329e-05</v>
       </c>
       <c r="O7">
-        <v>0.2604651162790698</v>
+        <v>-0.007575757575757576</v>
       </c>
       <c r="P7">
-        <v>112</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.05560520305828617</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.2604651162790698</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>1639.6</v>
+        <v>11.9</v>
       </c>
       <c r="V7">
-        <v>0.8140204547711249</v>
+        <v>0.2575757575757576</v>
       </c>
       <c r="W7">
-        <v>0.08419815938907382</v>
+        <v>-0.001432447097124254</v>
       </c>
       <c r="X7">
-        <v>0.04284884912049428</v>
+        <v>0.08061200005620994</v>
       </c>
       <c r="Y7">
-        <v>0.04134931026857954</v>
+        <v>-0.0820444471533342</v>
       </c>
       <c r="Z7">
-        <v>0.09872769018050814</v>
+        <v>0.4297966963151208</v>
       </c>
       <c r="AA7">
-        <v>0.06163360014207248</v>
+        <v>0.02970139771283355</v>
       </c>
       <c r="AB7">
-        <v>0.02924889505075273</v>
+        <v>0.06103480244919859</v>
       </c>
       <c r="AC7">
-        <v>0.03238470509131976</v>
+        <v>-0.03133340473636505</v>
       </c>
       <c r="AD7">
-        <v>5016.6</v>
+        <v>155.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>5016.6</v>
+        <v>155.6</v>
       </c>
       <c r="AG7">
-        <v>3377</v>
+        <v>143.7</v>
       </c>
       <c r="AH7">
-        <v>0.7135176651305684</v>
+        <v>0.7710604558969276</v>
       </c>
       <c r="AI7">
-        <v>0.4341722633801842</v>
+        <v>0.5060162601626016</v>
       </c>
       <c r="AJ7">
-        <v>0.6263911559578572</v>
+        <v>0.7567140600315956</v>
       </c>
       <c r="AK7">
-        <v>0.3406019284302255</v>
+        <v>0.4861299052774018</v>
       </c>
       <c r="AL7">
-        <v>122.3</v>
+        <v>13.2</v>
       </c>
       <c r="AM7">
-        <v>122.3</v>
+        <v>13.145</v>
       </c>
       <c r="AN7">
-        <v>7.99713055954089</v>
+        <v>8.104166666666666</v>
       </c>
       <c r="AO7">
-        <v>5.099754701553557</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="AP7">
-        <v>5.383389128008928</v>
+        <v>7.484375</v>
       </c>
       <c r="AQ7">
-        <v>5.099754701553557</v>
+        <v>1.422594142259414</v>
       </c>
     </row>
     <row r="8">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dingyi Group Investment Limited (SEHK:508)</t>
+          <t>G-Resources Group Limited (SEHK:1051)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1350,115 +1350,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.337</v>
+        <v>-0.0919</v>
       </c>
       <c r="G8">
-        <v>26.70744138634047</v>
+        <v>2.221276595744681</v>
       </c>
       <c r="H8">
-        <v>26.70744138634047</v>
+        <v>2.221276595744681</v>
       </c>
       <c r="I8">
-        <v>17.22731906218145</v>
+        <v>0.405531914893617</v>
       </c>
       <c r="J8">
-        <v>17.22731906218145</v>
+        <v>0.405531914893617</v>
       </c>
       <c r="K8">
-        <v>-11.8</v>
+        <v>-56.2</v>
       </c>
       <c r="L8">
-        <v>-12.02854230377166</v>
+        <v>-2.391489361702128</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>6.762</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.0538804780876494</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-0.1203202846975089</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>6.762</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.0538804780876494</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0.1203202846975089</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>16.1</v>
+        <v>865.5</v>
       </c>
       <c r="V8">
-        <v>0.1916666666666667</v>
+        <v>6.896414342629482</v>
       </c>
       <c r="W8">
-        <v>-0.06522940851299061</v>
+        <v>-0.03446161393181261</v>
       </c>
       <c r="X8">
-        <v>0.037240889629025</v>
+        <v>0.04977421969233153</v>
       </c>
       <c r="Y8">
-        <v>-0.1024702981420156</v>
+        <v>-0.08423583362414414</v>
       </c>
       <c r="Z8">
-        <v>0.002983576642335766</v>
+        <v>0.0242294019152569</v>
       </c>
       <c r="AA8">
-        <v>0.05139902676399026</v>
+        <v>0.009825795755421201</v>
       </c>
       <c r="AB8">
-        <v>0.03114002255670306</v>
+        <v>0.04977581366464987</v>
       </c>
       <c r="AC8">
-        <v>0.0202590042072872</v>
+        <v>-0.03995001790922867</v>
       </c>
       <c r="AD8">
-        <v>146.6</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>146.6</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AG8">
-        <v>130.5</v>
+        <v>-865.412</v>
       </c>
       <c r="AH8">
-        <v>0.6357328707718994</v>
+        <v>0.0007007038889065834</v>
       </c>
       <c r="AI8">
-        <v>0.4430341492898157</v>
+        <v>5.641430666817105e-05</v>
       </c>
       <c r="AJ8">
-        <v>0.6083916083916084</v>
+        <v>1.169614764999081</v>
       </c>
       <c r="AK8">
-        <v>0.4145489199491741</v>
+        <v>-1.246294578823367</v>
       </c>
       <c r="AL8">
-        <v>20.1</v>
+        <v>0.007</v>
       </c>
       <c r="AM8">
-        <v>19.981</v>
+        <v>0.007</v>
       </c>
       <c r="AN8">
-        <v>8.425287356321839</v>
+        <v>0.008543689320388348</v>
       </c>
       <c r="AO8">
-        <v>0.8407960199004973</v>
+        <v>1361.428571428571</v>
       </c>
       <c r="AP8">
-        <v>7.500000000000001</v>
+        <v>-84.02058252427184</v>
       </c>
       <c r="AQ8">
-        <v>0.8458035133376707</v>
+        <v>1361.428571428571</v>
       </c>
     </row>
     <row r="9">
@@ -1469,7 +1472,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lerado Financial Group Company Limited (SEHK:1225)</t>
+          <t>Shandong Hi-Speed Holdings Group Limited (SEHK:412)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1477,116 +1480,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>-0.006520000000000001</v>
-      </c>
       <c r="G9">
-        <v>0.4384057971014492</v>
+        <v>-0.01207207207207207</v>
       </c>
       <c r="H9">
-        <v>0.4384057971014492</v>
+        <v>-0.01207207207207207</v>
       </c>
       <c r="I9">
-        <v>0.4166666666666666</v>
+        <v>0.1292792792792793</v>
       </c>
       <c r="J9">
-        <v>0.4166666666666666</v>
+        <v>0.1292792792792793</v>
       </c>
       <c r="K9">
-        <v>-2.09</v>
+        <v>3.36</v>
       </c>
       <c r="L9">
-        <v>-0.07572463768115942</v>
+        <v>0.01513513513513513</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>38.3</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.008673400063408668</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>11.39880952380952</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>38.3</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.008673400063408668</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>11.39880952380952</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>24.6</v>
+        <v>1094.4</v>
       </c>
       <c r="V9">
-        <v>2.523076923076923</v>
+        <v>0.2478373114724399</v>
       </c>
       <c r="W9">
-        <v>-0.01473906911142454</v>
+        <v>0.00272572402044293</v>
       </c>
       <c r="X9">
-        <v>0.1025876966836957</v>
+        <v>0.06338633568867034</v>
       </c>
       <c r="Y9">
-        <v>-0.1173267657951202</v>
+        <v>-0.06066061166822741</v>
       </c>
       <c r="Z9">
-        <v>0.1272153211495471</v>
+        <v>0.08509333435547548</v>
       </c>
       <c r="AA9">
-        <v>0.05300638381231131</v>
+        <v>0.0110008049369466</v>
       </c>
       <c r="AB9">
-        <v>0.0365220416871767</v>
+        <v>0.05850476471924075</v>
       </c>
       <c r="AC9">
-        <v>0.01648434212513461</v>
+        <v>-0.04750395978229414</v>
       </c>
       <c r="AD9">
-        <v>101.7</v>
+        <v>6566.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>101.7</v>
+        <v>6566.5</v>
       </c>
       <c r="AG9">
-        <v>77.09999999999999</v>
+        <v>5472.1</v>
       </c>
       <c r="AH9">
-        <v>0.9125168236877523</v>
+        <v>0.5979166476967485</v>
       </c>
       <c r="AI9">
-        <v>0.4162914449447401</v>
+        <v>0.7495234507870197</v>
       </c>
       <c r="AJ9">
-        <v>0.8877374784110535</v>
+        <v>0.5534137683431264</v>
       </c>
       <c r="AK9">
-        <v>0.350933090578061</v>
+        <v>0.7137676906019697</v>
       </c>
       <c r="AL9">
-        <v>8.17</v>
+        <v>67.2</v>
       </c>
       <c r="AM9">
-        <v>8.154</v>
+        <v>65.24000000000001</v>
       </c>
       <c r="AN9">
-        <v>8.475</v>
+        <v>147.561797752809</v>
       </c>
       <c r="AO9">
-        <v>1.407588739290086</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="AP9">
-        <v>6.425</v>
+        <v>122.9685393258427</v>
       </c>
       <c r="AQ9">
-        <v>1.410350748099092</v>
+        <v>0.4399141630901287</v>
       </c>
     </row>
     <row r="10">
@@ -1597,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>China Success Finance Group Holdings Limited (SEHK:3623)</t>
+          <t>Doyen International Holdings Limited (SEHK:668)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1605,26 +1608,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D10">
-        <v>0.12</v>
-      </c>
       <c r="G10">
-        <v>0.132289156626506</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.1570281124497992</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.1080321285140562</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.1080321285140562</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>-8.859999999999999</v>
+        <v>5.47</v>
       </c>
       <c r="L10">
-        <v>-0.3558232931726907</v>
+        <v>0.2878947368421053</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1633,7 +1633,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1642,79 +1642,70 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>6.04</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="V10">
-        <v>0.0867816091954023</v>
+        <v>0.2531446540880503</v>
       </c>
       <c r="W10">
-        <v>-0.1176626826029216</v>
+        <v>0.05426587301587302</v>
       </c>
       <c r="X10">
-        <v>0.02699657083072881</v>
+        <v>0.049997326834937</v>
       </c>
       <c r="Y10">
-        <v>-0.1446592534336505</v>
+        <v>0.004268546180936014</v>
       </c>
       <c r="Z10">
-        <v>0.3030155523644948</v>
+        <v>0.1992407877351565</v>
       </c>
       <c r="AA10">
-        <v>0.03273541509479884</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0261070830673903</v>
+        <v>0.05004749132388601</v>
       </c>
       <c r="AC10">
-        <v>0.006628332027408534</v>
+        <v>-0.05004749132388601</v>
       </c>
       <c r="AD10">
-        <v>26.7</v>
+        <v>0.797</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>26.7</v>
+        <v>0.797</v>
       </c>
       <c r="AG10">
-        <v>20.66</v>
+        <v>-7.253000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.2772585669781931</v>
+        <v>0.02445010277019358</v>
       </c>
       <c r="AI10">
-        <v>0.258220502901354</v>
+        <v>0.006500974738370434</v>
       </c>
       <c r="AJ10">
-        <v>0.2288943053401285</v>
+        <v>-0.2954739886747872</v>
       </c>
       <c r="AK10">
-        <v>0.212202136400986</v>
+        <v>-0.06331898696604889</v>
       </c>
       <c r="AL10">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>2.01</v>
-      </c>
-      <c r="AN10">
-        <v>9.780219780219779</v>
-      </c>
-      <c r="AO10">
-        <v>1.338308457711443</v>
-      </c>
-      <c r="AP10">
-        <v>7.567765567765568</v>
+        <v>-0.053</v>
       </c>
       <c r="AQ10">
-        <v>1.338308457711443</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1725,7 +1716,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yue Da International Holdings Limited (SEHK:629)</t>
+          <t>DL Holdings Group Limited (SEHK:1709)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1734,115 +1725,118 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.09039999999999999</v>
+        <v>-0.0101</v>
+      </c>
+      <c r="E11">
+        <v>0.0149</v>
       </c>
       <c r="G11">
-        <v>0.5196662693682956</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0.5196662693682956</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.5613825983313468</v>
+        <v>0.0001714075455885206</v>
       </c>
       <c r="J11">
-        <v>0.3715332105320187</v>
+        <v>0.0001188203762623337</v>
       </c>
       <c r="K11">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="L11">
-        <v>0.433849821215733</v>
+        <v>0.1046920821114369</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>2.98</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.005341459042839219</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0.834733893557423</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>1.83</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.003280157734360997</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.5126050420168068</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="T11">
+        <v>0.3859060402684564</v>
       </c>
       <c r="U11">
-        <v>2.12</v>
+        <v>11.1</v>
       </c>
       <c r="V11">
-        <v>0.04416666666666667</v>
+        <v>0.01989603871661588</v>
       </c>
       <c r="W11">
-        <v>0.06907020872865274</v>
+        <v>0.05767366720516963</v>
       </c>
       <c r="X11">
-        <v>0.0253329384267666</v>
+        <v>0.05009956456562076</v>
       </c>
       <c r="Y11">
-        <v>0.04373727030188614</v>
+        <v>0.007574102639548864</v>
       </c>
       <c r="Z11">
-        <v>0.08248132127408574</v>
+        <v>0.4373994485573687</v>
       </c>
       <c r="AA11">
-        <v>0.03064455010188396</v>
+        <v>5.197196705452381e-05</v>
       </c>
       <c r="AB11">
-        <v>0.02565603206844077</v>
+        <v>0.05016771814651352</v>
       </c>
       <c r="AC11">
-        <v>0.00498851803344319</v>
+        <v>-0.050115746179459</v>
       </c>
       <c r="AD11">
-        <v>7.8</v>
+        <v>20.2</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>0.01077501347715725</v>
       </c>
       <c r="AF11">
-        <v>7.8</v>
+        <v>20.21077501347716</v>
       </c>
       <c r="AG11">
-        <v>5.68</v>
+        <v>9.110775013477157</v>
       </c>
       <c r="AH11">
-        <v>0.1397849462365592</v>
+        <v>0.03496003860679815</v>
       </c>
       <c r="AI11">
-        <v>0.1128798842257598</v>
+        <v>0.2532336643775767</v>
       </c>
       <c r="AJ11">
-        <v>0.1058122205663189</v>
+        <v>0.01606808091655861</v>
       </c>
       <c r="AK11">
-        <v>0.0848014332636608</v>
+        <v>0.1325960158605421</v>
       </c>
       <c r="AL11">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0.492</v>
+        <v>-0.004</v>
       </c>
       <c r="AN11">
-        <v>1.645569620253164</v>
-      </c>
-      <c r="AO11">
-        <v>4.528846153846153</v>
+        <v>2525</v>
       </c>
       <c r="AP11">
-        <v>1.19831223628692</v>
+        <v>1138.846876684645</v>
       </c>
       <c r="AQ11">
-        <v>9.573170731707318</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1853,7 +1847,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>China Shandong Hi-Speed Financial Group Limited (SEHK:412)</t>
+          <t>International Alliance Financial Leasing Co., Ltd. (SEHK:1563)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1862,115 +1856,100 @@
         </is>
       </c>
       <c r="G12">
-        <v>0.3252933507170795</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>0.3252933507170795</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0.3585397653194263</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.3585397653194263</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>26.7</v>
+        <v>12</v>
       </c>
       <c r="L12">
-        <v>0.1740547588005215</v>
+        <v>0.46875</v>
       </c>
       <c r="M12">
-        <v>38.7</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.01565914056809905</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>1.449438202247191</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>38.7</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.01565914056809905</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>1.449438202247191</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>259.2</v>
+        <v>25.3</v>
       </c>
       <c r="V12">
-        <v>0.1048798252002913</v>
+        <v>0.0125446251487505</v>
       </c>
       <c r="W12">
-        <v>0.02173028404004232</v>
+        <v>0.06240249609984399</v>
       </c>
       <c r="X12">
-        <v>0.02908896654015921</v>
+        <v>0.0501601328680177</v>
       </c>
       <c r="Y12">
-        <v>-0.007358682500116887</v>
+        <v>0.01224236323182629</v>
       </c>
       <c r="Z12">
-        <v>0.05698365527488856</v>
+        <v>0.07509533587562335</v>
       </c>
       <c r="AA12">
-        <v>0.02043090638930163</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.02952674591740841</v>
+        <v>0.05023772947878363</v>
       </c>
       <c r="AC12">
-        <v>-0.009095839528106772</v>
+        <v>-0.05023772947878363</v>
       </c>
       <c r="AD12">
-        <v>1635.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1635.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AG12">
-        <v>1376.2</v>
+        <v>61.10000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.398217590337976</v>
+        <v>0.04108025865348042</v>
       </c>
       <c r="AI12">
-        <v>0.5676895306859205</v>
+        <v>0.3046544428772919</v>
       </c>
       <c r="AJ12">
-        <v>0.3576775132550161</v>
+        <v>0.02940468742480389</v>
       </c>
       <c r="AK12">
-        <v>0.5249465974977112</v>
+        <v>0.2365466511807975</v>
       </c>
       <c r="AL12">
-        <v>48.1</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>44.19</v>
-      </c>
-      <c r="AN12">
-        <v>29.51985559566787</v>
-      </c>
-      <c r="AO12">
-        <v>1.143451143451143</v>
-      </c>
-      <c r="AP12">
-        <v>24.84115523465704</v>
-      </c>
-      <c r="AQ12">
-        <v>1.244625480878027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1981,7 +1960,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>G-Resources Group Limited (SEHK:1051)</t>
+          <t>Wealthy Way Group Limited (SEHK:3848)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1990,10 +1969,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.316</v>
+        <v>0.0522</v>
       </c>
       <c r="E13">
-        <v>-0.0649</v>
+        <v>-0.0269</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2008,82 +1987,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>105.2</v>
+        <v>4.07</v>
       </c>
       <c r="L13">
-        <v>1.142236699239957</v>
+        <v>0.3282258064516129</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>2.39</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.01944670463791701</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>0.5872235872235873</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>2.39</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.01944670463791701</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.5872235872235873</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>643.1</v>
+        <v>17.4</v>
       </c>
       <c r="V13">
-        <v>3.972205064854849</v>
+        <v>0.1415785191212368</v>
       </c>
       <c r="W13">
-        <v>0.06886619533909401</v>
+        <v>0.05037128712871287</v>
       </c>
       <c r="X13">
-        <v>0.02411945526962764</v>
+        <v>0.05202565628671682</v>
       </c>
       <c r="Y13">
-        <v>0.04474674006946636</v>
+        <v>-0.001654369158003946</v>
       </c>
       <c r="Z13">
-        <v>0.1563614138738923</v>
+        <v>0.1196103019195525</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.02411905499300766</v>
+        <v>0.0507586493786971</v>
       </c>
       <c r="AC13">
-        <v>-0.02411905499300766</v>
+        <v>-0.0507586493786971</v>
       </c>
       <c r="AD13">
-        <v>0.196</v>
+        <v>30.3</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.196</v>
+        <v>30.3</v>
       </c>
       <c r="AG13">
-        <v>-642.904</v>
+        <v>12.9</v>
       </c>
       <c r="AH13">
-        <v>0.001209160003948278</v>
+        <v>0.1977806788511749</v>
       </c>
       <c r="AI13">
-        <v>0.0001200100906443562</v>
+        <v>0.2700534759358289</v>
       </c>
       <c r="AJ13">
-        <v>1.336587637524844</v>
+        <v>0.09499263622974964</v>
       </c>
       <c r="AK13">
-        <v>-0.6493350139784425</v>
+        <v>0.1360759493670886</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2100,7 +2082,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zhong Ji Longevity Science Group Limited (SEHK:767)</t>
+          <t>Global International Credit Group Limited (SEHK:1669)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2109,7 +2091,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.225</v>
+        <v>-0.0121</v>
+      </c>
+      <c r="E14">
+        <v>-0.0364</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2124,82 +2109,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>-6.19</v>
+        <v>6.77</v>
       </c>
       <c r="L14">
-        <v>-0.6515789473684211</v>
+        <v>0.6099099099099099</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>2.7</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.1050583657587549</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>0.3988183161004432</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>2.7</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.1050583657587549</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>0.3988183161004432</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>2.61</v>
+        <v>3.59</v>
       </c>
       <c r="V14">
-        <v>0.02541382667964946</v>
+        <v>0.1396887159533074</v>
       </c>
       <c r="W14">
-        <v>-0.08308724832214766</v>
+        <v>0.06333021515434985</v>
       </c>
       <c r="X14">
-        <v>0.02418946606547279</v>
+        <v>0.05050899930129846</v>
       </c>
       <c r="Y14">
-        <v>-0.1072767143876204</v>
+        <v>0.01282121585305139</v>
       </c>
       <c r="Z14">
-        <v>0.1457502301319423</v>
+        <v>0.1118275236751964</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.02430069007892235</v>
+        <v>0.05086188322492169</v>
       </c>
       <c r="AC14">
-        <v>-0.02430069007892235</v>
+        <v>-0.05086188322492169</v>
       </c>
       <c r="AD14">
-        <v>1.08</v>
+        <v>2.08</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.08</v>
+        <v>2.08</v>
       </c>
       <c r="AG14">
-        <v>-1.53</v>
+        <v>-1.51</v>
       </c>
       <c r="AH14">
-        <v>0.01040662940836385</v>
+        <v>0.07487401007919367</v>
       </c>
       <c r="AI14">
-        <v>0.01765282772147761</v>
+        <v>0.01859134787272078</v>
       </c>
       <c r="AJ14">
-        <v>-0.01512306019571019</v>
+        <v>-0.06242248863166597</v>
       </c>
       <c r="AK14">
-        <v>-0.02612258835581355</v>
+        <v>-0.01394403915412319</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2216,7 +2204,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Global International Credit Group Limited (SEHK:1669)</t>
+          <t>Upbest Group Limited (SEHK:335)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2225,10 +2213,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.0237</v>
+        <v>-0.113</v>
       </c>
       <c r="E15">
-        <v>-0.008670000000000001</v>
+        <v>-0.192</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2243,28 +2231,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>7.29</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L15">
-        <v>0.6177966101694915</v>
+        <v>0.8105691056910569</v>
       </c>
       <c r="M15">
-        <v>6.13</v>
+        <v>6.83</v>
       </c>
       <c r="N15">
-        <v>0.2253676470588235</v>
+        <v>0.03609936575052854</v>
       </c>
       <c r="O15">
-        <v>0.840877914951989</v>
+        <v>0.6850551654964895</v>
       </c>
       <c r="P15">
-        <v>6.13</v>
+        <v>6.83</v>
       </c>
       <c r="Q15">
-        <v>0.2253676470588235</v>
+        <v>0.03609936575052854</v>
       </c>
       <c r="R15">
-        <v>0.840877914951989</v>
+        <v>0.6850551654964895</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2273,55 +2261,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>14.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V15">
-        <v>0.5257352941176471</v>
+        <v>0.3509513742071882</v>
       </c>
       <c r="W15">
-        <v>0.06962750716332378</v>
+        <v>0.02898255813953489</v>
       </c>
       <c r="X15">
-        <v>0.02595253228619433</v>
+        <v>0.05114732330378596</v>
       </c>
       <c r="Y15">
-        <v>0.04367497487712944</v>
+        <v>-0.02216476516425108</v>
       </c>
       <c r="Z15">
-        <v>0.1077723993058727</v>
+        <v>0.04079601990049751</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.02552686781754832</v>
+        <v>0.05126537015279916</v>
       </c>
       <c r="AC15">
-        <v>-0.02552686781754832</v>
+        <v>-0.05126537015279916</v>
       </c>
       <c r="AD15">
-        <v>6.66</v>
+        <v>28.5</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>6.66</v>
+        <v>28.5</v>
       </c>
       <c r="AG15">
-        <v>-7.640000000000001</v>
+        <v>-37.90000000000001</v>
       </c>
       <c r="AH15">
-        <v>0.1966922622563497</v>
+        <v>0.1309141019751952</v>
       </c>
       <c r="AI15">
-        <v>0.05864741106023248</v>
+        <v>0.07659231389411449</v>
       </c>
       <c r="AJ15">
-        <v>-0.3905930470347649</v>
+        <v>-0.2504957038995374</v>
       </c>
       <c r="AK15">
-        <v>-0.076969574853919</v>
+        <v>-0.1239777559699051</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2346,32 +2334,17 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>8.644214867637064e-05</v>
-      </c>
-      <c r="J16">
-        <v>7.954005004885237e-05</v>
-      </c>
       <c r="K16">
-        <v>479.4</v>
-      </c>
-      <c r="L16">
-        <v>1.141972367794188</v>
+        <v>-520.5</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>0.28</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.001299303944315545</v>
       </c>
       <c r="O16">
-        <v>-0</v>
+        <v>-0.0005379442843419789</v>
       </c>
       <c r="P16">
         <v>-0</v>
@@ -2380,73 +2353,70 @@
         <v>-0</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
       </c>
       <c r="U16">
-        <v>82.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="V16">
-        <v>0.187143834055163</v>
+        <v>0.3415313225058004</v>
       </c>
       <c r="W16">
-        <v>0.5531325718241605</v>
+        <v>-0.3691227572512588</v>
       </c>
       <c r="X16">
-        <v>0.02559284112773575</v>
+        <v>0.0520838865630659</v>
       </c>
       <c r="Y16">
-        <v>0.5275397306964248</v>
+        <v>-0.4212066438143247</v>
       </c>
       <c r="Z16">
-        <v>0.4897091335556175</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>3.895148899239395e-05</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.02593053061448823</v>
+        <v>0.05207685182163223</v>
       </c>
       <c r="AC16">
-        <v>-0.02589157912549584</v>
+        <v>-0.05207685182163223</v>
       </c>
       <c r="AD16">
-        <v>86.40000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="AE16">
-        <v>0.04355792992829804</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>86.4435579299283</v>
+        <v>54.5</v>
       </c>
       <c r="AG16">
-        <v>4.343557929928309</v>
+        <v>-19.09999999999999</v>
       </c>
       <c r="AH16">
-        <v>0.1646093846617514</v>
+        <v>0.2018518518518519</v>
       </c>
       <c r="AI16">
-        <v>0.05776213961289578</v>
+        <v>0.07320349227669577</v>
       </c>
       <c r="AJ16">
-        <v>0.00980390720547456</v>
+        <v>-0.09725050916496941</v>
       </c>
       <c r="AK16">
-        <v>0.00307085984843765</v>
+        <v>-0.02846922045014159</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
         <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>1920</v>
-      </c>
-      <c r="AP16">
-        <v>96.52350955396243</v>
       </c>
     </row>
     <row r="17">
@@ -2457,7 +2427,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oi Wah Pawnshop Credit Holdings Limited (SEHK:1319)</t>
+          <t>Zhong Ji Longevity Science Group Limited (SEHK:767)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2466,10 +2436,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.0429</v>
+        <v>-0.298</v>
       </c>
       <c r="E17">
-        <v>-0.04559999999999999</v>
+        <v>-0.368</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2484,85 +2454,82 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>10.1</v>
+        <v>4.22</v>
       </c>
       <c r="L17">
-        <v>0.5459459459459459</v>
+        <v>0.3322834645669291</v>
       </c>
       <c r="M17">
-        <v>4.181</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.06899339933993399</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>0.413960396039604</v>
+        <v>-0</v>
       </c>
       <c r="P17">
-        <v>4.1</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.06765676567656764</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.4059405940594059</v>
+        <v>-0</v>
       </c>
       <c r="S17">
-        <v>0.08100000000000041</v>
-      </c>
-      <c r="T17">
-        <v>0.01937335565654159</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>28.4</v>
+        <v>1.74</v>
       </c>
       <c r="V17">
-        <v>0.4686468646864686</v>
+        <v>0.07598253275109171</v>
       </c>
       <c r="W17">
-        <v>0.08480268681780016</v>
+        <v>0.07416520210896309</v>
       </c>
       <c r="X17">
-        <v>0.02721415873834885</v>
+        <v>0.05078358858907846</v>
       </c>
       <c r="Y17">
-        <v>0.05758852807945131</v>
+        <v>0.02338161351988462</v>
       </c>
       <c r="Z17">
-        <v>0.1247471341874579</v>
+        <v>0.2293660827162723</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.02621365044326771</v>
+        <v>0.05216880184701501</v>
       </c>
       <c r="AC17">
-        <v>-0.02621365044326771</v>
+        <v>-0.05216880184701501</v>
       </c>
       <c r="AD17">
-        <v>25</v>
+        <v>2.54</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>25</v>
+        <v>2.54</v>
       </c>
       <c r="AG17">
-        <v>-3.399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AH17">
-        <v>0.2920560747663551</v>
+        <v>0.09984276729559749</v>
       </c>
       <c r="AI17">
-        <v>0.1677852348993289</v>
+        <v>0.0425888665325285</v>
       </c>
       <c r="AJ17">
-        <v>-0.05944055944055941</v>
+        <v>0.03375527426160338</v>
       </c>
       <c r="AK17">
-        <v>-0.02819237147595356</v>
+        <v>0.01381692573402418</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2579,7 +2546,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wealthy Way Group Limited (SEHK:3848)</t>
+          <t>AEON Credit Service (Asia) Company Limited (SEHK:900)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2587,41 +2554,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.00792</v>
+      </c>
+      <c r="E18">
+        <v>0.00163</v>
+      </c>
       <c r="G18">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>-15.9</v>
+        <v>44.8</v>
       </c>
       <c r="L18">
-        <v>1.821305841924399</v>
+        <v>0.3438219493476592</v>
       </c>
       <c r="M18">
-        <v>0.999</v>
+        <v>23.6</v>
       </c>
       <c r="N18">
-        <v>0.007045133991537376</v>
+        <v>0.0885885885885886</v>
       </c>
       <c r="O18">
-        <v>-0.06283018867924528</v>
+        <v>0.5267857142857143</v>
       </c>
       <c r="P18">
-        <v>0.999</v>
+        <v>23.6</v>
       </c>
       <c r="Q18">
-        <v>0.007045133991537376</v>
+        <v>0.0885885885885886</v>
       </c>
       <c r="R18">
-        <v>-0.06283018867924528</v>
+        <v>0.5267857142857143</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2630,55 +2603,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>7.53</v>
+        <v>71.5</v>
       </c>
       <c r="V18">
-        <v>0.05310296191819464</v>
+        <v>0.2683933933933934</v>
       </c>
       <c r="W18">
-        <v>-0.1760797342192691</v>
+        <v>0.100044662795891</v>
       </c>
       <c r="X18">
-        <v>0.02572331345675135</v>
+        <v>0.05848931780907542</v>
       </c>
       <c r="Y18">
-        <v>-0.2018030476760205</v>
+        <v>0.0415553449868156</v>
       </c>
       <c r="Z18">
-        <v>-0.04539781591263651</v>
+        <v>0.2512533744697262</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.02651155972515213</v>
+        <v>0.05221155630357444</v>
       </c>
       <c r="AC18">
-        <v>-0.02651155972515213</v>
+        <v>-0.05221155630357444</v>
       </c>
       <c r="AD18">
-        <v>30.4</v>
+        <v>253.7</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>30.4</v>
+        <v>253.7</v>
       </c>
       <c r="AG18">
-        <v>22.87</v>
+        <v>182.2</v>
       </c>
       <c r="AH18">
-        <v>0.1765389082462253</v>
+        <v>0.4877908094597194</v>
       </c>
       <c r="AI18">
-        <v>0.2198120028922632</v>
+        <v>0.3460174577195854</v>
       </c>
       <c r="AJ18">
-        <v>0.1388838282625857</v>
+        <v>0.4061524743646902</v>
       </c>
       <c r="AK18">
-        <v>0.1748872065458438</v>
+        <v>0.2753513676892851</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2695,7 +2668,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AEON Credit Service (Asia) Company Limited (SEHK:900)</t>
+          <t>Hong Kong Finance Group Limited (SEHK:1273)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2704,10 +2677,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.00663</v>
+        <v>0.107</v>
       </c>
       <c r="E19">
-        <v>0.0115</v>
+        <v>0.0784</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2722,28 +2695,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>40.3</v>
+        <v>7.9</v>
       </c>
       <c r="L19">
-        <v>0.3375209380234506</v>
+        <v>0.4846625766871165</v>
       </c>
       <c r="M19">
-        <v>21.5</v>
+        <v>1.37</v>
       </c>
       <c r="N19">
-        <v>0.08055451479955041</v>
+        <v>0.07445652173913045</v>
       </c>
       <c r="O19">
-        <v>0.533498759305211</v>
+        <v>0.1734177215189873</v>
       </c>
       <c r="P19">
-        <v>21.5</v>
+        <v>1.37</v>
       </c>
       <c r="Q19">
-        <v>0.08055451479955041</v>
+        <v>0.07445652173913045</v>
       </c>
       <c r="R19">
-        <v>0.533498759305211</v>
+        <v>0.1734177215189873</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2752,55 +2725,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>68.09999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="V19">
-        <v>0.2551517422255526</v>
+        <v>0.625</v>
       </c>
       <c r="W19">
-        <v>0.09173685408604597</v>
+        <v>0.08700440528634362</v>
       </c>
       <c r="X19">
-        <v>0.02802579679340932</v>
+        <v>0.07669463644033186</v>
       </c>
       <c r="Y19">
-        <v>0.06371105729263665</v>
+        <v>0.01030976884601176</v>
       </c>
       <c r="Z19">
-        <v>0.2327031767686611</v>
+        <v>0.1194489227612487</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.02657539790791055</v>
+        <v>0.0535061818452679</v>
       </c>
       <c r="AC19">
-        <v>-0.02657539790791055</v>
+        <v>-0.0535061818452679</v>
       </c>
       <c r="AD19">
-        <v>138.9</v>
+        <v>54.1</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>138.9</v>
+        <v>54.1</v>
       </c>
       <c r="AG19">
-        <v>70.80000000000001</v>
+        <v>42.6</v>
       </c>
       <c r="AH19">
-        <v>0.34228684080828</v>
+        <v>0.7462068965517241</v>
       </c>
       <c r="AI19">
-        <v>0.2367479120504517</v>
+        <v>0.3589913735899138</v>
       </c>
       <c r="AJ19">
-        <v>0.2096535386437667</v>
+        <v>0.6983606557377049</v>
       </c>
       <c r="AK19">
-        <v>0.1365214037794061</v>
+        <v>0.3060344827586207</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2817,7 +2790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>International Alliance Financial Leasing Co., Ltd. (SEHK:1563)</t>
+          <t>Sun Hung Kai &amp; Co. Limited (SEHK:86)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2825,6 +2798,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.0247</v>
+      </c>
+      <c r="F20">
+        <v>0.1</v>
+      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2832,94 +2811,103 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.001429786020694399</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>0.0007148930103471996</v>
       </c>
       <c r="K20">
-        <v>15</v>
+        <v>-35.7</v>
       </c>
       <c r="L20">
-        <v>0.3947368421052632</v>
+        <v>-0.09826589595375723</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>72.50999999999999</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.09807926416880833</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>-2.031092436974789</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.09008521574462329</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>-1.865546218487395</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>5.909999999999997</v>
+      </c>
+      <c r="T20">
+        <v>0.08150599917252789</v>
       </c>
       <c r="U20">
-        <v>32.7</v>
+        <v>1039.7</v>
       </c>
       <c r="V20">
-        <v>0.06588756800322386</v>
+        <v>1.40633031245773</v>
       </c>
       <c r="W20">
-        <v>0.09242144177449167</v>
+        <v>-0.01096336332647483</v>
       </c>
       <c r="X20">
-        <v>0.02685875696904134</v>
+        <v>0.08173766854507669</v>
       </c>
       <c r="Y20">
-        <v>0.06556268480545033</v>
+        <v>-0.09270103187155153</v>
       </c>
       <c r="Z20">
-        <v>0.09433962264150943</v>
+        <v>0.08024813893148271</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>5.736883361548798e-05</v>
       </c>
       <c r="AB20">
-        <v>0.02706893858976343</v>
+        <v>0.05366208638981464</v>
       </c>
       <c r="AC20">
-        <v>-0.02706893858976343</v>
+        <v>-0.05360471755619915</v>
       </c>
       <c r="AD20">
-        <v>181.3</v>
+        <v>2580.2</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>0.6077936934086237</v>
       </c>
       <c r="AF20">
-        <v>181.3</v>
+        <v>2580.807793693408</v>
       </c>
       <c r="AG20">
-        <v>148.6</v>
+        <v>1541.107793693408</v>
       </c>
       <c r="AH20">
-        <v>0.2675619834710744</v>
+        <v>0.7773265068669425</v>
       </c>
       <c r="AI20">
-        <v>0.4852783725910064</v>
+        <v>0.4280295974395814</v>
       </c>
       <c r="AJ20">
-        <v>0.2304233214451853</v>
+        <v>0.6758035987929114</v>
       </c>
       <c r="AK20">
-        <v>0.4359049574655324</v>
+        <v>0.3088511336330843</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>4025.273010920436</v>
+      </c>
+      <c r="AP20">
+        <v>2404.224327134802</v>
       </c>
     </row>
     <row r="21">
@@ -2930,7 +2918,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hao Wen Holdings Limited (SEHK:8019)</t>
+          <t>Oi Wah Pawnshop Credit Holdings Limited (SEHK:1319)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2939,7 +2927,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.00508</v>
+        <v>-0.0441</v>
+      </c>
+      <c r="E21">
+        <v>-0.0553</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2954,82 +2945,85 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>-3.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L21">
-        <v>-0.6605960264900662</v>
+        <v>0.5297872340425532</v>
       </c>
       <c r="M21">
-        <v>-0</v>
+        <v>3.736</v>
       </c>
       <c r="N21">
-        <v>-0</v>
+        <v>0.06300168634064082</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>0.3751004016064257</v>
       </c>
       <c r="P21">
-        <v>-0</v>
+        <v>3.66</v>
       </c>
       <c r="Q21">
-        <v>-0</v>
+        <v>0.06172006745362564</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>0.3674698795180723</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>0.07600000000000007</v>
+      </c>
+      <c r="T21">
+        <v>0.02034261241970023</v>
       </c>
       <c r="U21">
-        <v>0.727</v>
+        <v>14.4</v>
       </c>
       <c r="V21">
-        <v>0.07127450980392157</v>
+        <v>0.2428330522765599</v>
       </c>
       <c r="W21">
-        <v>-0.07673076923076924</v>
+        <v>0.0803225806451613</v>
       </c>
       <c r="X21">
-        <v>0.03002599310606296</v>
+        <v>0.05313452367109668</v>
       </c>
       <c r="Y21">
-        <v>-0.1067567623368322</v>
+        <v>0.02718805697406462</v>
       </c>
       <c r="Z21">
-        <v>0.1065857273946495</v>
+        <v>0.1558872305140962</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.02897763011828816</v>
+        <v>0.05369565510106083</v>
       </c>
       <c r="AC21">
-        <v>-0.02897763011828816</v>
+        <v>-0.05369565510106083</v>
       </c>
       <c r="AD21">
-        <v>8.02</v>
+        <v>21.8</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>8.02</v>
+        <v>21.8</v>
       </c>
       <c r="AG21">
-        <v>7.292999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AH21">
-        <v>0.4401756311745335</v>
+        <v>0.2688039457459926</v>
       </c>
       <c r="AI21">
-        <v>0.1452372328866353</v>
+        <v>0.1453333333333333</v>
       </c>
       <c r="AJ21">
-        <v>0.4169096209912536</v>
+        <v>0.1109445277361319</v>
       </c>
       <c r="AK21">
-        <v>0.1338337034114473</v>
+        <v>0.05457227138643068</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3046,7 +3040,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sun Hung Kai &amp; Co. Limited (SEHK:86)</t>
+          <t>Allied Group Limited (SEHK:373)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3055,13 +3049,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0582</v>
+        <v>0.1</v>
       </c>
       <c r="E22">
-        <v>0.53</v>
-      </c>
-      <c r="F22">
-        <v>0.19</v>
+        <v>-0.0353</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3070,103 +3061,97 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0.0008060600338754083</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>0.0007399763965429117</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>585.3</v>
+        <v>495.1</v>
       </c>
       <c r="L22">
-        <v>1.889283408650742</v>
+        <v>0.6973239436619718</v>
       </c>
       <c r="M22">
-        <v>73.92</v>
+        <v>59.797</v>
       </c>
       <c r="N22">
-        <v>0.0702394526795895</v>
+        <v>0.07208800482218203</v>
       </c>
       <c r="O22">
-        <v>0.1262942080984111</v>
+        <v>0.1207776206826904</v>
       </c>
       <c r="P22">
-        <v>66.40000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="Q22">
-        <v>0.06309388065374383</v>
+        <v>0.07148884870403857</v>
       </c>
       <c r="R22">
-        <v>0.1134460960191355</v>
+        <v>0.1197737830741264</v>
       </c>
       <c r="S22">
-        <v>7.519999999999996</v>
+        <v>0.4969999999999999</v>
       </c>
       <c r="T22">
-        <v>0.1017316017316017</v>
+        <v>0.008311453751860459</v>
       </c>
       <c r="U22">
-        <v>745.2</v>
+        <v>1492.8</v>
       </c>
       <c r="V22">
-        <v>0.7080957810718358</v>
+        <v>1.799638336347197</v>
       </c>
       <c r="W22">
-        <v>0.2197237029807042</v>
+        <v>0.09369086367421089</v>
       </c>
       <c r="X22">
-        <v>0.04071612517073366</v>
+        <v>0.09233341909543141</v>
       </c>
       <c r="Y22">
-        <v>0.1790075778099706</v>
+        <v>0.001357444578779482</v>
       </c>
       <c r="Z22">
-        <v>0.08343654244641463</v>
+        <v>0.09761597052272666</v>
       </c>
       <c r="AA22">
-        <v>6.17410720194976e-05</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.02906653851105018</v>
+        <v>0.05389061207302159</v>
       </c>
       <c r="AC22">
-        <v>-0.02900479743903069</v>
+        <v>-0.05389061207302159</v>
       </c>
       <c r="AD22">
-        <v>2322.5</v>
+        <v>3855.4</v>
       </c>
       <c r="AE22">
-        <v>0.3014130075269924</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2322.801413007527</v>
+        <v>3855.4</v>
       </c>
       <c r="AG22">
-        <v>1577.601413007527</v>
+        <v>2362.6</v>
       </c>
       <c r="AH22">
-        <v>0.6881963855714784</v>
+        <v>0.822941791713804</v>
       </c>
       <c r="AI22">
-        <v>0.3878121487646785</v>
+        <v>0.3001806347130088</v>
       </c>
       <c r="AJ22">
-        <v>0.5998481237329328</v>
+        <v>0.7401397199335861</v>
       </c>
       <c r="AK22">
-        <v>0.3008220330537403</v>
+        <v>0.2081439193713218</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
         <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>7491.935483870968</v>
-      </c>
-      <c r="AP22">
-        <v>5089.036816153313</v>
       </c>
     </row>
     <row r="23">
@@ -3177,7 +3162,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hong Kong Finance Group Limited (SEHK:1273)</t>
+          <t>Hao Wen Holdings Limited (SEHK:8019)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3186,10 +3171,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.098</v>
-      </c>
-      <c r="E23">
-        <v>0.0998</v>
+        <v>-0.038</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3204,85 +3186,82 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>9.58</v>
+        <v>-1.71</v>
       </c>
       <c r="L23">
-        <v>0.5702380952380952</v>
+        <v>-0.3190298507462686</v>
       </c>
       <c r="M23">
-        <v>1.39</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>0.06017316017316016</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>0.1450939457202505</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>1.39</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.06017316017316016</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.1450939457202505</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>0.1965367965367965</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>0.115421686746988</v>
+        <v>-0.03468559837728195</v>
       </c>
       <c r="X23">
-        <v>0.04046042117223878</v>
+        <v>0.0551134216040054</v>
       </c>
       <c r="Y23">
-        <v>0.07496126557474918</v>
+        <v>-0.08979901998128734</v>
       </c>
       <c r="Z23">
-        <v>0.1263157894736842</v>
+        <v>0.09523132684244191</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.02904248744263938</v>
+        <v>0.05515345331111729</v>
       </c>
       <c r="AC23">
-        <v>-0.02904248744263938</v>
+        <v>-0.05515345331111729</v>
       </c>
       <c r="AD23">
-        <v>50.2</v>
+        <v>7.88</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>50.2</v>
+        <v>7.88</v>
       </c>
       <c r="AG23">
-        <v>45.66</v>
+        <v>7.88</v>
       </c>
       <c r="AH23">
-        <v>0.6848567530695771</v>
+        <v>0.3685687558465856</v>
       </c>
       <c r="AI23">
-        <v>0.3560283687943263</v>
+        <v>0.1513056835637481</v>
       </c>
       <c r="AJ23">
-        <v>0.6640488656195462</v>
+        <v>0.3685687558465856</v>
       </c>
       <c r="AK23">
-        <v>0.334603546826909</v>
+        <v>0.1513056835637481</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3299,7 +3278,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Allied Group Limited (SEHK:373)</t>
+          <t>China Tonghai International Financial Limited (SEHK:952)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3307,104 +3286,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D24">
-        <v>0.116</v>
-      </c>
-      <c r="E24">
-        <v>0.237</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
       <c r="K24">
-        <v>522.6</v>
-      </c>
-      <c r="L24">
-        <v>0.9015007762635846</v>
+        <v>-321.1</v>
       </c>
       <c r="M24">
-        <v>56.6</v>
+        <v>-0</v>
       </c>
       <c r="N24">
-        <v>0.04599382415082074</v>
+        <v>-0</v>
       </c>
       <c r="O24">
-        <v>0.1083046306926904</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>56.6</v>
+        <v>-0</v>
       </c>
       <c r="Q24">
-        <v>0.04599382415082074</v>
+        <v>-0</v>
       </c>
       <c r="R24">
-        <v>0.1083046306926904</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
       <c r="U24">
-        <v>808.6</v>
+        <v>27.2</v>
       </c>
       <c r="V24">
-        <v>0.6570778482041282</v>
+        <v>0.1845318860244233</v>
       </c>
       <c r="W24">
-        <v>0.1465425382760361</v>
+        <v>-0.424454725710509</v>
       </c>
       <c r="X24">
-        <v>0.04131885398033282</v>
+        <v>0.05918064661080635</v>
       </c>
       <c r="Y24">
-        <v>0.1052236842957033</v>
+        <v>-0.4836353723213153</v>
       </c>
       <c r="Z24">
-        <v>0.1189860426929393</v>
+        <v>0</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.02912126240291488</v>
+        <v>0.05717419102150335</v>
       </c>
       <c r="AC24">
-        <v>-0.02912126240291488</v>
+        <v>-0.05717419102150335</v>
       </c>
       <c r="AD24">
-        <v>2814.7</v>
+        <v>151.5</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>2814.7</v>
+        <v>151.5</v>
       </c>
       <c r="AG24">
-        <v>2006.1</v>
+        <v>124.3</v>
       </c>
       <c r="AH24">
-        <v>0.6957951202630213</v>
+        <v>0.506858481097357</v>
       </c>
       <c r="AI24">
-        <v>0.3000714278099381</v>
+        <v>0.2619294605809129</v>
       </c>
       <c r="AJ24">
-        <v>0.6197979423486885</v>
+        <v>0.4574898785425101</v>
       </c>
       <c r="AK24">
-        <v>0.234043049641253</v>
+        <v>0.2255079825834543</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3421,7 +3376,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shougang Concord Grand (Group) Limited (SEHK:730)</t>
+          <t>CSSC (Hong Kong) Shipping Company Limited (SEHK:3877)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3429,9 +3384,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D25">
-        <v>1.593</v>
-      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3445,82 +3397,85 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>1.97</v>
+        <v>201.3</v>
       </c>
       <c r="L25">
-        <v>0.01302048909451421</v>
+        <v>0.6604330708661418</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.07711688027166175</v>
       </c>
       <c r="O25">
-        <v>-0</v>
+        <v>0.3497267759562842</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.07711688027166175</v>
       </c>
       <c r="R25">
-        <v>-0</v>
+        <v>0.3497267759562842</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
       <c r="U25">
-        <v>26.3</v>
+        <v>161.8</v>
       </c>
       <c r="V25">
-        <v>0.3065268065268065</v>
+        <v>0.1772373753970862</v>
       </c>
       <c r="W25">
-        <v>0.0114868804664723</v>
+        <v>0.1664737016209064</v>
       </c>
       <c r="X25">
-        <v>0.02710051147675033</v>
+        <v>0.08717370225196334</v>
       </c>
       <c r="Y25">
-        <v>-0.01561363101027803</v>
+        <v>0.07929999936894304</v>
       </c>
       <c r="Z25">
-        <v>1.270894582108358</v>
+        <v>0.07688039146446048</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.02931225010417228</v>
+        <v>0.05895728017123679</v>
       </c>
       <c r="AC25">
-        <v>-0.02931225010417228</v>
+        <v>-0.05895728017123679</v>
       </c>
       <c r="AD25">
-        <v>34.1</v>
+        <v>3728.7</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>34.1</v>
+        <v>3728.7</v>
       </c>
       <c r="AG25">
-        <v>7.800000000000001</v>
+        <v>3566.9</v>
       </c>
       <c r="AH25">
-        <v>0.2844036697247707</v>
+        <v>0.8033221302998966</v>
       </c>
       <c r="AI25">
-        <v>0.1294608959757023</v>
+        <v>0.7270688713828874</v>
       </c>
       <c r="AJ25">
-        <v>0.08333333333333334</v>
+        <v>0.7962185811866601</v>
       </c>
       <c r="AK25">
-        <v>0.03289751159848165</v>
+        <v>0.7181774252003382</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3537,7 +3492,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Styland Holdings Limited (SEHK:211)</t>
+          <t>VCREDIT Holdings Limited (SEHK:2003)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3545,113 +3500,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D26">
-        <v>-0.038</v>
-      </c>
       <c r="G26">
-        <v>0</v>
+        <v>0.03545721141029059</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0.004065928741102566</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>0.004065928741102566</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>-6.47</v>
+        <v>108.9</v>
       </c>
       <c r="L26">
-        <v>-1.359243697478992</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="M26">
-        <v>0.602</v>
+        <v>8.57</v>
       </c>
       <c r="N26">
-        <v>0.02306513409961686</v>
+        <v>0.04698464912280702</v>
       </c>
       <c r="O26">
-        <v>-0.09304482225656878</v>
+        <v>0.07869605142332414</v>
       </c>
       <c r="P26">
-        <v>0.602</v>
+        <v>6.03</v>
       </c>
       <c r="Q26">
-        <v>0.02306513409961686</v>
+        <v>0.03305921052631579</v>
       </c>
       <c r="R26">
-        <v>-0.09304482225656878</v>
+        <v>0.05537190082644628</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>0.2963827304550758</v>
       </c>
       <c r="U26">
-        <v>8.48</v>
+        <v>275.1</v>
       </c>
       <c r="V26">
-        <v>0.324904214559387</v>
+        <v>1.508223684210526</v>
       </c>
       <c r="W26">
-        <v>-0.1018897637795276</v>
+        <v>0.2279673435210383</v>
       </c>
       <c r="X26">
-        <v>0.03213072877862101</v>
+        <v>0.09395668969015894</v>
       </c>
       <c r="Y26">
-        <v>-0.1340204925581486</v>
+        <v>0.1340106538308794</v>
       </c>
       <c r="Z26">
-        <v>0.05985672295215706</v>
+        <v>0.2869492044063647</v>
       </c>
       <c r="AA26">
-        <v>0.000243373170199389</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.02981582805529429</v>
+        <v>0.0592433471881823</v>
       </c>
       <c r="AC26">
-        <v>-0.02957245488509491</v>
+        <v>-0.0592433471881823</v>
       </c>
       <c r="AD26">
-        <v>27.8</v>
+        <v>880.1</v>
       </c>
       <c r="AE26">
-        <v>0.02323089596175896</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>27.82323089596176</v>
+        <v>880.1</v>
       </c>
       <c r="AG26">
-        <v>19.34323089596176</v>
+        <v>605</v>
       </c>
       <c r="AH26">
-        <v>0.5159785575468069</v>
+        <v>0.8283294117647059</v>
       </c>
       <c r="AI26">
-        <v>0.3276280306627476</v>
+        <v>0.6171376481312671</v>
       </c>
       <c r="AJ26">
-        <v>0.4256570343831046</v>
+        <v>0.7683515367030734</v>
       </c>
       <c r="AK26">
-        <v>0.2530404676679305</v>
+        <v>0.525629887054735</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
         <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>1158.333333333333</v>
-      </c>
-      <c r="AP26">
-        <v>805.9679539984066</v>
       </c>
     </row>
     <row r="27">
@@ -3662,7 +3608,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VCREDIT Holdings Limited (SEHK:2003)</t>
+          <t>Gome Finance Technology Co., Ltd. (SEHK:628)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3671,7 +3617,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>0.03543083900226757</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -3683,85 +3629,82 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>153.2</v>
+        <v>-20</v>
       </c>
       <c r="L27">
-        <v>0.4342403628117913</v>
+        <v>-2.212389380530974</v>
       </c>
       <c r="M27">
-        <v>9.561</v>
+        <v>-0</v>
       </c>
       <c r="N27">
-        <v>0.03602486812358704</v>
+        <v>-0</v>
       </c>
       <c r="O27">
-        <v>0.06240861618798956</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>6.331</v>
+        <v>-0</v>
       </c>
       <c r="Q27">
-        <v>0.02385455915599096</v>
+        <v>-0</v>
       </c>
       <c r="R27">
-        <v>0.04132506527415144</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>3.23</v>
-      </c>
-      <c r="T27">
-        <v>0.3378307708398703</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>255.6</v>
+        <v>33.4</v>
       </c>
       <c r="V27">
-        <v>0.9630746043707612</v>
+        <v>0.4751066856330014</v>
       </c>
       <c r="W27">
-        <v>0.5260989010989011</v>
+        <v>-0.07572889057175312</v>
       </c>
       <c r="X27">
-        <v>0.05487109098832749</v>
+        <v>0.06692460133560967</v>
       </c>
       <c r="Y27">
-        <v>0.4712278101105736</v>
+        <v>-0.1426534919073628</v>
       </c>
       <c r="Z27">
-        <v>0.3759190197123069</v>
+        <v>0.02484881803188565</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.02989677918155202</v>
+        <v>0.0592947601776672</v>
       </c>
       <c r="AC27">
-        <v>-0.02989677918155202</v>
+        <v>-0.0592947601776672</v>
       </c>
       <c r="AD27">
-        <v>1085.1</v>
+        <v>131.7</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>1085.1</v>
+        <v>131.7</v>
       </c>
       <c r="AG27">
-        <v>829.4999999999999</v>
+        <v>98.29999999999998</v>
       </c>
       <c r="AH27">
-        <v>0.8034801925212883</v>
+        <v>0.6519801980198019</v>
       </c>
       <c r="AI27">
-        <v>0.6941086163884091</v>
+        <v>0.3558497703323426</v>
       </c>
       <c r="AJ27">
-        <v>0.7576034341035711</v>
+        <v>0.5830367734282326</v>
       </c>
       <c r="AK27">
-        <v>0.6343197981188345</v>
+        <v>0.2919512919512919</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3787,7 +3730,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.156</v>
+        <v>-0.485</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3802,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>2.58</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L28">
-        <v>0.548936170212766</v>
+        <v>-32.21498371335505</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3814,7 +3757,7 @@
         <v>-0</v>
       </c>
       <c r="O28">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P28">
         <v>-0</v>
@@ -3823,61 +3766,61 @@
         <v>-0</v>
       </c>
       <c r="R28">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>0.577</v>
+        <v>1.16</v>
       </c>
       <c r="V28">
-        <v>0.03297142857142857</v>
+        <v>0.1611111111111111</v>
       </c>
       <c r="W28">
-        <v>0.03189122373300371</v>
+        <v>-0.116903073286052</v>
       </c>
       <c r="X28">
-        <v>0.03296674573002711</v>
+        <v>0.07177270459580326</v>
       </c>
       <c r="Y28">
-        <v>-0.001075521997023397</v>
+        <v>-0.1886757778818553</v>
       </c>
       <c r="Z28">
-        <v>0.04680808684393984</v>
+        <v>0.002934345220458217</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.03008899326264616</v>
+        <v>0.06008590563725386</v>
       </c>
       <c r="AC28">
-        <v>-0.03008899326264616</v>
+        <v>-0.06008590563725386</v>
       </c>
       <c r="AD28">
-        <v>20.6</v>
+        <v>17.3</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>20.6</v>
+        <v>17.3</v>
       </c>
       <c r="AG28">
-        <v>20.023</v>
+        <v>16.14</v>
       </c>
       <c r="AH28">
-        <v>0.5406824146981627</v>
+        <v>0.7061224489795919</v>
       </c>
       <c r="AI28">
-        <v>0.1958174904942966</v>
+        <v>0.1787190082644628</v>
       </c>
       <c r="AJ28">
-        <v>0.5336193801135304</v>
+        <v>0.6915167095115682</v>
       </c>
       <c r="AK28">
-        <v>0.1913823920170518</v>
+        <v>0.1687578419071518</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3894,7 +3837,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gome Finance Technology Co., Ltd. (SEHK:628)</t>
+          <t>Aceso Life Science Group Limited (SEHK:474)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3902,6 +3845,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D29">
+        <v>-0.0533</v>
+      </c>
       <c r="G29">
         <v>0</v>
       </c>
@@ -3909,25 +3855,25 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>0.004882066335114467</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>0.004882066335114467</v>
       </c>
       <c r="K29">
-        <v>2.08</v>
+        <v>-43.1</v>
       </c>
       <c r="L29">
-        <v>0.2740447957839262</v>
+        <v>-2.023474178403756</v>
       </c>
       <c r="M29">
-        <v>-0</v>
+        <v>0.764</v>
       </c>
       <c r="N29">
-        <v>-0</v>
+        <v>0.006725352112676056</v>
       </c>
       <c r="O29">
-        <v>-0</v>
+        <v>-0.01772621809744779</v>
       </c>
       <c r="P29">
         <v>-0</v>
@@ -3936,67 +3882,76 @@
         <v>-0</v>
       </c>
       <c r="R29">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>0.764</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
       </c>
       <c r="U29">
-        <v>30.4</v>
+        <v>34.8</v>
       </c>
       <c r="V29">
-        <v>0.3374028856825749</v>
+        <v>0.3063380281690141</v>
       </c>
       <c r="W29">
-        <v>0.00827037773359841</v>
+        <v>-0.1544802867383513</v>
       </c>
       <c r="X29">
-        <v>0.03497411531587734</v>
+        <v>0.07782419308461461</v>
       </c>
       <c r="Y29">
-        <v>-0.02670373758227893</v>
+        <v>-0.2323044798229659</v>
       </c>
       <c r="Z29">
-        <v>0.02066993464052288</v>
+        <v>0.03275310314450209</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>0.0001599028222323054</v>
       </c>
       <c r="AB29">
-        <v>0.03064346640445252</v>
+        <v>0.06078419655412031</v>
       </c>
       <c r="AC29">
-        <v>-0.03064346640445252</v>
+        <v>-0.060624293731888</v>
       </c>
       <c r="AD29">
-        <v>130.1</v>
+        <v>347.9</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>0.1200599353103094</v>
       </c>
       <c r="AF29">
-        <v>130.1</v>
+        <v>348.0200599353103</v>
       </c>
       <c r="AG29">
-        <v>99.69999999999999</v>
+        <v>313.2200599353103</v>
       </c>
       <c r="AH29">
-        <v>0.5908265213442325</v>
+        <v>0.7539101744930247</v>
       </c>
       <c r="AI29">
-        <v>0.3300355149670218</v>
+        <v>0.5033409935602263</v>
       </c>
       <c r="AJ29">
-        <v>0.5252897787144363</v>
+        <v>0.7338456865939773</v>
       </c>
       <c r="AK29">
-        <v>0.2740516767454645</v>
+        <v>0.4770187191146254</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
         <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>2717.96875</v>
+      </c>
+      <c r="AP29">
+        <v>2447.031718244612</v>
       </c>
     </row>
     <row r="30">
@@ -4007,7 +3962,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>China Tonghai International Financial Limited (SEHK:952)</t>
+          <t>Styland Holdings Limited (SEHK:211)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4015,104 +3970,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D30">
+        <v>-0.243</v>
+      </c>
+      <c r="E30">
+        <v>0.05889999999999999</v>
+      </c>
       <c r="G30">
-        <v>0.001783893985728848</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>0.005141812348592668</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>0.005141812348592668</v>
       </c>
       <c r="K30">
-        <v>35.9</v>
+        <v>1.12</v>
       </c>
       <c r="L30">
-        <v>0.3659531090723752</v>
+        <v>0.4725738396624473</v>
       </c>
       <c r="M30">
-        <v>3.99</v>
+        <v>-0</v>
       </c>
       <c r="N30">
-        <v>0.0255278310940499</v>
+        <v>-0</v>
       </c>
       <c r="O30">
-        <v>0.1111420612813371</v>
+        <v>-0</v>
       </c>
       <c r="P30">
-        <v>3.99</v>
+        <v>-0</v>
       </c>
       <c r="Q30">
-        <v>0.0255278310940499</v>
+        <v>-0</v>
       </c>
       <c r="R30">
-        <v>0.1111420612813371</v>
+        <v>-0</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
       <c r="U30">
-        <v>42.3</v>
+        <v>5.88</v>
       </c>
       <c r="V30">
-        <v>0.2706333973128598</v>
+        <v>0.8609077598828697</v>
       </c>
       <c r="W30">
-        <v>0.04949675996139528</v>
+        <v>0.01961471103327496</v>
       </c>
       <c r="X30">
-        <v>0.03555224819932002</v>
+        <v>0.09014671505484201</v>
       </c>
       <c r="Y30">
-        <v>0.01394451176207526</v>
+        <v>-0.07053200402156705</v>
       </c>
       <c r="Z30">
-        <v>0.09763136942675159</v>
+        <v>0.03100711521406154</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>0.0001594327679018972</v>
       </c>
       <c r="AB30">
-        <v>0.0307813874464981</v>
+        <v>0.06167870272574415</v>
       </c>
       <c r="AC30">
-        <v>-0.0307813874464981</v>
+        <v>-0.06151926995784226</v>
       </c>
       <c r="AD30">
-        <v>237.7</v>
+        <v>30.1</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>0.01406952366917688</v>
       </c>
       <c r="AF30">
-        <v>237.7</v>
+        <v>30.11406952366918</v>
       </c>
       <c r="AG30">
-        <v>195.4</v>
+        <v>24.23406952366918</v>
       </c>
       <c r="AH30">
-        <v>0.6032994923857867</v>
+        <v>0.8151259434041456</v>
       </c>
       <c r="AI30">
-        <v>0.2390867028766847</v>
+        <v>0.3417623279285716</v>
       </c>
       <c r="AJ30">
-        <v>0.5555871481376172</v>
+        <v>0.7801318338282787</v>
       </c>
       <c r="AK30">
-        <v>0.2052736631999159</v>
+        <v>0.2946962209707251</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
         <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>2006.666666666667</v>
+      </c>
+      <c r="AP30">
+        <v>1615.604634911279</v>
       </c>
     </row>
     <row r="31">
@@ -4123,7 +4087,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aceso Life Science Group Limited (SEHK:474)</t>
+          <t>China Everbright Limited (SEHK:165)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4132,109 +4096,118 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.004500000000000001</v>
+        <v>-0.407</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>10.76017130620985</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>10.76017130620985</v>
       </c>
       <c r="I31">
-        <v>0.01109027578263424</v>
+        <v>-1.693790149892933</v>
       </c>
       <c r="J31">
-        <v>0.005545137891317118</v>
+        <v>-1.693790149892933</v>
       </c>
       <c r="K31">
-        <v>-3.21</v>
+        <v>-226</v>
       </c>
       <c r="L31">
-        <v>-0.3422174840085287</v>
+        <v>-4.839400428265525</v>
       </c>
       <c r="M31">
-        <v>-0</v>
+        <v>135.9</v>
       </c>
       <c r="N31">
-        <v>-0</v>
+        <v>0.1082264872182846</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>-0.6013274336283186</v>
       </c>
       <c r="P31">
-        <v>-0</v>
+        <v>135.9</v>
       </c>
       <c r="Q31">
-        <v>-0</v>
+        <v>0.1082264872182846</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>-0.6013274336283186</v>
       </c>
       <c r="S31">
         <v>0</v>
       </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
       <c r="U31">
-        <v>46.9</v>
+        <v>1319.4</v>
       </c>
       <c r="V31">
-        <v>0.2488063660477454</v>
+        <v>1.050728677231823</v>
       </c>
       <c r="W31">
-        <v>-0.0115218951902369</v>
+        <v>-0.03579290793620626</v>
       </c>
       <c r="X31">
-        <v>0.04080304307228329</v>
+        <v>0.08371487560484642</v>
       </c>
       <c r="Y31">
-        <v>-0.05232493826252019</v>
+        <v>-0.1195077835410527</v>
       </c>
       <c r="Z31">
-        <v>0.01721590967302478</v>
+        <v>0.004818854412811755</v>
       </c>
       <c r="AA31">
-        <v>9.546459306138259e-05</v>
+        <v>-0.008162128138188646</v>
       </c>
       <c r="AB31">
-        <v>0.03173251769540115</v>
+        <v>0.05371325642863657</v>
       </c>
       <c r="AC31">
-        <v>-0.03163705310233977</v>
+        <v>-0.06187538456682522</v>
       </c>
       <c r="AD31">
-        <v>418.1</v>
+        <v>4654.6</v>
       </c>
       <c r="AE31">
-        <v>0.1248660657944544</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>418.2248660657945</v>
+        <v>4654.6</v>
       </c>
       <c r="AG31">
-        <v>371.3248660657945</v>
+        <v>3335.2</v>
       </c>
       <c r="AH31">
-        <v>0.6893155192034627</v>
+        <v>0.7875403955805966</v>
       </c>
       <c r="AI31">
-        <v>0.5064328809305604</v>
+        <v>0.4462532597024083</v>
       </c>
       <c r="AJ31">
-        <v>0.6632875539725558</v>
+        <v>0.7264806464963297</v>
       </c>
       <c r="AK31">
-        <v>0.4767146129783836</v>
+        <v>0.3660630007683021</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>120.1</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>120.1</v>
       </c>
       <c r="AN31">
-        <v>3241.08527131783</v>
+        <v>-61.08398950131234</v>
+      </c>
+      <c r="AO31">
+        <v>-0.6586178184845961</v>
       </c>
       <c r="AP31">
-        <v>2878.487333843368</v>
+        <v>-43.76902887139108</v>
+      </c>
+      <c r="AQ31">
+        <v>-0.6586178184845961</v>
       </c>
     </row>
     <row r="32">
@@ -4245,7 +4218,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CSSC (Hong Kong) Shipping Company Limited (SEHK:3877)</t>
+          <t>Lerado Financial Group Company Limited (SEHK:1225)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4253,104 +4226,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D32">
+        <v>-0.0204</v>
+      </c>
       <c r="G32">
-        <v>0</v>
+        <v>0.1344</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>0.1344</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>-0.01472</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>-0.01472</v>
       </c>
       <c r="K32">
-        <v>160.9</v>
+        <v>-20.2</v>
       </c>
       <c r="L32">
-        <v>0.7761698022190062</v>
+        <v>-0.8079999999999999</v>
       </c>
       <c r="M32">
-        <v>23.7</v>
+        <v>-0</v>
       </c>
       <c r="N32">
-        <v>0.02763203917453655</v>
+        <v>-0</v>
       </c>
       <c r="O32">
-        <v>0.1472964574269733</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>23.7</v>
+        <v>-0</v>
       </c>
       <c r="Q32">
-        <v>0.02763203917453655</v>
+        <v>-0</v>
       </c>
       <c r="R32">
-        <v>0.1472964574269733</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
       <c r="U32">
-        <v>211.2</v>
+        <v>20</v>
       </c>
       <c r="V32">
-        <v>0.2462399440363763</v>
+        <v>3.5650623885918</v>
       </c>
       <c r="W32">
-        <v>0.1479540229885057</v>
+        <v>-0.1416549789621318</v>
       </c>
       <c r="X32">
-        <v>0.05013300011198802</v>
+        <v>0.2154626832364991</v>
       </c>
       <c r="Y32">
-        <v>0.09782102287651773</v>
+        <v>-0.3571176621986309</v>
       </c>
       <c r="Z32">
-        <v>0.05925565973016236</v>
+        <v>0.1137915339098771</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>-0.001675011379153391</v>
       </c>
       <c r="AB32">
-        <v>0.03268798380166102</v>
+        <v>0.06060799889205788</v>
       </c>
       <c r="AC32">
-        <v>-0.03268798380166102</v>
+        <v>-0.06228301027121127</v>
       </c>
       <c r="AD32">
-        <v>2966.6</v>
+        <v>101.5</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>2966.6</v>
+        <v>101.5</v>
       </c>
       <c r="AG32">
-        <v>2755.4</v>
+        <v>81.5</v>
       </c>
       <c r="AH32">
-        <v>0.7757236618466123</v>
+        <v>0.9476239380076557</v>
       </c>
       <c r="AI32">
-        <v>0.7091022086241514</v>
+        <v>0.4527207850133809</v>
       </c>
       <c r="AJ32">
-        <v>0.7626138219257701</v>
+        <v>0.9355986683503617</v>
       </c>
       <c r="AK32">
-        <v>0.6936360890141979</v>
+        <v>0.3991185112634672</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>6.88</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>6.795</v>
+      </c>
+      <c r="AN32">
+        <v>2360.46511627907</v>
+      </c>
+      <c r="AO32">
+        <v>-0.05348837209302326</v>
+      </c>
+      <c r="AP32">
+        <v>1895.348837209302</v>
+      </c>
+      <c r="AQ32">
+        <v>-0.05415746872700515</v>
       </c>
     </row>
     <row r="33">
@@ -4361,7 +4346,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AVIC Joy Holdings (HK) Limited (SEHK:260)</t>
+          <t>Far East Horizon Limited (SEHK:3360)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4369,95 +4354,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D33">
+        <v>0.165</v>
+      </c>
+      <c r="E33">
+        <v>0.142</v>
+      </c>
       <c r="G33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>-6.21</v>
+        <v>913.1</v>
       </c>
       <c r="L33">
-        <v>0.7582417582417583</v>
+        <v>0.184841798416972</v>
       </c>
       <c r="M33">
-        <v>-0</v>
+        <v>1082.8</v>
       </c>
       <c r="N33">
-        <v>-0</v>
+        <v>0.3207250970054205</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>1.185850399737159</v>
       </c>
       <c r="P33">
-        <v>-0</v>
+        <v>278.2</v>
       </c>
       <c r="Q33">
-        <v>-0</v>
+        <v>0.0824027724297266</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>0.304676377176651</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>804.5999999999999</v>
+      </c>
+      <c r="T33">
+        <v>0.7430735131141485</v>
       </c>
       <c r="U33">
-        <v>4</v>
+        <v>2052.8</v>
       </c>
       <c r="V33">
-        <v>0.25</v>
+        <v>0.6080388614081337</v>
       </c>
       <c r="W33">
-        <v>0.09687987519500781</v>
+        <v>0.1294497923075833</v>
       </c>
       <c r="X33">
-        <v>0.08759105712319247</v>
+        <v>0.1563947875416113</v>
       </c>
       <c r="Y33">
-        <v>0.009288818071815336</v>
+        <v>-0.02694499523402807</v>
       </c>
       <c r="Z33">
-        <v>-0.1077631578947368</v>
+        <v>0.1204824272578718</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.03399627483026931</v>
+        <v>0.06483917756479511</v>
       </c>
       <c r="AC33">
-        <v>-0.03399627483026931</v>
+        <v>-0.06483917756479511</v>
       </c>
       <c r="AD33">
-        <v>135</v>
+        <v>39307.6</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>135</v>
+        <v>39307.6</v>
       </c>
       <c r="AG33">
-        <v>131</v>
+        <v>37254.8</v>
       </c>
       <c r="AH33">
-        <v>0.8940397350993378</v>
+        <v>0.9209042327633266</v>
       </c>
       <c r="AI33">
-        <v>2.076923076923077</v>
+        <v>0.841864937857536</v>
       </c>
       <c r="AJ33">
-        <v>0.891156462585034</v>
+        <v>0.9169080675052731</v>
       </c>
       <c r="AK33">
-        <v>2.147540983606557</v>
+        <v>0.8345927152243701</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -4474,7 +4468,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Far East Horizon Limited (SEHK:3360)</t>
+          <t>Kingkey Financial International (Holdings) Limited (SEHK:1468)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4483,109 +4477,118 @@
         </is>
       </c>
       <c r="D34">
-        <v>0.172</v>
-      </c>
-      <c r="E34">
-        <v>0.149</v>
+        <v>-0.00044</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>-0.08235294117647059</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>-0.08235294117647059</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>-0.128921568627451</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>-0.128921568627451</v>
       </c>
       <c r="K34">
-        <v>845.1</v>
+        <v>-7.29</v>
       </c>
       <c r="L34">
-        <v>0.188251804330393</v>
+        <v>-0.3573529411764706</v>
       </c>
       <c r="M34">
-        <v>1235.5</v>
+        <v>0.59</v>
       </c>
       <c r="N34">
-        <v>0.3227196740152544</v>
+        <v>0.0007436349886564154</v>
       </c>
       <c r="O34">
-        <v>1.461957164832564</v>
+        <v>-0.08093278463648834</v>
       </c>
       <c r="P34">
-        <v>461.2</v>
+        <v>-0</v>
       </c>
       <c r="Q34">
-        <v>0.1204680806603281</v>
+        <v>-0</v>
       </c>
       <c r="R34">
-        <v>0.5457342326351911</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>774.3</v>
+        <v>0.59</v>
       </c>
       <c r="T34">
-        <v>0.6267098340752731</v>
+        <v>1</v>
       </c>
       <c r="U34">
-        <v>2072</v>
+        <v>17.8</v>
       </c>
       <c r="V34">
-        <v>0.541218263504336</v>
+        <v>0.0224350894882783</v>
       </c>
       <c r="W34">
-        <v>0.1365354788677782</v>
+        <v>-0.06597285067873303</v>
       </c>
       <c r="X34">
-        <v>0.0955145695311479</v>
+        <v>0.0501648727239653</v>
       </c>
       <c r="Y34">
-        <v>0.0410209093366303</v>
+        <v>-0.1161377234026983</v>
       </c>
       <c r="Z34">
-        <v>0.1418626183847532</v>
+        <v>0.184115523465704</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>-0.02373646209386282</v>
       </c>
       <c r="AB34">
-        <v>0.03761600498985903</v>
+        <v>0.05037502783538275</v>
       </c>
       <c r="AC34">
-        <v>-0.03761600498985903</v>
+        <v>-0.07411148992924557</v>
       </c>
       <c r="AD34">
-        <v>36334</v>
+        <v>34.4</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>36334</v>
+        <v>34.4</v>
       </c>
       <c r="AG34">
-        <v>34262</v>
+        <v>16.6</v>
       </c>
       <c r="AH34">
-        <v>0.904677011333984</v>
+        <v>0.04155593138439236</v>
       </c>
       <c r="AI34">
-        <v>0.8290436814340215</v>
+        <v>0.2273628552544613</v>
       </c>
       <c r="AJ34">
-        <v>0.8994917354504022</v>
+        <v>0.02049382716049383</v>
       </c>
       <c r="AK34">
-        <v>0.8205602283831165</v>
+        <v>0.1243445692883895</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM34">
-        <v>0</v>
+        <v>1.281</v>
+      </c>
+      <c r="AN34">
+        <v>-18.01047120418848</v>
+      </c>
+      <c r="AO34">
+        <v>-1.502857142857143</v>
+      </c>
+      <c r="AP34">
+        <v>-8.69109947643979</v>
+      </c>
+      <c r="AQ34">
+        <v>-2.053083528493364</v>
       </c>
     </row>
     <row r="35">
@@ -4596,7 +4599,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AGM Group Holdings Inc. (NasdaqCM:AGMH)</t>
+          <t>Capital Industrial Financial Services Group Limited (SEHK:730)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4604,23 +4607,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D35">
+        <v>0.715</v>
+      </c>
       <c r="G35">
-        <v>-0.1742056074766355</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>-0.1833644859813084</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>-0.06064941834047104</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>-0.06064941834047104</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>-0.398</v>
+        <v>3.21</v>
       </c>
       <c r="L35">
-        <v>-0.07439252336448599</v>
+        <v>0.02820738137082601</v>
       </c>
       <c r="M35">
         <v>-0</v>
@@ -4629,7 +4635,7 @@
         <v>-0</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P35">
         <v>-0</v>
@@ -4638,73 +4644,67 @@
         <v>-0</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="U35">
-        <v>1.4</v>
+        <v>58.5</v>
       </c>
       <c r="V35">
-        <v>0.02405498281786941</v>
+        <v>0.8810240963855421</v>
       </c>
       <c r="W35">
-        <v>-0.03553571428571429</v>
+        <v>0.01712913553895411</v>
       </c>
       <c r="X35">
-        <v>0.02463743765056282</v>
+        <v>0.055367486657525</v>
       </c>
       <c r="Y35">
-        <v>-0.06017315193627711</v>
+        <v>-0.03823835111857089</v>
       </c>
       <c r="Z35">
-        <v>2.142251986181268</v>
+        <v>0.6070304582066464</v>
       </c>
       <c r="AA35">
-        <v>-0.1299263369006127</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.02500085995866134</v>
+        <v>0.0856330977327877</v>
       </c>
       <c r="AC35">
-        <v>-0.1549271968592741</v>
+        <v>-0.0856330977327877</v>
       </c>
       <c r="AD35">
-        <v>4.06</v>
+        <v>40.6</v>
       </c>
       <c r="AE35">
-        <v>0.01737194060760043</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>4.0773719406076</v>
+        <v>40.6</v>
       </c>
       <c r="AG35">
-        <v>2.6773719406076</v>
+        <v>-17.9</v>
       </c>
       <c r="AH35">
-        <v>0.0654711625355047</v>
+        <v>0.3794392523364486</v>
       </c>
       <c r="AI35">
-        <v>0.5526862375156034</v>
+        <v>0.1483918128654971</v>
       </c>
       <c r="AJ35">
-        <v>0.04397975561789466</v>
+        <v>-0.3690721649484535</v>
       </c>
       <c r="AK35">
-        <v>0.4479179089423445</v>
+        <v>-0.08321710832171082</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
         <v>0</v>
-      </c>
-      <c r="AN35">
-        <v>-13.35526315789474</v>
-      </c>
-      <c r="AP35">
-        <v>-8.80714454147237</v>
       </c>
     </row>
     <row r="36">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hong Kong Exchanges and Clearing Limited (SEHK:388)</t>
+          <t>China Ever Grand Financial Leasing Group Co., Ltd. (SEHK:379)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4724,124 +4724,115 @@
         </is>
       </c>
       <c r="D36">
-        <v>0.135</v>
-      </c>
-      <c r="E36">
-        <v>0.161</v>
-      </c>
-      <c r="F36">
-        <v>0.138</v>
+        <v>-0.09789999999999999</v>
       </c>
       <c r="G36">
-        <v>0.6617961774038816</v>
+        <v>-0.5633540372670807</v>
       </c>
       <c r="H36">
-        <v>0.6617961774038816</v>
+        <v>-0.5633540372670807</v>
       </c>
       <c r="I36">
-        <v>0.7221607261456719</v>
+        <v>-0.4770186335403726</v>
       </c>
       <c r="J36">
-        <v>0.6106371709687455</v>
+        <v>-0.4770186335403726</v>
       </c>
       <c r="K36">
-        <v>1642.4</v>
+        <v>-6.97</v>
       </c>
       <c r="L36">
-        <v>0.606006936757435</v>
+        <v>-0.432919254658385</v>
       </c>
       <c r="M36">
-        <v>1492.936</v>
+        <v>-0</v>
       </c>
       <c r="N36">
-        <v>0.02020533725276837</v>
+        <v>-0</v>
       </c>
       <c r="O36">
-        <v>0.9089965903555771</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>1492.936</v>
+        <v>-0</v>
       </c>
       <c r="Q36">
-        <v>0.02020533725276837</v>
+        <v>-0</v>
       </c>
       <c r="R36">
-        <v>0.9089965903555771</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
       </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
       <c r="U36">
-        <v>22666.8</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>0.3067715819305383</v>
+        <v>0.1220338983050847</v>
       </c>
       <c r="W36">
-        <v>0.2774418054664009</v>
+        <v>-0.1011611030478955</v>
       </c>
       <c r="X36">
-        <v>0.02414366399578909</v>
+        <v>0.06917057643095924</v>
       </c>
       <c r="Y36">
-        <v>0.2532981414706118</v>
+        <v>-0.1703316794788547</v>
       </c>
       <c r="Z36">
-        <v>-0.280370351212952</v>
+        <v>0.1357504215851602</v>
       </c>
       <c r="AA36">
-        <v>-0.1712045580881905</v>
+        <v>-0.06475548060708262</v>
       </c>
       <c r="AB36">
-        <v>0.02414209779281927</v>
+        <v>0.05969466550670617</v>
       </c>
       <c r="AC36">
-        <v>-0.1953466558810098</v>
+        <v>-0.1244501461137888</v>
       </c>
       <c r="AD36">
-        <v>327.2</v>
+        <v>50</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>327.2</v>
+        <v>50</v>
       </c>
       <c r="AG36">
-        <v>-22339.6</v>
+        <v>47.12</v>
       </c>
       <c r="AH36">
-        <v>0.004408788472473368</v>
+        <v>0.6793478260869565</v>
       </c>
       <c r="AI36">
-        <v>0.05092686267490545</v>
+        <v>0.4668534080298786</v>
       </c>
       <c r="AJ36">
-        <v>-0.4333696744431468</v>
+        <v>0.666289592760181</v>
       </c>
       <c r="AK36">
-        <v>1.375430214445354</v>
+        <v>0.4521205142966801</v>
       </c>
       <c r="AL36">
-        <v>13.5</v>
+        <v>0.005</v>
       </c>
       <c r="AM36">
-        <v>13.5</v>
+        <v>-0.333</v>
       </c>
       <c r="AN36">
-        <v>0.1630293971101146</v>
+        <v>-6.544502617801047</v>
       </c>
       <c r="AO36">
-        <v>144.9777777777778</v>
+        <v>-1536</v>
       </c>
       <c r="AP36">
-        <v>-11.13084205281515</v>
+        <v>-6.167539267015707</v>
       </c>
       <c r="AQ36">
-        <v>144.9777777777778</v>
+        <v>23.06306306306306</v>
       </c>
     </row>
     <row r="37">
@@ -4852,7 +4843,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>China Ever Grand Financial Leasing Group Co., Ltd. (SEHK:379)</t>
+          <t>China Smartpay Group Holdings Limited (SEHK:8325)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4861,25 +4852,25 @@
         </is>
       </c>
       <c r="D37">
-        <v>0.137</v>
+        <v>-0.102</v>
       </c>
       <c r="G37">
-        <v>-2.598360655737705</v>
+        <v>-0.1889150943396226</v>
       </c>
       <c r="H37">
-        <v>-2.598360655737705</v>
+        <v>-0.1889150943396226</v>
       </c>
       <c r="I37">
-        <v>-2.69672131147541</v>
+        <v>-0.1011218111799636</v>
       </c>
       <c r="J37">
-        <v>-2.69672131147541</v>
+        <v>-0.1011218111799636</v>
       </c>
       <c r="K37">
-        <v>-28.2</v>
+        <v>-3.36</v>
       </c>
       <c r="L37">
-        <v>-2.311475409836066</v>
+        <v>-0.07924528301886792</v>
       </c>
       <c r="M37">
         <v>-0</v>
@@ -4903,73 +4894,73 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>4.71</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>0.1385294117647059</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="W37">
-        <v>-0.3068552774755168</v>
+        <v>-0.16</v>
       </c>
       <c r="X37">
-        <v>0.03687840614663872</v>
+        <v>0.06524962907330287</v>
       </c>
       <c r="Y37">
-        <v>-0.3437336836221556</v>
+        <v>-0.2252496290733029</v>
       </c>
       <c r="Z37">
-        <v>0.07529934575978274</v>
+        <v>0.7530705746212204</v>
       </c>
       <c r="AA37">
-        <v>-0.2030613504505616</v>
+        <v>-0.07615186045203372</v>
       </c>
       <c r="AB37">
-        <v>0.03106806930737331</v>
+        <v>0.05695539872026534</v>
       </c>
       <c r="AC37">
-        <v>-0.2341294197579349</v>
+        <v>-0.1331072591722991</v>
       </c>
       <c r="AD37">
-        <v>57.7</v>
+        <v>26.2</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>0.002823970152276329</v>
       </c>
       <c r="AF37">
-        <v>57.7</v>
+        <v>26.20282397015228</v>
       </c>
       <c r="AG37">
-        <v>52.99</v>
+        <v>24.20282397015228</v>
       </c>
       <c r="AH37">
-        <v>0.6292257360959651</v>
+        <v>0.6283225325197707</v>
       </c>
       <c r="AI37">
-        <v>0.4568487727632621</v>
+        <v>0.6150489927266346</v>
       </c>
       <c r="AJ37">
-        <v>0.6091504770663294</v>
+        <v>0.6095995586698677</v>
       </c>
       <c r="AK37">
-        <v>0.4358088658606794</v>
+        <v>0.5960872078243653</v>
       </c>
       <c r="AL37">
-        <v>0.058</v>
+        <v>3.07</v>
       </c>
       <c r="AM37">
-        <v>-0.75</v>
+        <v>1.98</v>
       </c>
       <c r="AN37">
-        <v>-1.759146341463415</v>
+        <v>-7.203739345614517</v>
       </c>
       <c r="AO37">
-        <v>-567.2413793103448</v>
+        <v>-1.397394136807818</v>
       </c>
       <c r="AP37">
-        <v>-1.615548780487805</v>
+        <v>-6.654612034685806</v>
       </c>
       <c r="AQ37">
-        <v>43.86666666666667</v>
+        <v>-2.166666666666667</v>
       </c>
     </row>
     <row r="38">
@@ -4980,7 +4971,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Greater China Financial Holdings Limited (SEHK:431)</t>
+          <t>Finet Group Limited (SEHK:8317)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4989,25 +4980,25 @@
         </is>
       </c>
       <c r="D38">
-        <v>0.379</v>
+        <v>0.202</v>
       </c>
       <c r="G38">
-        <v>-0.3266787658802178</v>
+        <v>-1.269387755102041</v>
       </c>
       <c r="H38">
-        <v>-0.3266787658802178</v>
+        <v>-1.269387755102041</v>
       </c>
       <c r="I38">
-        <v>-0.1696914700544465</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="J38">
-        <v>-0.1696914700544465</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="K38">
-        <v>-33.5</v>
+        <v>0.198</v>
       </c>
       <c r="L38">
-        <v>-0.6079854809437386</v>
+        <v>0.08081632653061224</v>
       </c>
       <c r="M38">
         <v>-0</v>
@@ -5016,7 +5007,7 @@
         <v>-0</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P38">
         <v>-0</v>
@@ -5025,79 +5016,79 @@
         <v>-0</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
       <c r="U38">
-        <v>7.36</v>
+        <v>1.37</v>
       </c>
       <c r="V38">
-        <v>0.03618485742379548</v>
+        <v>0.04335443037974684</v>
       </c>
       <c r="W38">
-        <v>-0.9544159544159544</v>
+        <v>0.04016227180527384</v>
       </c>
       <c r="X38">
-        <v>0.02592652548887445</v>
+        <v>0.0503126477332142</v>
       </c>
       <c r="Y38">
-        <v>-0.9803424799048288</v>
+        <v>-0.01015037592794036</v>
       </c>
       <c r="Z38">
-        <v>1.481979558902636</v>
+        <v>0.2428146679881071</v>
       </c>
       <c r="AA38">
-        <v>-0.2514792899408285</v>
+        <v>-0.2081268582755203</v>
       </c>
       <c r="AB38">
-        <v>0.02551075890983851</v>
+        <v>0.05041015099176915</v>
       </c>
       <c r="AC38">
-        <v>-0.276990048850667</v>
+        <v>-0.2585370092672895</v>
       </c>
       <c r="AD38">
-        <v>49.1</v>
+        <v>1.88</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>49.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG38">
-        <v>41.74</v>
+        <v>0.5099999999999998</v>
       </c>
       <c r="AH38">
-        <v>0.1944554455445545</v>
+        <v>0.05615292712066905</v>
       </c>
       <c r="AI38">
-        <v>0.4387846291331546</v>
+        <v>0.29375</v>
       </c>
       <c r="AJ38">
-        <v>0.1702700497674798</v>
+        <v>0.01588290252257863</v>
       </c>
       <c r="AK38">
-        <v>0.3992730055481156</v>
+        <v>0.1013916500994036</v>
       </c>
       <c r="AL38">
-        <v>3.22</v>
+        <v>0.08</v>
       </c>
       <c r="AM38">
-        <v>-0.8500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AN38">
-        <v>-6.129837702871411</v>
+        <v>-0.9353233830845772</v>
       </c>
       <c r="AO38">
-        <v>-2.903726708074534</v>
+        <v>-26.25</v>
       </c>
       <c r="AP38">
-        <v>-5.210986267166043</v>
+        <v>-0.253731343283582</v>
       </c>
       <c r="AQ38">
-        <v>11</v>
+        <v>-26.25</v>
       </c>
     </row>
     <row r="39">
@@ -5108,7 +5099,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Joyas International Holdings Limited (Catalist:E9L)</t>
+          <t>China Success Finance Group Holdings Limited (SEHK:3623)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5117,25 +5108,25 @@
         </is>
       </c>
       <c r="D39">
-        <v>-0.464</v>
+        <v>-0.0178</v>
       </c>
       <c r="G39">
-        <v>-1.084745762711864</v>
+        <v>-0.5590909090909092</v>
       </c>
       <c r="H39">
-        <v>-1.084745762711864</v>
+        <v>-0.5776859504132231</v>
       </c>
       <c r="I39">
-        <v>-0.7259887005649718</v>
+        <v>-1.975206611570248</v>
       </c>
       <c r="J39">
-        <v>-0.7259887005649718</v>
+        <v>-1.975206611570248</v>
       </c>
       <c r="K39">
-        <v>-0.246</v>
+        <v>-21.2</v>
       </c>
       <c r="L39">
-        <v>-0.6949152542372882</v>
+        <v>-1.752066115702479</v>
       </c>
       <c r="M39">
         <v>-0</v>
@@ -5159,73 +5150,73 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>1.54</v>
+        <v>5.13</v>
       </c>
       <c r="V39">
-        <v>0.2358346094946401</v>
+        <v>0.09063604240282686</v>
       </c>
       <c r="W39">
-        <v>-0.2256880733944954</v>
+        <v>-0.2742561448900388</v>
       </c>
       <c r="X39">
-        <v>0.02886878985872588</v>
+        <v>0.05462192071176206</v>
       </c>
       <c r="Y39">
-        <v>-0.2545568632532213</v>
+        <v>-0.3288780656018009</v>
       </c>
       <c r="Z39">
-        <v>0.3778014941302028</v>
+        <v>0.1235198040016333</v>
       </c>
       <c r="AA39">
-        <v>-0.2742796157950907</v>
+        <v>-0.2439771335238873</v>
       </c>
       <c r="AB39">
-        <v>0.0293800125104804</v>
+        <v>0.05482981268821586</v>
       </c>
       <c r="AC39">
-        <v>-0.3036596283055711</v>
+        <v>-0.2988069462121032</v>
       </c>
       <c r="AD39">
-        <v>4.13</v>
+        <v>30</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>4.13</v>
+        <v>30</v>
       </c>
       <c r="AG39">
-        <v>2.59</v>
+        <v>24.87</v>
       </c>
       <c r="AH39">
-        <v>0.3874296435272045</v>
+        <v>0.3464203233256351</v>
       </c>
       <c r="AI39">
-        <v>0.7495462794918331</v>
+        <v>0.3640776699029126</v>
       </c>
       <c r="AJ39">
-        <v>0.2839912280701754</v>
+        <v>0.3052657419909169</v>
       </c>
       <c r="AK39">
-        <v>0.6523929471032746</v>
+        <v>0.3218584185324188</v>
       </c>
       <c r="AL39">
-        <v>0.028</v>
+        <v>0.997</v>
       </c>
       <c r="AM39">
-        <v>0.028</v>
+        <v>0.997</v>
       </c>
       <c r="AN39">
-        <v>-16.07003891050584</v>
+        <v>-1.310043668122271</v>
       </c>
       <c r="AO39">
-        <v>-9.178571428571429</v>
+        <v>-23.97191574724172</v>
       </c>
       <c r="AP39">
-        <v>-10.07782101167315</v>
+        <v>-1.086026200873363</v>
       </c>
       <c r="AQ39">
-        <v>-9.178571428571429</v>
+        <v>-23.97191574724172</v>
       </c>
     </row>
     <row r="40">
@@ -5236,7 +5227,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Finet Group Limited (SEHK:8317)</t>
+          <t>Greater China Financial Holdings Limited (SEHK:431)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5245,25 +5236,25 @@
         </is>
       </c>
       <c r="D40">
-        <v>-0.00168</v>
+        <v>0.162</v>
       </c>
       <c r="G40">
-        <v>-1.18957345971564</v>
+        <v>-0.5</v>
       </c>
       <c r="H40">
-        <v>-1.18957345971564</v>
+        <v>-0.5</v>
       </c>
       <c r="I40">
-        <v>-1.535545023696683</v>
+        <v>-0.5822368421052632</v>
       </c>
       <c r="J40">
-        <v>-1.535545023696683</v>
+        <v>-0.5822368421052632</v>
       </c>
       <c r="K40">
-        <v>-2.66</v>
+        <v>-23.4</v>
       </c>
       <c r="L40">
-        <v>-1.260663507109005</v>
+        <v>-0.7697368421052632</v>
       </c>
       <c r="M40">
         <v>-0</v>
@@ -5287,73 +5278,73 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>1.07</v>
+        <v>5.18</v>
       </c>
       <c r="V40">
-        <v>0.04476987447698745</v>
+        <v>0.03936170212765958</v>
       </c>
       <c r="W40">
-        <v>-0.35</v>
+        <v>-0.6964285714285714</v>
       </c>
       <c r="X40">
-        <v>0.02607153004588194</v>
+        <v>0.05384580207513867</v>
       </c>
       <c r="Y40">
-        <v>-0.376071530045882</v>
+        <v>-0.7502743735037101</v>
       </c>
       <c r="Z40">
-        <v>0.1904332129963899</v>
+        <v>0.9145607701564379</v>
       </c>
       <c r="AA40">
-        <v>-0.2924187725631769</v>
+        <v>-0.5324909747292418</v>
       </c>
       <c r="AB40">
-        <v>0.02639673285886529</v>
+        <v>0.05131131617426461</v>
       </c>
       <c r="AC40">
-        <v>-0.3188155054220422</v>
+        <v>-0.5838022909035064</v>
       </c>
       <c r="AD40">
-        <v>6.23</v>
+        <v>58.6</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>6.23</v>
+        <v>58.6</v>
       </c>
       <c r="AG40">
-        <v>5.16</v>
+        <v>53.42</v>
       </c>
       <c r="AH40">
-        <v>0.2067706604712911</v>
+        <v>0.3080967402733965</v>
       </c>
       <c r="AI40">
-        <v>0.5973154362416108</v>
+        <v>0.6362649294245386</v>
       </c>
       <c r="AJ40">
-        <v>0.1775636613902271</v>
+        <v>0.2887255431845206</v>
       </c>
       <c r="AK40">
-        <v>0.5512820512820513</v>
+        <v>0.6145881270133456</v>
       </c>
       <c r="AL40">
-        <v>0.096</v>
+        <v>4.16</v>
       </c>
       <c r="AM40">
-        <v>0.093</v>
+        <v>-0.05999999999999961</v>
       </c>
       <c r="AN40">
-        <v>-2.083612040133779</v>
+        <v>-3.573170731707318</v>
       </c>
       <c r="AO40">
-        <v>-33.75</v>
+        <v>-4.254807692307692</v>
       </c>
       <c r="AP40">
-        <v>-1.725752508361204</v>
+        <v>-3.257317073170732</v>
       </c>
       <c r="AQ40">
-        <v>-34.83870967741936</v>
+        <v>295.0000000000019</v>
       </c>
     </row>
     <row r="41">
@@ -5364,7 +5355,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>China Smartpay Group Holdings Limited (SEHK:8325)</t>
+          <t>Metalpha Technology Holding Limited (NasdaqCM:MATH)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5373,25 +5364,25 @@
         </is>
       </c>
       <c r="D41">
-        <v>-0.349</v>
+        <v>-0.108</v>
       </c>
       <c r="G41">
-        <v>-1.104097452934662</v>
+        <v>-6.157635467980296</v>
       </c>
       <c r="H41">
-        <v>-1.104097452934662</v>
+        <v>-6.157635467980296</v>
       </c>
       <c r="I41">
-        <v>-1.495016611295681</v>
+        <v>-6.124579860655265</v>
       </c>
       <c r="J41">
-        <v>-1.495016611295681</v>
+        <v>-6.124579860655265</v>
       </c>
       <c r="K41">
-        <v>-13.7</v>
+        <v>-14.4</v>
       </c>
       <c r="L41">
-        <v>-1.517165005537099</v>
+        <v>-7.093596059113302</v>
       </c>
       <c r="M41">
         <v>-0</v>
@@ -5415,73 +5406,67 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>0.1564748201438849</v>
-      </c>
-      <c r="W41">
-        <v>-0.8303030303030302</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>0.03006430646393439</v>
-      </c>
-      <c r="Y41">
-        <v>-0.8603673367669646</v>
+        <v>0.04994663712715092</v>
       </c>
       <c r="Z41">
-        <v>0.1993377483443708</v>
+        <v>7.532870431999445</v>
       </c>
       <c r="AA41">
-        <v>-0.2980132450331126</v>
+        <v>-46.13566654074933</v>
       </c>
       <c r="AB41">
-        <v>0.03011908877740242</v>
+        <v>0.05022840827314789</v>
       </c>
       <c r="AC41">
-        <v>-0.328132333810515</v>
+        <v>-46.18589494902248</v>
       </c>
       <c r="AD41">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>0.2694855856509373</v>
       </c>
       <c r="AF41">
-        <v>44</v>
+        <v>0.2694855856509373</v>
       </c>
       <c r="AG41">
-        <v>35.3</v>
+        <v>0.2694855856509373</v>
       </c>
       <c r="AH41">
-        <v>0.4417670682730924</v>
+        <v>0.0191539046691073</v>
       </c>
       <c r="AI41">
-        <v>0.624113475177305</v>
+        <v>1</v>
       </c>
       <c r="AJ41">
-        <v>0.3883388338833883</v>
+        <v>0.0191539046691073</v>
       </c>
       <c r="AK41">
-        <v>0.5711974110032362</v>
+        <v>1</v>
       </c>
       <c r="AL41">
-        <v>3.99</v>
+        <v>1.97</v>
       </c>
       <c r="AM41">
-        <v>3.553</v>
+        <v>1.762</v>
       </c>
       <c r="AN41">
-        <v>-3.826086956521739</v>
+        <v>-0</v>
       </c>
       <c r="AO41">
-        <v>-3.383458646616541</v>
+        <v>-6.345177664974619</v>
       </c>
       <c r="AP41">
-        <v>-3.069565217391304</v>
+        <v>-0.02176957635115416</v>
       </c>
       <c r="AQ41">
-        <v>-3.799605966788629</v>
+        <v>-7.094211123723042</v>
       </c>
     </row>
     <row r="42">
@@ -5501,25 +5486,25 @@
         </is>
       </c>
       <c r="D42">
-        <v>0.185</v>
+        <v>0.0189</v>
       </c>
       <c r="G42">
-        <v>-0.7165841584158417</v>
+        <v>-1.336666666666667</v>
       </c>
       <c r="H42">
-        <v>-0.8094059405940595</v>
+        <v>-1.336666666666667</v>
       </c>
       <c r="I42">
-        <v>-1.066831683168317</v>
+        <v>-2.253333333333333</v>
       </c>
       <c r="J42">
-        <v>-1.066831683168317</v>
+        <v>-2.253333333333333</v>
       </c>
       <c r="K42">
-        <v>-45.6</v>
+        <v>-66.8</v>
       </c>
       <c r="L42">
-        <v>-1.128712871287129</v>
+        <v>-2.226666666666667</v>
       </c>
       <c r="M42">
         <v>-0</v>
@@ -5543,73 +5528,174 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>251.6</v>
+        <v>129.9</v>
       </c>
       <c r="V42">
-        <v>0.5150460593654043</v>
+        <v>0.7405929304446979</v>
       </c>
       <c r="W42">
-        <v>-2.4</v>
+        <v>-0.387695879280325</v>
       </c>
       <c r="X42">
-        <v>0.02497745222548779</v>
+        <v>0.05131851590306034</v>
       </c>
       <c r="Y42">
-        <v>-2.424977452225488</v>
-      </c>
-      <c r="Z42">
-        <v>0.7482867197629189</v>
-      </c>
-      <c r="AA42">
-        <v>-0.7982959807371734</v>
+        <v>-0.4390143951833853</v>
       </c>
       <c r="AB42">
-        <v>0.02525304614127308</v>
-      </c>
-      <c r="AC42">
-        <v>-0.8235490268784466</v>
+        <v>0.05325010480373187</v>
       </c>
       <c r="AD42">
-        <v>56.3</v>
+        <v>29.7</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>56.3</v>
+        <v>29.7</v>
       </c>
       <c r="AG42">
-        <v>-195.3</v>
+        <v>-100.2</v>
       </c>
       <c r="AH42">
-        <v>0.1033406754772394</v>
+        <v>0.1448074110190151</v>
       </c>
       <c r="AI42">
-        <v>0.24769027716674</v>
+        <v>0.2069686411149826</v>
       </c>
       <c r="AJ42">
-        <v>-0.6660982264665758</v>
+        <v>-1.332446808510638</v>
       </c>
       <c r="AK42">
-        <v>8.037037037037035</v>
+        <v>-7.367647058823533</v>
       </c>
       <c r="AL42">
-        <v>6.15</v>
+        <v>3.25</v>
       </c>
       <c r="AM42">
-        <v>4.69</v>
+        <v>2.942</v>
       </c>
       <c r="AN42">
-        <v>-1.383292383292383</v>
+        <v>-0.4541284403669724</v>
       </c>
       <c r="AO42">
-        <v>-7.008130081300813</v>
+        <v>-20.8</v>
       </c>
       <c r="AP42">
-        <v>4.798525798525798</v>
+        <v>1.532110091743119</v>
       </c>
       <c r="AQ42">
-        <v>-9.189765458422174</v>
+        <v>-22.97756628144119</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Temir Corp. (OTCPK:TMRR)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>-0.7565579827529731</v>
+      </c>
+      <c r="J43">
+        <v>-0.7565579827529731</v>
+      </c>
+      <c r="K43">
+        <v>-0.283</v>
+      </c>
+      <c r="L43">
+        <v>-0.9248366013071895</v>
+      </c>
+      <c r="M43">
+        <v>-0</v>
+      </c>
+      <c r="N43">
+        <v>-0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>-0</v>
+      </c>
+      <c r="Q43">
+        <v>-0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0.014</v>
+      </c>
+      <c r="V43">
+        <v>0.01494130202774813</v>
+      </c>
+      <c r="W43">
+        <v>0.7389033942558746</v>
+      </c>
+      <c r="X43">
+        <v>0.0537118820574379</v>
+      </c>
+      <c r="Y43">
+        <v>0.6851915121984367</v>
+      </c>
+      <c r="AB43">
+        <v>0.05416647550852007</v>
+      </c>
+      <c r="AD43">
+        <v>0.336</v>
+      </c>
+      <c r="AE43">
+        <v>0.06753371361204902</v>
+      </c>
+      <c r="AF43">
+        <v>0.403533713612049</v>
+      </c>
+      <c r="AG43">
+        <v>0.389533713612049</v>
+      </c>
+      <c r="AH43">
+        <v>0.3010246661568348</v>
+      </c>
+      <c r="AI43">
+        <v>-1.531633208728082</v>
+      </c>
+      <c r="AJ43">
+        <v>0.29364780526488</v>
+      </c>
+      <c r="AK43">
+        <v>-1.40389565407383</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
+      <c r="AN43">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AP43">
+        <v>5.410190466834015</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ43"/>
+  <dimension ref="A1:AQ62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0121</v>
+        <v>-0.0248</v>
       </c>
       <c r="E2">
-        <v>0.00163</v>
+        <v>-0.0176</v>
       </c>
       <c r="F2">
-        <v>0.12</v>
+        <v>0.053</v>
       </c>
       <c r="G2">
-        <v>0.242276691368887</v>
+        <v>0.084309550516722</v>
       </c>
       <c r="H2">
-        <v>0.2407482494618995</v>
+        <v>0.07955214678982876</v>
       </c>
       <c r="I2">
-        <v>0.1326584464573266</v>
+        <v>0.1276489238176885</v>
       </c>
       <c r="J2">
-        <v>0.1173742045708487</v>
+        <v>0.114385406014776</v>
       </c>
       <c r="K2">
-        <v>1703.829</v>
+        <v>1393.863</v>
       </c>
       <c r="L2">
-        <v>0.1672362988659475</v>
+        <v>0.110510274660088</v>
       </c>
       <c r="M2">
-        <v>2754.767</v>
+        <v>2447.7905</v>
       </c>
       <c r="N2">
-        <v>0.03829479524710135</v>
+        <v>0.04090535065386483</v>
       </c>
       <c r="O2">
-        <v>1.616809550723693</v>
+        <v>1.75611986256899</v>
       </c>
       <c r="P2">
-        <v>1936.358</v>
+        <v>1993.2245</v>
       </c>
       <c r="Q2">
-        <v>0.02691786025282235</v>
+        <v>0.03330903813229702</v>
       </c>
       <c r="R2">
-        <v>1.136474376243156</v>
+        <v>1.430000294146555</v>
       </c>
       <c r="S2">
-        <v>818.4089999999999</v>
+        <v>454.5660000000001</v>
       </c>
       <c r="T2">
-        <v>0.2970882836915064</v>
+        <v>0.185704618103551</v>
       </c>
       <c r="U2">
-        <v>31333.244</v>
+        <v>27135.582</v>
       </c>
       <c r="V2">
-        <v>0.4355722873867252</v>
+        <v>0.4534662982419053</v>
       </c>
       <c r="W2">
-        <v>0.01712913553895411</v>
+        <v>-0.01519518538974868</v>
       </c>
       <c r="X2">
-        <v>0.0551134216040054</v>
+        <v>0.05728817980347345</v>
       </c>
       <c r="Y2">
-        <v>-0.03798428606505129</v>
+        <v>-0.07248336519322213</v>
       </c>
       <c r="Z2">
-        <v>0.1306666163132563</v>
+        <v>0.1483777891525199</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05369565510106083</v>
+        <v>0.0537256021042803</v>
       </c>
       <c r="AC2">
-        <v>-0.05515345331111729</v>
+        <v>-0.05371520668557572</v>
       </c>
       <c r="AD2">
-        <v>63662.881</v>
+        <v>58874.185</v>
       </c>
       <c r="AE2">
-        <v>1.142253752244955</v>
+        <v>0.4934902868076165</v>
       </c>
       <c r="AF2">
-        <v>63664.02325375225</v>
+        <v>58874.6784902868</v>
       </c>
       <c r="AG2">
-        <v>32330.77925375225</v>
+        <v>31739.0964902868</v>
       </c>
       <c r="AH2">
-        <v>0.4694992842883045</v>
+        <v>0.4959328169230393</v>
       </c>
       <c r="AI2">
-        <v>0.6034420134617593</v>
+        <v>0.5840585788702293</v>
       </c>
       <c r="AJ2">
-        <v>0.3100780452816327</v>
+        <v>0.346574452092295</v>
       </c>
       <c r="AK2">
-        <v>0.4359114174804483</v>
+        <v>0.4308448562371938</v>
       </c>
       <c r="AL2">
-        <v>237.811</v>
+        <v>545.636</v>
       </c>
       <c r="AM2">
-        <v>228.575</v>
+        <v>508.275</v>
       </c>
       <c r="AN2">
-        <v>44.41315409815937</v>
+        <v>30.59802756277295</v>
       </c>
       <c r="AO2">
-        <v>5.679855010912027</v>
+        <v>2.950274542002361</v>
       </c>
       <c r="AP2">
-        <v>22.55493088838491</v>
+        <v>16.4954087980548</v>
       </c>
       <c r="AQ2">
-        <v>5.909360166247402</v>
+        <v>3.16713590084108</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07829999999999999</v>
+        <v>0.0568</v>
       </c>
       <c r="E3">
-        <v>0.07629999999999999</v>
+        <v>0.0551</v>
       </c>
       <c r="F3">
-        <v>0.14</v>
+        <v>0.114</v>
       </c>
       <c r="G3">
-        <v>0.8688596684110999</v>
+        <v>0.5968089530795115</v>
       </c>
       <c r="H3">
-        <v>0.8688596684110999</v>
+        <v>0.5968089530795115</v>
       </c>
       <c r="I3">
-        <v>0.6508641540964862</v>
+        <v>0.6793829634390715</v>
       </c>
       <c r="J3">
-        <v>0.5581078264366741</v>
+        <v>0.605885275882721</v>
       </c>
       <c r="K3">
-        <v>1245</v>
+        <v>1563.6</v>
       </c>
       <c r="L3">
-        <v>0.5475174809798143</v>
+        <v>0.591175469772014</v>
       </c>
       <c r="M3">
-        <v>1230.066</v>
+        <v>1328.67</v>
       </c>
       <c r="N3">
-        <v>0.02247545647395454</v>
+        <v>0.03060527813033393</v>
       </c>
       <c r="O3">
-        <v>0.9880048192771085</v>
+        <v>0.8497505755947814</v>
       </c>
       <c r="P3">
-        <v>1230.066</v>
+        <v>1328.67</v>
       </c>
       <c r="Q3">
-        <v>0.02247545647395454</v>
+        <v>0.03060527813033393</v>
       </c>
       <c r="R3">
-        <v>0.9880048192771085</v>
+        <v>0.8497505755947814</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,64 +776,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>22344.5</v>
+        <v>17739</v>
       </c>
       <c r="V3">
-        <v>0.4082730822429667</v>
+        <v>0.4086093828821254</v>
       </c>
       <c r="W3">
-        <v>0.205408259226873</v>
+        <v>0.2611484116644954</v>
       </c>
       <c r="X3">
-        <v>0.04981542152606089</v>
+        <v>0.05198270329725804</v>
       </c>
       <c r="Y3">
-        <v>0.1555928377008121</v>
+        <v>0.2091657083672374</v>
       </c>
       <c r="AB3">
-        <v>0.04982697654309011</v>
+        <v>0.05192932132941967</v>
       </c>
       <c r="AD3">
-        <v>284.6</v>
+        <v>261.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>284.6</v>
+        <v>261.4</v>
       </c>
       <c r="AG3">
-        <v>-22059.9</v>
+        <v>-17477.6</v>
       </c>
       <c r="AH3">
-        <v>0.005173238036205396</v>
+        <v>0.00598518586360462</v>
       </c>
       <c r="AI3">
-        <v>0.04512661138154661</v>
+        <v>0.03983602310306466</v>
       </c>
       <c r="AJ3">
-        <v>-0.6752465610020386</v>
+        <v>-0.6738871431050104</v>
       </c>
       <c r="AK3">
-        <v>1.375494145082243</v>
+        <v>1.563697202315449</v>
       </c>
       <c r="AL3">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="AM3">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="AN3">
-        <v>0.1854675790159661</v>
+        <v>0.1408556956568596</v>
       </c>
       <c r="AO3">
-        <v>130.9734513274336</v>
+        <v>167.9345794392524</v>
       </c>
       <c r="AP3">
-        <v>-14.37595307917889</v>
+        <v>-9.417825196680676</v>
       </c>
       <c r="AQ3">
-        <v>130.9734513274336</v>
+        <v>167.9345794392524</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital Finance Holdings Limited (SEHK:8239)</t>
+          <t>HM International Holdings Limited (SEHK:8416)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,47 +853,53 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.09849999999999999</v>
+        <v>0.0636</v>
+      </c>
+      <c r="E4">
+        <v>-0.358</v>
       </c>
       <c r="G4">
-        <v>0.8015122873345936</v>
+        <v>0.04425531914893617</v>
       </c>
       <c r="H4">
-        <v>0.8015122873345936</v>
+        <v>0.04425531914893617</v>
       </c>
       <c r="I4">
-        <v>0.3478260869565217</v>
+        <v>0.01531914893617021</v>
       </c>
       <c r="J4">
-        <v>0.1739130434782609</v>
+        <v>0.01531914893617021</v>
       </c>
       <c r="K4">
-        <v>-0.612</v>
+        <v>0.138</v>
       </c>
       <c r="L4">
-        <v>-0.1156899810964083</v>
+        <v>0.005872340425531915</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.8</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.1646090534979424</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>5.797101449275362</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.8</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.1646090534979424</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>5.797101449275362</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
         <v>0</v>
       </c>
@@ -901,52 +907,52 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>0.1094305612606592</v>
+        <v>0.0554999783148904</v>
       </c>
       <c r="AB4">
-        <v>0.07061555859359278</v>
+        <v>0.0541799933695476</v>
       </c>
       <c r="AD4">
-        <v>24.3</v>
+        <v>1.59</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>24.3</v>
+        <v>1.59</v>
       </c>
       <c r="AG4">
-        <v>24.3</v>
+        <v>1.59</v>
       </c>
       <c r="AH4">
-        <v>0.8669282911166607</v>
+        <v>0.2465116279069768</v>
       </c>
       <c r="AI4">
-        <v>0.7126099706744868</v>
+        <v>0.1196388261851016</v>
       </c>
       <c r="AJ4">
-        <v>0.8669282911166607</v>
+        <v>0.2465116279069768</v>
       </c>
       <c r="AK4">
-        <v>0.7126099706744868</v>
+        <v>0.1196388261851016</v>
       </c>
       <c r="AL4">
-        <v>3.76</v>
+        <v>0.102</v>
       </c>
       <c r="AM4">
-        <v>3.566</v>
+        <v>0.093</v>
       </c>
       <c r="AN4">
-        <v>12.65625</v>
+        <v>3.063583815028902</v>
       </c>
       <c r="AO4">
-        <v>0.4893617021276596</v>
+        <v>3.529411764705882</v>
       </c>
       <c r="AP4">
-        <v>12.65625</v>
+        <v>3.063583815028902</v>
       </c>
       <c r="AQ4">
-        <v>0.5159842961301179</v>
+        <v>3.870967741935484</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AGM Group Holdings Inc. (NasdaqCM:AGMH)</t>
+          <t>Capital Finance Holdings Limited (SEHK:8239)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,28 +972,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.6509999999999999</v>
-      </c>
-      <c r="E5">
-        <v>0.313</v>
+        <v>-0.142</v>
       </c>
       <c r="G5">
-        <v>0.03331557922769641</v>
+        <v>0.1239005736137667</v>
       </c>
       <c r="H5">
-        <v>0.03322237017310253</v>
+        <v>0.1239005736137667</v>
       </c>
       <c r="I5">
-        <v>0.1693945242117651</v>
+        <v>0.372848948374761</v>
       </c>
       <c r="J5">
-        <v>0.1254326119758546</v>
+        <v>0.1864244741873805</v>
       </c>
       <c r="K5">
-        <v>18.6</v>
+        <v>-0.392</v>
       </c>
       <c r="L5">
-        <v>0.1238348868175766</v>
+        <v>-0.07495219885277246</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,7 +999,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1005,73 +1008,64 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>9.65</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.24125</v>
-      </c>
-      <c r="W5">
-        <v>6.019417475728156</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>0.0518328863203748</v>
-      </c>
-      <c r="Y5">
-        <v>5.967584589407782</v>
-      </c>
-      <c r="Z5">
-        <v>42.80772728895199</v>
-      </c>
-      <c r="AA5">
-        <v>5.369485046603319</v>
+        <v>0.09983390477141812</v>
       </c>
       <c r="AB5">
-        <v>0.05245649567281157</v>
-      </c>
-      <c r="AC5">
-        <v>5.317028550930508</v>
+        <v>0.0643885441239572</v>
       </c>
       <c r="AD5">
-        <v>8.970000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="AE5">
-        <v>0.04971231696442497</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>9.019712316964426</v>
+        <v>18.2</v>
       </c>
       <c r="AG5">
-        <v>-0.6302876830355739</v>
+        <v>18.2</v>
       </c>
       <c r="AH5">
-        <v>0.1840017391094101</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="AI5">
-        <v>0.2030565225772453</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AJ5">
-        <v>-0.01600945615149905</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="AK5">
-        <v>-0.01812749203357807</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>2.152</v>
       </c>
       <c r="AN5">
-        <v>0.3496667056484621</v>
+        <v>9.1</v>
+      </c>
+      <c r="AO5">
+        <v>0.8628318584070797</v>
       </c>
       <c r="AP5">
-        <v>-0.02456974556720749</v>
+        <v>9.1</v>
+      </c>
+      <c r="AQ5">
+        <v>0.9061338289962826</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TradeGo FinTech Limited (SEHK:8017)</t>
+          <t>A.Plus Group Holdings Limited (SEHK:1841)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,116 +1084,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.0454</v>
+      </c>
+      <c r="E6">
+        <v>-0.15</v>
+      </c>
       <c r="G6">
-        <v>0.4532786885245902</v>
+        <v>0.1377245508982036</v>
       </c>
       <c r="H6">
-        <v>0.3057377049180328</v>
+        <v>0.1377245508982036</v>
       </c>
       <c r="I6">
-        <v>0.3868852459016394</v>
+        <v>0.1239520958083832</v>
       </c>
       <c r="J6">
-        <v>0.3767283540044603</v>
+        <v>0.1097531057288408</v>
       </c>
       <c r="K6">
-        <v>4.19</v>
+        <v>2.37</v>
       </c>
       <c r="L6">
-        <v>0.3434426229508197</v>
+        <v>0.1419161676646707</v>
       </c>
       <c r="M6">
-        <v>4.42</v>
+        <v>1.28</v>
       </c>
       <c r="N6">
-        <v>0.05573770491803279</v>
+        <v>0.1207547169811321</v>
       </c>
       <c r="O6">
-        <v>1.054892601431981</v>
+        <v>0.540084388185654</v>
       </c>
       <c r="P6">
-        <v>2.42</v>
+        <v>1.28</v>
       </c>
       <c r="Q6">
-        <v>0.03051702395964691</v>
+        <v>0.1207547169811321</v>
       </c>
       <c r="R6">
-        <v>0.5775656324582338</v>
+        <v>0.540084388185654</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.4524886877828054</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>15.9</v>
+        <v>10.1</v>
       </c>
       <c r="V6">
-        <v>0.2005044136191677</v>
+        <v>0.9528301886792453</v>
       </c>
       <c r="W6">
-        <v>0.2635220125786163</v>
+        <v>0.176865671641791</v>
       </c>
       <c r="X6">
-        <v>0.04996528067209265</v>
+        <v>0.05301200501164949</v>
       </c>
       <c r="Y6">
-        <v>0.2135567319065237</v>
+        <v>0.1238536666301416</v>
       </c>
       <c r="Z6">
-        <v>1.71830985915493</v>
+        <v>6.774847870182554</v>
       </c>
       <c r="AA6">
-        <v>0.6473360449090727</v>
+        <v>0.7435605945929579</v>
       </c>
       <c r="AB6">
-        <v>0.05027541220945848</v>
+        <v>0.05254879613827568</v>
       </c>
       <c r="AC6">
-        <v>0.5970606326996142</v>
+        <v>0.6910117984546822</v>
       </c>
       <c r="AD6">
-        <v>1.71</v>
+        <v>1.06</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.71</v>
+        <v>1.06</v>
       </c>
       <c r="AG6">
-        <v>-14.19</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.02110850512282434</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AI6">
-        <v>0.09238249594813613</v>
+        <v>0.06768837803320563</v>
       </c>
       <c r="AJ6">
-        <v>-0.2179388726770081</v>
+        <v>-5.794871794871792</v>
       </c>
       <c r="AK6">
-        <v>-5.436781609195404</v>
+        <v>-1.625899280575539</v>
       </c>
       <c r="AL6">
-        <v>0.082</v>
+        <v>0.013</v>
       </c>
       <c r="AM6">
-        <v>-0.17</v>
+        <v>-0.222</v>
       </c>
       <c r="AN6">
-        <v>0.3475609756097561</v>
+        <v>0.3799283154121864</v>
       </c>
       <c r="AO6">
-        <v>57.56097560975609</v>
+        <v>159.2307692307692</v>
       </c>
       <c r="AP6">
-        <v>-2.884146341463415</v>
+        <v>-3.240143369175627</v>
       </c>
       <c r="AQ6">
-        <v>-27.76470588235294</v>
+        <v>-9.324324324324325</v>
       </c>
     </row>
     <row r="7">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dingyi Group Investment Limited (SEHK:508)</t>
+          <t>TradeGo FinTech Limited (SEHK:8017)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,34 +1219,34 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0522</v>
+        <v>0.118</v>
       </c>
       <c r="G7">
-        <v>0.03991130820399113</v>
+        <v>0.5048076923076923</v>
       </c>
       <c r="H7">
-        <v>0.03991130820399113</v>
+        <v>0.3067307692307692</v>
       </c>
       <c r="I7">
-        <v>0.1382113821138211</v>
+        <v>0.1451923076923077</v>
       </c>
       <c r="J7">
-        <v>0.06910569105691056</v>
+        <v>0.1265247252747253</v>
       </c>
       <c r="K7">
-        <v>-0.264</v>
+        <v>2.22</v>
       </c>
       <c r="L7">
-        <v>-0.001951219512195122</v>
+        <v>0.2134615384615385</v>
       </c>
       <c r="M7">
-        <v>0.002</v>
+        <v>1.66</v>
       </c>
       <c r="N7">
-        <v>4.329004329004329e-05</v>
+        <v>0.06887966804979252</v>
       </c>
       <c r="O7">
-        <v>-0.007575757575757576</v>
+        <v>0.7477477477477477</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1255,82 +1255,82 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>0.002</v>
+        <v>1.66</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
       <c r="U7">
-        <v>11.9</v>
+        <v>13.6</v>
       </c>
       <c r="V7">
-        <v>0.2575757575757576</v>
+        <v>0.5643153526970954</v>
       </c>
       <c r="W7">
-        <v>-0.001432447097124254</v>
+        <v>0.1345454545454546</v>
       </c>
       <c r="X7">
-        <v>0.08061200005620994</v>
+        <v>0.05250755417344277</v>
       </c>
       <c r="Y7">
-        <v>-0.0820444471533342</v>
+        <v>0.08203790037201178</v>
       </c>
       <c r="Z7">
-        <v>0.4297966963151208</v>
+        <v>4.502164502164502</v>
       </c>
       <c r="AA7">
-        <v>0.02970139771283355</v>
+        <v>0.5696351267779838</v>
       </c>
       <c r="AB7">
-        <v>0.06103480244919859</v>
+        <v>0.05270097744904998</v>
       </c>
       <c r="AC7">
-        <v>-0.03133340473636505</v>
+        <v>0.5169341493289338</v>
       </c>
       <c r="AD7">
-        <v>155.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>155.6</v>
+        <v>1.3</v>
       </c>
       <c r="AG7">
-        <v>143.7</v>
+        <v>-12.3</v>
       </c>
       <c r="AH7">
-        <v>0.7710604558969276</v>
+        <v>0.05118110236220472</v>
       </c>
       <c r="AI7">
-        <v>0.5060162601626016</v>
+        <v>0.07027027027027027</v>
       </c>
       <c r="AJ7">
-        <v>0.7567140600315956</v>
+        <v>-1.042372881355932</v>
       </c>
       <c r="AK7">
-        <v>0.4861299052774018</v>
+        <v>-2.510204081632653</v>
       </c>
       <c r="AL7">
-        <v>13.2</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AM7">
-        <v>13.145</v>
+        <v>-0.157</v>
       </c>
       <c r="AN7">
-        <v>8.104166666666666</v>
+        <v>0.8176100628930818</v>
       </c>
       <c r="AO7">
-        <v>1.416666666666667</v>
+        <v>20.97222222222222</v>
       </c>
       <c r="AP7">
-        <v>7.484375</v>
+        <v>-7.735849056603772</v>
       </c>
       <c r="AQ7">
-        <v>1.422594142259414</v>
+        <v>-9.617834394904458</v>
       </c>
     </row>
     <row r="8">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G-Resources Group Limited (SEHK:1051)</t>
+          <t>AGM Group Holdings Inc. (NasdaqCM:AGMH)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1350,118 +1350,109 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0919</v>
+        <v>0.723</v>
       </c>
       <c r="G8">
-        <v>2.221276595744681</v>
+        <v>0.09909365558912386</v>
       </c>
       <c r="H8">
-        <v>2.221276595744681</v>
+        <v>0.09909365558912386</v>
       </c>
       <c r="I8">
-        <v>0.405531914893617</v>
+        <v>0.1094529454874253</v>
       </c>
       <c r="J8">
-        <v>0.405531914893617</v>
+        <v>0.08012201571354782</v>
       </c>
       <c r="K8">
-        <v>-56.2</v>
+        <v>13</v>
       </c>
       <c r="L8">
-        <v>-2.391489361702128</v>
+        <v>0.07854984894259819</v>
       </c>
       <c r="M8">
-        <v>6.762</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.0538804780876494</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>-0.1203202846975089</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>6.762</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.0538804780876494</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>-0.1203202846975089</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>865.5</v>
+        <v>3.74</v>
       </c>
       <c r="V8">
-        <v>6.896414342629482</v>
+        <v>0.08519362186788156</v>
       </c>
       <c r="W8">
-        <v>-0.03446161393181261</v>
+        <v>0.3672316384180791</v>
       </c>
       <c r="X8">
-        <v>0.04977421969233153</v>
+        <v>0.0543686388507086</v>
       </c>
       <c r="Y8">
-        <v>-0.08423583362414414</v>
+        <v>0.3128629995673705</v>
       </c>
       <c r="Z8">
-        <v>0.0242294019152569</v>
+        <v>4.72213750149856</v>
       </c>
       <c r="AA8">
-        <v>0.009825795755421201</v>
+        <v>0.3783471750966011</v>
       </c>
       <c r="AB8">
-        <v>0.04977581366464987</v>
+        <v>0.0531884732870998</v>
       </c>
       <c r="AC8">
-        <v>-0.03995001790922867</v>
+        <v>0.3251587018095013</v>
       </c>
       <c r="AD8">
-        <v>0.08799999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>0.3276876091555856</v>
       </c>
       <c r="AF8">
-        <v>0.08799999999999999</v>
+        <v>9.827687609155586</v>
       </c>
       <c r="AG8">
-        <v>-865.412</v>
+        <v>6.087687609155585</v>
       </c>
       <c r="AH8">
-        <v>0.0007007038889065834</v>
+        <v>0.1829166310049956</v>
       </c>
       <c r="AI8">
-        <v>5.641430666817105e-05</v>
+        <v>0.1856814089768691</v>
       </c>
       <c r="AJ8">
-        <v>1.169614764999081</v>
+        <v>0.1217837411635057</v>
       </c>
       <c r="AK8">
-        <v>-1.246294578823367</v>
+        <v>0.1237644602756737</v>
       </c>
       <c r="AL8">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>0.008543689320388348</v>
-      </c>
-      <c r="AO8">
-        <v>1361.428571428571</v>
+        <v>0.5196936542669583</v>
       </c>
       <c r="AP8">
-        <v>-84.02058252427184</v>
-      </c>
-      <c r="AQ8">
-        <v>1361.428571428571</v>
+        <v>0.3330244862776578</v>
       </c>
     </row>
     <row r="9">
@@ -1472,7 +1463,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shandong Hi-Speed Holdings Group Limited (SEHK:412)</t>
+          <t>Sun Hing Printing Holdings Limited (SEHK:1975)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1480,41 +1471,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.146</v>
+      </c>
+      <c r="E9">
+        <v>0.5379999999999999</v>
+      </c>
       <c r="G9">
-        <v>-0.01207207207207207</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="H9">
-        <v>-0.01207207207207207</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="I9">
-        <v>0.1292792792792793</v>
+        <v>0.2008797653958944</v>
       </c>
       <c r="J9">
-        <v>0.1292792792792793</v>
+        <v>0.1498291182501709</v>
       </c>
       <c r="K9">
-        <v>3.36</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L9">
-        <v>0.01513513513513513</v>
+        <v>0.1450146627565982</v>
       </c>
       <c r="M9">
-        <v>38.3</v>
+        <v>5.51</v>
       </c>
       <c r="N9">
-        <v>0.008673400063408668</v>
+        <v>0.1493224932249322</v>
       </c>
       <c r="O9">
-        <v>11.39880952380952</v>
+        <v>0.557128412537917</v>
       </c>
       <c r="P9">
-        <v>38.3</v>
+        <v>5.51</v>
       </c>
       <c r="Q9">
-        <v>0.008673400063408668</v>
+        <v>0.1493224932249322</v>
       </c>
       <c r="R9">
-        <v>11.39880952380952</v>
+        <v>0.557128412537917</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1523,73 +1520,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1094.4</v>
+        <v>39</v>
       </c>
       <c r="V9">
-        <v>0.2478373114724399</v>
+        <v>1.056910569105691</v>
       </c>
       <c r="W9">
-        <v>0.00272572402044293</v>
+        <v>0.1659395973154363</v>
       </c>
       <c r="X9">
-        <v>0.06338633568867034</v>
+        <v>0.05630962498236871</v>
       </c>
       <c r="Y9">
-        <v>-0.06066061166822741</v>
+        <v>0.1096299723330675</v>
       </c>
       <c r="Z9">
-        <v>0.08509333435547548</v>
+        <v>1.489082969432315</v>
       </c>
       <c r="AA9">
-        <v>0.0110008049369466</v>
+        <v>0.2231079883113898</v>
       </c>
       <c r="AB9">
-        <v>0.05850476471924075</v>
+        <v>0.05454498904132614</v>
       </c>
       <c r="AC9">
-        <v>-0.04750395978229414</v>
+        <v>0.1685629992700637</v>
       </c>
       <c r="AD9">
-        <v>6566.5</v>
+        <v>14.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>6566.5</v>
+        <v>14.8</v>
       </c>
       <c r="AG9">
-        <v>5472.1</v>
+        <v>-24.2</v>
       </c>
       <c r="AH9">
-        <v>0.5979166476967485</v>
+        <v>0.2862669245647969</v>
       </c>
       <c r="AI9">
-        <v>0.7495234507870197</v>
+        <v>0.1917098445595855</v>
       </c>
       <c r="AJ9">
-        <v>0.5534137683431264</v>
+        <v>-1.905511811023622</v>
       </c>
       <c r="AK9">
-        <v>0.7137676906019697</v>
+        <v>-0.6335078534031413</v>
       </c>
       <c r="AL9">
-        <v>67.2</v>
+        <v>1.08</v>
       </c>
       <c r="AM9">
-        <v>65.24000000000001</v>
+        <v>-0.3799999999999999</v>
       </c>
       <c r="AN9">
-        <v>147.561797752809</v>
+        <v>0.896969696969697</v>
       </c>
       <c r="AO9">
-        <v>0.4270833333333333</v>
+        <v>12.68518518518518</v>
       </c>
       <c r="AP9">
-        <v>122.9685393258427</v>
+        <v>-1.466666666666667</v>
       </c>
       <c r="AQ9">
-        <v>0.4399141630901287</v>
+        <v>-36.05263157894738</v>
       </c>
     </row>
     <row r="10">
@@ -1600,7 +1597,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Doyen International Holdings Limited (SEHK:668)</t>
+          <t>Lion Rock Group Limited (SEHK:1127)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1608,104 +1605,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.0941</v>
+      </c>
+      <c r="E10">
+        <v>-0.0182</v>
+      </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.1624775583482944</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.1624775583482944</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.09216038300418912</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.07268041866656896</v>
       </c>
       <c r="K10">
-        <v>5.47</v>
+        <v>19.2</v>
       </c>
       <c r="L10">
-        <v>0.2878947368421053</v>
+        <v>0.05745062836624776</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>18</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.1660516605166052</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.9375</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>18</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.1660516605166052</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.9375</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>8.050000000000001</v>
+        <v>103.1</v>
       </c>
       <c r="V10">
-        <v>0.2531446540880503</v>
+        <v>0.9511070110701106</v>
       </c>
       <c r="W10">
-        <v>0.05426587301587302</v>
+        <v>0.1115630447414294</v>
       </c>
       <c r="X10">
-        <v>0.049997326834937</v>
+        <v>0.05942386008330293</v>
       </c>
       <c r="Y10">
-        <v>0.004268546180936014</v>
+        <v>0.05213918465812648</v>
       </c>
       <c r="Z10">
-        <v>0.1992407877351565</v>
+        <v>2.952296819787986</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.2145741688901709</v>
       </c>
       <c r="AB10">
-        <v>0.05004749132388601</v>
+        <v>0.05277054410064137</v>
       </c>
       <c r="AC10">
-        <v>-0.05004749132388601</v>
+        <v>0.1618036247895295</v>
       </c>
       <c r="AD10">
-        <v>0.797</v>
+        <v>74.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.797</v>
+        <v>74.3</v>
       </c>
       <c r="AG10">
-        <v>-7.253000000000001</v>
+        <v>-28.8</v>
       </c>
       <c r="AH10">
-        <v>0.02445010277019358</v>
+        <v>0.4066776135741653</v>
       </c>
       <c r="AI10">
-        <v>0.006500974738370434</v>
+        <v>0.2597902097902098</v>
       </c>
       <c r="AJ10">
-        <v>-0.2954739886747872</v>
+        <v>-0.3618090452261306</v>
       </c>
       <c r="AK10">
-        <v>-0.06331898696604889</v>
+        <v>-0.1574630945872061</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AM10">
-        <v>-0.053</v>
+        <v>1.95</v>
+      </c>
+      <c r="AN10">
+        <v>1.43159922928709</v>
+      </c>
+      <c r="AO10">
+        <v>8.191489361702128</v>
+      </c>
+      <c r="AP10">
+        <v>-0.5549132947976878</v>
       </c>
       <c r="AQ10">
-        <v>-0</v>
+        <v>15.7948717948718</v>
       </c>
     </row>
     <row r="11">
@@ -1716,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DL Holdings Group Limited (SEHK:1709)</t>
+          <t>REF Holdings Limited (SEHK:1631)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1725,118 +1740,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0101</v>
+        <v>-0.09449999999999999</v>
       </c>
       <c r="E11">
-        <v>0.0149</v>
+        <v>-0.274</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.1158823529411765</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.1158823529411765</v>
       </c>
       <c r="I11">
-        <v>0.0001714075455885206</v>
+        <v>0.08941176470588236</v>
       </c>
       <c r="J11">
-        <v>0.0001188203762623337</v>
+        <v>0.0763921568627451</v>
       </c>
       <c r="K11">
-        <v>3.57</v>
+        <v>1.46</v>
       </c>
       <c r="L11">
-        <v>0.1046920821114369</v>
+        <v>0.08588235294117647</v>
       </c>
       <c r="M11">
-        <v>2.98</v>
+        <v>4.9</v>
       </c>
       <c r="N11">
-        <v>0.005341459042839219</v>
+        <v>0.533769063180828</v>
       </c>
       <c r="O11">
-        <v>0.834733893557423</v>
+        <v>3.356164383561644</v>
       </c>
       <c r="P11">
-        <v>1.83</v>
+        <v>4.9</v>
       </c>
       <c r="Q11">
-        <v>0.003280157734360997</v>
+        <v>0.533769063180828</v>
       </c>
       <c r="R11">
-        <v>0.5126050420168068</v>
+        <v>3.356164383561644</v>
       </c>
       <c r="S11">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>0.3859060402684564</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>11.1</v>
+        <v>5.23</v>
       </c>
       <c r="V11">
-        <v>0.01989603871661588</v>
+        <v>0.5697167755991286</v>
       </c>
       <c r="W11">
-        <v>0.05767366720516963</v>
+        <v>0.1168</v>
       </c>
       <c r="X11">
-        <v>0.05009956456562076</v>
+        <v>0.05450574345905564</v>
       </c>
       <c r="Y11">
-        <v>0.007574102639548864</v>
+        <v>0.06229425654094436</v>
       </c>
       <c r="Z11">
-        <v>0.4373994485573687</v>
+        <v>1.577433423030528</v>
       </c>
       <c r="AA11">
-        <v>5.197196705452381e-05</v>
+        <v>0.120503541492685</v>
       </c>
       <c r="AB11">
-        <v>0.05016771814651352</v>
+        <v>0.0532459894292491</v>
       </c>
       <c r="AC11">
-        <v>-0.050115746179459</v>
+        <v>0.06725755206343592</v>
       </c>
       <c r="AD11">
-        <v>20.2</v>
+        <v>2.17</v>
       </c>
       <c r="AE11">
-        <v>0.01077501347715725</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>20.21077501347716</v>
+        <v>2.17</v>
       </c>
       <c r="AG11">
-        <v>9.110775013477157</v>
+        <v>-3.06</v>
       </c>
       <c r="AH11">
-        <v>0.03496003860679815</v>
+        <v>0.1911894273127753</v>
       </c>
       <c r="AI11">
-        <v>0.2532336643775767</v>
+        <v>0.1930604982206406</v>
       </c>
       <c r="AJ11">
-        <v>0.01606808091655861</v>
+        <v>-0.5000000000000001</v>
       </c>
       <c r="AK11">
-        <v>0.1325960158605421</v>
+        <v>-0.5091514143094843</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="AM11">
-        <v>-0.004</v>
+        <v>-0.124</v>
       </c>
       <c r="AN11">
-        <v>2525</v>
+        <v>1.068965517241379</v>
+      </c>
+      <c r="AO11">
+        <v>15.04950495049505</v>
       </c>
       <c r="AP11">
-        <v>1138.846876684645</v>
+        <v>-1.507389162561577</v>
       </c>
       <c r="AQ11">
-        <v>-0</v>
+        <v>-12.25806451612903</v>
       </c>
     </row>
     <row r="12">
@@ -1847,7 +1865,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>International Alliance Financial Leasing Co., Ltd. (SEHK:1563)</t>
+          <t>Joyas International Holdings Limited (Catalist:E9L)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1855,6 +1873,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.08259999999999999</v>
+      </c>
       <c r="G12">
         <v>0</v>
       </c>
@@ -1862,16 +1883,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>0.3119469026548672</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.2632946334334659</v>
       </c>
       <c r="K12">
-        <v>12</v>
+        <v>0.046</v>
       </c>
       <c r="L12">
-        <v>0.46875</v>
+        <v>0.1017699115044248</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1895,61 +1916,67 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>25.3</v>
+        <v>1.31</v>
       </c>
       <c r="V12">
-        <v>0.0125446251487505</v>
+        <v>0.7797619047619048</v>
       </c>
       <c r="W12">
-        <v>0.06240249609984399</v>
+        <v>0.03622047244094488</v>
       </c>
       <c r="X12">
-        <v>0.0501601328680177</v>
+        <v>0.06384714806382653</v>
       </c>
       <c r="Y12">
-        <v>0.01224236323182629</v>
+        <v>-0.02762667562288165</v>
       </c>
       <c r="Z12">
-        <v>0.07509533587562335</v>
+        <v>0.261271676300578</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>0.06879143023810785</v>
       </c>
       <c r="AB12">
-        <v>0.05023772947878363</v>
+        <v>0.05670346118163314</v>
       </c>
       <c r="AC12">
-        <v>-0.05023772947878363</v>
+        <v>0.01208796905647471</v>
       </c>
       <c r="AD12">
-        <v>86.40000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>86.40000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>61.10000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="AH12">
-        <v>0.04108025865348042</v>
+        <v>0.5213675213675214</v>
       </c>
       <c r="AI12">
-        <v>0.3046544428772919</v>
+        <v>0.5648148148148148</v>
       </c>
       <c r="AJ12">
-        <v>0.02940468742480389</v>
+        <v>0.2363636363636364</v>
       </c>
       <c r="AK12">
-        <v>0.2365466511807975</v>
+        <v>0.2694300518134715</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>0.126</v>
+      </c>
+      <c r="AO12">
+        <v>0.8343195266272188</v>
+      </c>
+      <c r="AQ12">
+        <v>1.119047619047619</v>
       </c>
     </row>
     <row r="13">
@@ -1960,7 +1987,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wealthy Way Group Limited (SEHK:3848)</t>
+          <t>G-Resources Group Limited (SEHK:1051)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1969,46 +1996,43 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0522</v>
-      </c>
-      <c r="E13">
-        <v>-0.0269</v>
+        <v>0.0405</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.4788461538461538</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.4788461538461538</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.825</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>0.825</v>
       </c>
       <c r="K13">
-        <v>4.07</v>
+        <v>-30.5</v>
       </c>
       <c r="L13">
-        <v>0.3282258064516129</v>
+        <v>-0.5865384615384616</v>
       </c>
       <c r="M13">
-        <v>2.39</v>
+        <v>6.91</v>
       </c>
       <c r="N13">
-        <v>0.01944670463791701</v>
+        <v>0.06142222222222223</v>
       </c>
       <c r="O13">
-        <v>0.5872235872235873</v>
+        <v>-0.2265573770491803</v>
       </c>
       <c r="P13">
-        <v>2.39</v>
+        <v>6.91</v>
       </c>
       <c r="Q13">
-        <v>0.01944670463791701</v>
+        <v>0.06142222222222223</v>
       </c>
       <c r="R13">
-        <v>0.5872235872235873</v>
+        <v>-0.2265573770491803</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2017,61 +2041,67 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>17.4</v>
+        <v>474.5</v>
       </c>
       <c r="V13">
-        <v>0.1415785191212368</v>
+        <v>4.217777777777778</v>
       </c>
       <c r="W13">
-        <v>0.05037128712871287</v>
+        <v>-0.01958769507417635</v>
       </c>
       <c r="X13">
-        <v>0.05202565628671682</v>
+        <v>0.05191675589446192</v>
       </c>
       <c r="Y13">
-        <v>-0.001654369158003946</v>
+        <v>-0.07150445096863828</v>
       </c>
       <c r="Z13">
-        <v>0.1196103019195525</v>
+        <v>0.07718706582275477</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>0.06367932930377268</v>
       </c>
       <c r="AB13">
-        <v>0.0507586493786971</v>
+        <v>0.05191675589446192</v>
       </c>
       <c r="AC13">
-        <v>-0.0507586493786971</v>
+        <v>0.01176257340931076</v>
       </c>
       <c r="AD13">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>12.9</v>
+        <v>-474.5</v>
       </c>
       <c r="AH13">
-        <v>0.1977806788511749</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>0.2700534759358289</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>0.09499263622974964</v>
+        <v>1.310773480662983</v>
       </c>
       <c r="AK13">
-        <v>0.1360759493670886</v>
+        <v>-0.453113063407181</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>-10.88302752293578</v>
       </c>
     </row>
     <row r="14">
@@ -2082,7 +2112,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Global International Credit Group Limited (SEHK:1669)</t>
+          <t>Hi Sun Technology (China) Limited (SEHK:818)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2091,109 +2121,121 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.0121</v>
+        <v>-0.0451</v>
       </c>
       <c r="E14">
-        <v>-0.0364</v>
+        <v>0.198</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.2481065552363542</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.1574823713763385</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.05928440846173936</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.05928440846173936</v>
       </c>
       <c r="K14">
-        <v>6.77</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L14">
-        <v>0.6099099099099099</v>
+        <v>0.1817706973100026</v>
       </c>
       <c r="M14">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
-        <v>0.1050583657587549</v>
+        <v>0.005692391899288452</v>
       </c>
       <c r="O14">
-        <v>0.3988183161004432</v>
+        <v>0.01494252873563219</v>
       </c>
       <c r="P14">
-        <v>2.7</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.1050583657587549</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.3988183161004432</v>
+        <v>-0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>3.59</v>
+        <v>405.5</v>
       </c>
       <c r="V14">
-        <v>0.1396887159533074</v>
+        <v>2.219485495347564</v>
       </c>
       <c r="W14">
-        <v>0.06333021515434985</v>
+        <v>0.08228895720028376</v>
       </c>
       <c r="X14">
-        <v>0.05050899930129846</v>
+        <v>0.05411085100606921</v>
       </c>
       <c r="Y14">
-        <v>0.01282121585305139</v>
+        <v>0.02817810619421455</v>
       </c>
       <c r="Z14">
-        <v>0.1118275236751964</v>
+        <v>0.9825254676554361</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>0.05824844114854635</v>
       </c>
       <c r="AB14">
-        <v>0.05086188322492169</v>
+        <v>0.05226713833932932</v>
       </c>
       <c r="AC14">
-        <v>-0.05086188322492169</v>
+        <v>0.005981302809217034</v>
       </c>
       <c r="AD14">
-        <v>2.08</v>
+        <v>36.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.08</v>
+        <v>36.6</v>
       </c>
       <c r="AG14">
-        <v>-1.51</v>
+        <v>-368.9</v>
       </c>
       <c r="AH14">
-        <v>0.07487401007919367</v>
+        <v>0.1668946648426813</v>
       </c>
       <c r="AI14">
-        <v>0.01859134787272078</v>
+        <v>0.0364578145233589</v>
       </c>
       <c r="AJ14">
-        <v>-0.06242248863166597</v>
+        <v>1.981203007518797</v>
       </c>
       <c r="AK14">
-        <v>-0.01394403915412319</v>
+        <v>-0.6164772727272727</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>-0.9500000000000002</v>
+      </c>
+      <c r="AN14">
+        <v>0.9457364341085271</v>
+      </c>
+      <c r="AO14">
+        <v>2.91025641025641</v>
+      </c>
+      <c r="AP14">
+        <v>-9.532299741602065</v>
+      </c>
+      <c r="AQ14">
+        <v>-23.89473684210526</v>
       </c>
     </row>
     <row r="15">
@@ -2204,7 +2246,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Upbest Group Limited (SEHK:335)</t>
+          <t>Yue Da International Holdings Limited (SEHK:629)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2213,109 +2255,118 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.113</v>
+        <v>0.0313</v>
       </c>
       <c r="E15">
-        <v>-0.192</v>
+        <v>0.0203</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.4883870967741936</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.4883870967741936</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.5496774193548387</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.3332585320243104</v>
       </c>
       <c r="K15">
-        <v>9.970000000000001</v>
+        <v>5.02</v>
       </c>
       <c r="L15">
-        <v>0.8105691056910569</v>
+        <v>0.3238709677419355</v>
       </c>
       <c r="M15">
-        <v>6.83</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.03609936575052854</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.6850551654964895</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>6.83</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.03609936575052854</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.6850551654964895</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>66.40000000000001</v>
+        <v>5.65</v>
       </c>
       <c r="V15">
-        <v>0.3509513742071882</v>
+        <v>0.2062043795620438</v>
       </c>
       <c r="W15">
-        <v>0.02898255813953489</v>
+        <v>0.08283828382838283</v>
       </c>
       <c r="X15">
-        <v>0.05114732330378596</v>
+        <v>0.05963146682939627</v>
       </c>
       <c r="Y15">
-        <v>-0.02216476516425108</v>
+        <v>0.02320681699898657</v>
       </c>
       <c r="Z15">
-        <v>0.04079601990049751</v>
+        <v>0.1756772072991046</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.05854592821463007</v>
       </c>
       <c r="AB15">
-        <v>0.05126537015279916</v>
+        <v>0.05571106881227051</v>
       </c>
       <c r="AC15">
-        <v>-0.05126537015279916</v>
+        <v>0.002834859402359557</v>
       </c>
       <c r="AD15">
-        <v>28.5</v>
+        <v>19.3</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>28.5</v>
+        <v>19.3</v>
       </c>
       <c r="AG15">
-        <v>-37.90000000000001</v>
+        <v>13.65</v>
       </c>
       <c r="AH15">
-        <v>0.1309141019751952</v>
+        <v>0.4132762312633833</v>
       </c>
       <c r="AI15">
-        <v>0.07659231389411449</v>
+        <v>0.2403486924034869</v>
       </c>
       <c r="AJ15">
-        <v>-0.2504957038995374</v>
+        <v>0.3325213154689404</v>
       </c>
       <c r="AK15">
-        <v>-0.1239777559699051</v>
+        <v>0.1828533154722036</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>3.318</v>
+      </c>
+      <c r="AN15">
+        <v>2.259953161592506</v>
+      </c>
+      <c r="AO15">
+        <v>2.535714285714286</v>
+      </c>
+      <c r="AP15">
+        <v>1.598360655737705</v>
+      </c>
+      <c r="AQ15">
+        <v>2.567811934900542</v>
       </c>
     </row>
     <row r="16">
@@ -2326,7 +2377,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Oshidori International Holdings Limited (SEHK:622)</t>
+          <t>Shandong Hi-Speed Holdings Group Limited (SEHK:412)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2334,89 +2385,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="G16">
+        <v>0.4349177567672581</v>
+      </c>
+      <c r="H16">
+        <v>0.4349177567672581</v>
+      </c>
+      <c r="I16">
+        <v>0.4818028752752234</v>
+      </c>
+      <c r="J16">
+        <v>0.4818028752752234</v>
+      </c>
       <c r="K16">
-        <v>-520.5</v>
+        <v>-69.90000000000001</v>
+      </c>
+      <c r="L16">
+        <v>-0.09053231446703795</v>
       </c>
       <c r="M16">
-        <v>0.28</v>
+        <v>39.84</v>
       </c>
       <c r="N16">
-        <v>0.001299303944315545</v>
+        <v>0.00851773459046886</v>
       </c>
       <c r="O16">
-        <v>-0.0005379442843419789</v>
+        <v>-0.5699570815450644</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>38.6</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.008252624377311698</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>-0.5522174535050072</v>
       </c>
       <c r="S16">
-        <v>0.28</v>
+        <v>1.240000000000002</v>
       </c>
       <c r="T16">
-        <v>1</v>
+        <v>0.03112449799196792</v>
       </c>
       <c r="U16">
-        <v>73.59999999999999</v>
+        <v>446</v>
       </c>
       <c r="V16">
-        <v>0.3415313225058004</v>
+        <v>0.09535415731297971</v>
       </c>
       <c r="W16">
-        <v>-0.3691227572512588</v>
+        <v>-0.06585021196420161</v>
       </c>
       <c r="X16">
-        <v>0.0520838865630659</v>
+        <v>0.06636295429667106</v>
       </c>
       <c r="Y16">
-        <v>-0.4212066438143247</v>
+        <v>-0.1322131662608727</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>0.1181737480102853</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>0.05693645157340516</v>
       </c>
       <c r="AB16">
-        <v>0.05207685182163223</v>
+        <v>0.05587114755984669</v>
       </c>
       <c r="AC16">
-        <v>-0.05207685182163223</v>
+        <v>0.00106530401355847</v>
       </c>
       <c r="AD16">
-        <v>54.5</v>
+        <v>6169.3</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>54.5</v>
+        <v>6169.3</v>
       </c>
       <c r="AG16">
-        <v>-19.09999999999999</v>
+        <v>5723.3</v>
       </c>
       <c r="AH16">
-        <v>0.2018518518518519</v>
+        <v>0.5687773127062858</v>
       </c>
       <c r="AI16">
-        <v>0.07320349227669577</v>
+        <v>0.7714710884353742</v>
       </c>
       <c r="AJ16">
-        <v>-0.09725050916496941</v>
+        <v>0.5502855604484357</v>
       </c>
       <c r="AK16">
-        <v>-0.02846922045014159</v>
+        <v>0.7579726651480638</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>285.3</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>275.95</v>
+      </c>
+      <c r="AN16">
+        <v>11.25784671532847</v>
+      </c>
+      <c r="AO16">
+        <v>1.303890641430073</v>
+      </c>
+      <c r="AP16">
+        <v>10.44397810218978</v>
+      </c>
+      <c r="AQ16">
+        <v>1.348070302591049</v>
       </c>
     </row>
     <row r="17">
@@ -2427,7 +2505,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zhong Ji Longevity Science Group Limited (SEHK:767)</t>
+          <t>Dingyi Group Investment Limited (SEHK:508)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2436,28 +2514,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.298</v>
-      </c>
-      <c r="E17">
-        <v>-0.368</v>
+        <v>-0.0421</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>0.6569506726457399</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.6569506726457399</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>0.6412556053811659</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>0.3206278026905829</v>
       </c>
       <c r="K17">
-        <v>4.22</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="L17">
-        <v>0.3322834645669291</v>
+        <v>0.2123318385650224</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2481,61 +2556,73 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>1.74</v>
+        <v>26.7</v>
       </c>
       <c r="V17">
-        <v>0.07598253275109171</v>
+        <v>1.491620111731844</v>
       </c>
       <c r="W17">
-        <v>0.07416520210896309</v>
+        <v>0.06234364713627387</v>
       </c>
       <c r="X17">
-        <v>0.05078358858907846</v>
+        <v>0.1286453811991107</v>
       </c>
       <c r="Y17">
-        <v>0.02338161351988462</v>
+        <v>-0.06630173406283686</v>
       </c>
       <c r="Z17">
-        <v>0.2293660827162723</v>
+        <v>0.1508795669824086</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>0.04837618403247632</v>
       </c>
       <c r="AB17">
-        <v>0.05216880184701501</v>
+        <v>0.0599509822260509</v>
       </c>
       <c r="AC17">
-        <v>-0.05216880184701501</v>
+        <v>-0.01157479819357458</v>
       </c>
       <c r="AD17">
-        <v>2.54</v>
+        <v>125.4</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.54</v>
+        <v>125.4</v>
       </c>
       <c r="AG17">
-        <v>0.8</v>
+        <v>98.7</v>
       </c>
       <c r="AH17">
-        <v>0.09984276729559749</v>
+        <v>0.8750872295882763</v>
       </c>
       <c r="AI17">
-        <v>0.0425888665325285</v>
+        <v>0.4445232187167671</v>
       </c>
       <c r="AJ17">
-        <v>0.03375527426160338</v>
+        <v>0.8464837049742711</v>
       </c>
       <c r="AK17">
-        <v>0.01381692573402418</v>
+        <v>0.3864526233359437</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>7.145</v>
+      </c>
+      <c r="AN17">
+        <v>4.339100346020762</v>
+      </c>
+      <c r="AO17">
+        <v>3.966712898751734</v>
+      </c>
+      <c r="AP17">
+        <v>3.41522491349481</v>
+      </c>
+      <c r="AQ17">
+        <v>4.002799160251925</v>
       </c>
     </row>
     <row r="18">
@@ -2546,7 +2633,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AEON Credit Service (Asia) Company Limited (SEHK:900)</t>
+          <t>Left Field Printing Group Limited (SEHK:1540)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2554,47 +2641,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D18">
-        <v>0.00792</v>
-      </c>
-      <c r="E18">
-        <v>0.00163</v>
-      </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.02694444444444444</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>0.02694444444444444</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>0.002652777777777778</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>0.00169483024691358</v>
       </c>
       <c r="K18">
-        <v>44.8</v>
+        <v>1.27</v>
       </c>
       <c r="L18">
-        <v>0.3438219493476592</v>
+        <v>0.01763888888888889</v>
       </c>
       <c r="M18">
-        <v>23.6</v>
+        <v>1.91</v>
       </c>
       <c r="N18">
-        <v>0.0885885885885886</v>
+        <v>0.07490196078431373</v>
       </c>
       <c r="O18">
-        <v>0.5267857142857143</v>
+        <v>1.503937007874016</v>
       </c>
       <c r="P18">
-        <v>23.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
-        <v>0.0885885885885886</v>
+        <v>0.07490196078431373</v>
       </c>
       <c r="R18">
-        <v>0.5267857142857143</v>
+        <v>1.503937007874016</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2603,61 +2684,73 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>71.5</v>
+        <v>7.96</v>
       </c>
       <c r="V18">
-        <v>0.2683933933933934</v>
+        <v>0.312156862745098</v>
       </c>
       <c r="W18">
-        <v>0.100044662795891</v>
+        <v>0.0370262390670554</v>
       </c>
       <c r="X18">
-        <v>0.05848931780907542</v>
+        <v>0.05332554691578555</v>
       </c>
       <c r="Y18">
-        <v>0.0415553449868156</v>
+        <v>-0.01629930784873015</v>
       </c>
       <c r="Z18">
-        <v>0.2512533744697262</v>
+        <v>2.33387358184765</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>0.003955519538987934</v>
       </c>
       <c r="AB18">
-        <v>0.05221155630357444</v>
+        <v>0.05270911211394769</v>
       </c>
       <c r="AC18">
-        <v>-0.05221155630357444</v>
+        <v>-0.04875359257495976</v>
       </c>
       <c r="AD18">
-        <v>253.7</v>
+        <v>3.28</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>253.7</v>
+        <v>3.28</v>
       </c>
       <c r="AG18">
-        <v>182.2</v>
+        <v>-4.68</v>
       </c>
       <c r="AH18">
-        <v>0.4877908094597194</v>
+        <v>0.1139680333564976</v>
       </c>
       <c r="AI18">
-        <v>0.3460174577195854</v>
+        <v>0.09116175653140632</v>
       </c>
       <c r="AJ18">
-        <v>0.4061524743646902</v>
+        <v>-0.2247838616714697</v>
       </c>
       <c r="AK18">
-        <v>0.2753513676892851</v>
+        <v>-0.1670235546038544</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>-0.167</v>
+      </c>
+      <c r="AN18">
+        <v>1.895953757225433</v>
+      </c>
+      <c r="AO18">
+        <v>1.085227272727273</v>
+      </c>
+      <c r="AP18">
+        <v>-2.705202312138728</v>
+      </c>
+      <c r="AQ18">
+        <v>-1.143712574850299</v>
       </c>
     </row>
     <row r="19">
@@ -2668,7 +2761,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hong Kong Finance Group Limited (SEHK:1273)</t>
+          <t>Global International Credit Group Limited (SEHK:1669)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2677,10 +2770,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.107</v>
+        <v>-0.0191</v>
       </c>
       <c r="E19">
-        <v>0.0784</v>
+        <v>-0.0515</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2695,28 +2788,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="L19">
-        <v>0.4846625766871165</v>
+        <v>0.5855855855855856</v>
       </c>
       <c r="M19">
-        <v>1.37</v>
+        <v>2.6</v>
       </c>
       <c r="N19">
-        <v>0.07445652173913045</v>
+        <v>0.1069958847736626</v>
       </c>
       <c r="O19">
-        <v>0.1734177215189873</v>
+        <v>0.4</v>
       </c>
       <c r="P19">
-        <v>1.37</v>
+        <v>2.6</v>
       </c>
       <c r="Q19">
-        <v>0.07445652173913045</v>
+        <v>0.1069958847736626</v>
       </c>
       <c r="R19">
-        <v>0.1734177215189873</v>
+        <v>0.4</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2725,55 +2818,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>11.5</v>
+        <v>13.8</v>
       </c>
       <c r="V19">
-        <v>0.625</v>
+        <v>0.5679012345679012</v>
       </c>
       <c r="W19">
-        <v>0.08700440528634362</v>
+        <v>0.05919854280510018</v>
       </c>
       <c r="X19">
-        <v>0.07669463644033186</v>
+        <v>0.0521074103704168</v>
       </c>
       <c r="Y19">
-        <v>0.01030976884601176</v>
+        <v>0.00709113243468338</v>
       </c>
       <c r="Z19">
-        <v>0.1194489227612487</v>
+        <v>0.1025025394773294</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.0535061818452679</v>
+        <v>0.05195267612236572</v>
       </c>
       <c r="AC19">
-        <v>-0.0535061818452679</v>
+        <v>-0.05195267612236572</v>
       </c>
       <c r="AD19">
-        <v>54.1</v>
+        <v>0.423</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>54.1</v>
+        <v>0.423</v>
       </c>
       <c r="AG19">
-        <v>42.6</v>
+        <v>-13.377</v>
       </c>
       <c r="AH19">
-        <v>0.7462068965517241</v>
+        <v>0.01710957408081544</v>
       </c>
       <c r="AI19">
-        <v>0.3589913735899138</v>
+        <v>0.003700042861016593</v>
       </c>
       <c r="AJ19">
-        <v>0.6983606557377049</v>
+        <v>-1.22466355396869</v>
       </c>
       <c r="AK19">
-        <v>0.3060344827586207</v>
+        <v>-0.1330740228604399</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2790,7 +2883,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sun Hung Kai &amp; Co. Limited (SEHK:86)</t>
+          <t>Upbest Group Limited (SEHK:335)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2799,10 +2892,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0247</v>
-      </c>
-      <c r="F20">
-        <v>0.1</v>
+        <v>-0.113</v>
+      </c>
+      <c r="E20">
+        <v>-0.09810000000000001</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2811,103 +2904,97 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0.001429786020694399</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0.0007148930103471996</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>-35.7</v>
+        <v>14.7</v>
       </c>
       <c r="L20">
-        <v>-0.09826589595375723</v>
+        <v>1.495422177009156</v>
       </c>
       <c r="M20">
-        <v>72.50999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="N20">
-        <v>0.09807926416880833</v>
+        <v>0.03067622033139274</v>
       </c>
       <c r="O20">
-        <v>-2.031092436974789</v>
+        <v>0.4659863945578231</v>
       </c>
       <c r="P20">
-        <v>66.59999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="Q20">
-        <v>0.09008521574462329</v>
+        <v>0.03067622033139274</v>
       </c>
       <c r="R20">
-        <v>-1.865546218487395</v>
+        <v>0.4659863945578231</v>
       </c>
       <c r="S20">
-        <v>5.909999999999997</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>0.08150599917252789</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>1039.7</v>
+        <v>50.9</v>
       </c>
       <c r="V20">
-        <v>1.40633031245773</v>
+        <v>0.2279444693237797</v>
       </c>
       <c r="W20">
-        <v>-0.01096336332647483</v>
+        <v>0.04275741710296684</v>
       </c>
       <c r="X20">
-        <v>0.08173766854507669</v>
+        <v>0.05222232696477444</v>
       </c>
       <c r="Y20">
-        <v>-0.09270103187155153</v>
+        <v>-0.009464909861807605</v>
       </c>
       <c r="Z20">
-        <v>0.08024813893148271</v>
+        <v>0.03213468453743053</v>
       </c>
       <c r="AA20">
-        <v>5.736883361548798e-05</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.05366208638981464</v>
+        <v>0.05210546202398118</v>
       </c>
       <c r="AC20">
-        <v>-0.05360471755619915</v>
+        <v>-0.05210546202398118</v>
       </c>
       <c r="AD20">
-        <v>2580.2</v>
+        <v>6.23</v>
       </c>
       <c r="AE20">
-        <v>0.6077936934086237</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>2580.807793693408</v>
+        <v>6.23</v>
       </c>
       <c r="AG20">
-        <v>1541.107793693408</v>
+        <v>-44.67</v>
       </c>
       <c r="AH20">
-        <v>0.7773265068669425</v>
+        <v>0.02714242146996036</v>
       </c>
       <c r="AI20">
-        <v>0.4280295974395814</v>
+        <v>0.01738620824379761</v>
       </c>
       <c r="AJ20">
-        <v>0.6758035987929114</v>
+        <v>-0.2500699770475284</v>
       </c>
       <c r="AK20">
-        <v>0.3088511336330843</v>
+        <v>-0.1453013694174284</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>4025.273010920436</v>
-      </c>
-      <c r="AP20">
-        <v>2404.224327134802</v>
       </c>
     </row>
     <row r="21">
@@ -2918,7 +3005,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Oi Wah Pawnshop Credit Holdings Limited (SEHK:1319)</t>
+          <t>DL Holdings Group Limited (SEHK:1709)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2927,10 +3014,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.0441</v>
-      </c>
-      <c r="E21">
-        <v>-0.0553</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2939,97 +3023,106 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>8.364231089960392e-05</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>8.364231089960392e-05</v>
       </c>
       <c r="K21">
-        <v>9.960000000000001</v>
+        <v>-1.53</v>
       </c>
       <c r="L21">
-        <v>0.5297872340425532</v>
+        <v>-0.07886597938144331</v>
       </c>
       <c r="M21">
-        <v>3.736</v>
+        <v>6.21</v>
       </c>
       <c r="N21">
-        <v>0.06300168634064082</v>
+        <v>0.00811764705882353</v>
       </c>
       <c r="O21">
-        <v>0.3751004016064257</v>
+        <v>-4.058823529411764</v>
       </c>
       <c r="P21">
-        <v>3.66</v>
+        <v>2.46</v>
       </c>
       <c r="Q21">
-        <v>0.06172006745362564</v>
+        <v>0.003215686274509804</v>
       </c>
       <c r="R21">
-        <v>0.3674698795180723</v>
+        <v>-1.607843137254902</v>
       </c>
       <c r="S21">
-        <v>0.07600000000000007</v>
+        <v>3.75</v>
       </c>
       <c r="T21">
-        <v>0.02034261241970023</v>
+        <v>0.6038647342995169</v>
       </c>
       <c r="U21">
-        <v>14.4</v>
+        <v>7.35</v>
       </c>
       <c r="V21">
-        <v>0.2428330522765599</v>
+        <v>0.009607843137254901</v>
       </c>
       <c r="W21">
-        <v>0.0803225806451613</v>
+        <v>-0.02567114093959732</v>
       </c>
       <c r="X21">
-        <v>0.05313452367109668</v>
+        <v>0.0521945323555782</v>
       </c>
       <c r="Y21">
-        <v>0.02718805697406462</v>
+        <v>-0.07786567329517552</v>
       </c>
       <c r="Z21">
-        <v>0.1558872305140962</v>
+        <v>0.2858705390318805</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.391087250274191e-05</v>
       </c>
       <c r="AB21">
-        <v>0.05369565510106083</v>
+        <v>0.05214384591542498</v>
       </c>
       <c r="AC21">
-        <v>-0.05369565510106083</v>
+        <v>-0.05211993504292224</v>
       </c>
       <c r="AD21">
-        <v>21.8</v>
+        <v>19.4</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>0.001886695842738421</v>
       </c>
       <c r="AF21">
-        <v>21.8</v>
+        <v>19.40188669584274</v>
       </c>
       <c r="AG21">
-        <v>7.4</v>
+        <v>12.05188669584274</v>
       </c>
       <c r="AH21">
-        <v>0.2688039457459926</v>
+        <v>0.02473462522836327</v>
       </c>
       <c r="AI21">
-        <v>0.1453333333333333</v>
+        <v>0.2621809735147292</v>
       </c>
       <c r="AJ21">
-        <v>0.1109445277361319</v>
+        <v>0.01550975797393584</v>
       </c>
       <c r="AK21">
-        <v>0.05457227138643068</v>
+        <v>0.1808183877950817</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>-0.451</v>
+      </c>
+      <c r="AN21">
+        <v>9699.999999999998</v>
+      </c>
+      <c r="AP21">
+        <v>6025.943347921369</v>
+      </c>
+      <c r="AQ21">
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -3040,7 +3133,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Allied Group Limited (SEHK:373)</t>
+          <t>Oi Wah Pawnshop Credit Holdings Limited (SEHK:1319)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3049,10 +3142,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.1</v>
+        <v>-0.0103</v>
       </c>
       <c r="E22">
-        <v>-0.0353</v>
+        <v>-0.0176</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3067,85 +3160,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>495.1</v>
+        <v>11.7</v>
       </c>
       <c r="L22">
-        <v>0.6973239436619718</v>
+        <v>0.5545023696682464</v>
       </c>
       <c r="M22">
-        <v>59.797</v>
+        <v>4.415</v>
       </c>
       <c r="N22">
-        <v>0.07208800482218203</v>
+        <v>0.07333887043189369</v>
       </c>
       <c r="O22">
-        <v>0.1207776206826904</v>
+        <v>0.3773504273504274</v>
       </c>
       <c r="P22">
-        <v>59.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q22">
-        <v>0.07148884870403857</v>
+        <v>0.07308970099667775</v>
       </c>
       <c r="R22">
-        <v>0.1197737830741264</v>
+        <v>0.3760683760683761</v>
       </c>
       <c r="S22">
-        <v>0.4969999999999999</v>
+        <v>0.01499999999999968</v>
       </c>
       <c r="T22">
-        <v>0.008311453751860459</v>
+        <v>0.003397508493771162</v>
       </c>
       <c r="U22">
-        <v>1492.8</v>
+        <v>11.7</v>
       </c>
       <c r="V22">
-        <v>1.799638336347197</v>
+        <v>0.1943521594684385</v>
       </c>
       <c r="W22">
-        <v>0.09369086367421089</v>
+        <v>0.09126365054602184</v>
       </c>
       <c r="X22">
-        <v>0.09233341909543141</v>
+        <v>0.05431829880922537</v>
       </c>
       <c r="Y22">
-        <v>0.001357444578779482</v>
+        <v>0.03694535173679647</v>
       </c>
       <c r="Z22">
-        <v>0.09761597052272666</v>
+        <v>0.1556047197640118</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.05389061207302159</v>
+        <v>0.05229430874734691</v>
       </c>
       <c r="AC22">
-        <v>-0.05389061207302159</v>
+        <v>-0.05229430874734691</v>
       </c>
       <c r="AD22">
-        <v>3855.4</v>
+        <v>13.2</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>3855.4</v>
+        <v>13.2</v>
       </c>
       <c r="AG22">
-        <v>2362.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH22">
-        <v>0.822941791713804</v>
+        <v>0.1798365122615803</v>
       </c>
       <c r="AI22">
-        <v>0.3001806347130088</v>
+        <v>0.08876933422999328</v>
       </c>
       <c r="AJ22">
-        <v>0.7401397199335861</v>
+        <v>0.02431118314424635</v>
       </c>
       <c r="AK22">
-        <v>0.2081439193713218</v>
+        <v>0.01094890510948905</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3162,7 +3255,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hao Wen Holdings Limited (SEHK:8019)</t>
+          <t>Capital Industrial Financial Services Group Limited (SEHK:730)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3171,7 +3264,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>-0.038</v>
+        <v>0.255</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3186,82 +3279,85 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>-1.71</v>
+        <v>3.53</v>
       </c>
       <c r="L23">
-        <v>-0.3190298507462686</v>
+        <v>0.08485576923076922</v>
       </c>
       <c r="M23">
-        <v>-0</v>
+        <v>1.53</v>
       </c>
       <c r="N23">
-        <v>-0</v>
+        <v>0.01877300613496933</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>0.4334277620396601</v>
       </c>
       <c r="P23">
-        <v>-0</v>
+        <v>1.53</v>
       </c>
       <c r="Q23">
-        <v>-0</v>
+        <v>0.01877300613496933</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>0.4334277620396601</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
       <c r="U23">
-        <v>0</v>
+        <v>48.3</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>0.592638036809816</v>
       </c>
       <c r="W23">
-        <v>-0.03468559837728195</v>
+        <v>0.01868713605082054</v>
       </c>
       <c r="X23">
-        <v>0.0551134216040054</v>
+        <v>0.05257390536477446</v>
       </c>
       <c r="Y23">
-        <v>-0.08979901998128734</v>
+        <v>-0.03388676931395393</v>
       </c>
       <c r="Z23">
-        <v>0.09523132684244191</v>
+        <v>0.2545276554087127</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.05515345331111729</v>
+        <v>0.05231029038589313</v>
       </c>
       <c r="AC23">
-        <v>-0.05515345331111729</v>
+        <v>-0.05231029038589313</v>
       </c>
       <c r="AD23">
-        <v>7.88</v>
+        <v>4.89</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>7.88</v>
+        <v>4.89</v>
       </c>
       <c r="AG23">
-        <v>7.88</v>
+        <v>-43.41</v>
       </c>
       <c r="AH23">
-        <v>0.3685687558465856</v>
+        <v>0.05660377358490565</v>
       </c>
       <c r="AI23">
-        <v>0.1513056835637481</v>
+        <v>0.02185084230752044</v>
       </c>
       <c r="AJ23">
-        <v>0.3685687558465856</v>
+        <v>-1.139669204515621</v>
       </c>
       <c r="AK23">
-        <v>0.1513056835637481</v>
+        <v>-0.2473645221949968</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3278,7 +3374,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>China Tonghai International Financial Limited (SEHK:952)</t>
+          <t>China Financial Services Holdings Limited (SEHK:605)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3286,8 +3382,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D24">
+        <v>-0.292</v>
+      </c>
+      <c r="G24">
+        <v>0.3983695652173914</v>
+      </c>
+      <c r="H24">
+        <v>0.3983695652173914</v>
+      </c>
+      <c r="I24">
+        <v>0.09565217391304348</v>
+      </c>
+      <c r="J24">
+        <v>0.09565217391304348</v>
+      </c>
       <c r="K24">
-        <v>-321.1</v>
+        <v>-16.4</v>
+      </c>
+      <c r="L24">
+        <v>-0.8913043478260869</v>
       </c>
       <c r="M24">
         <v>-0</v>
@@ -3311,61 +3425,73 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>27.2</v>
+        <v>56.6</v>
       </c>
       <c r="V24">
-        <v>0.1845318860244233</v>
+        <v>7.284427284427285</v>
       </c>
       <c r="W24">
-        <v>-0.424454725710509</v>
+        <v>-0.1534144059869036</v>
       </c>
       <c r="X24">
-        <v>0.05918064661080635</v>
+        <v>0.2727990424624057</v>
       </c>
       <c r="Y24">
-        <v>-0.4836353723213153</v>
+        <v>-0.4262134484493093</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>0.0856610800744879</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>0.00819366852886406</v>
       </c>
       <c r="AB24">
-        <v>0.05717419102150335</v>
+        <v>0.06066407600610404</v>
       </c>
       <c r="AC24">
-        <v>-0.05717419102150335</v>
+        <v>-0.05247040747723998</v>
       </c>
       <c r="AD24">
-        <v>151.5</v>
+        <v>156.7</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>151.5</v>
+        <v>156.7</v>
       </c>
       <c r="AG24">
-        <v>124.3</v>
+        <v>100.1</v>
       </c>
       <c r="AH24">
-        <v>0.506858481097357</v>
+        <v>0.9527573417644555</v>
       </c>
       <c r="AI24">
-        <v>0.2619294605809129</v>
+        <v>0.626298960831335</v>
       </c>
       <c r="AJ24">
-        <v>0.4574898785425101</v>
+        <v>0.9279688513951979</v>
       </c>
       <c r="AK24">
-        <v>0.2255079825834543</v>
+        <v>0.5170454545454546</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>6.499999999999999</v>
+      </c>
+      <c r="AN24">
+        <v>76.06796116504853</v>
+      </c>
+      <c r="AO24">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AP24">
+        <v>48.59223300970874</v>
+      </c>
+      <c r="AQ24">
+        <v>0.2707692307692308</v>
       </c>
     </row>
     <row r="25">
@@ -3376,7 +3502,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CSSC (Hong Kong) Shipping Company Limited (SEHK:3877)</t>
+          <t>Quam Plus International Financial Limited (SEHK:952)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3384,98 +3510,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
       <c r="K25">
-        <v>201.3</v>
-      </c>
-      <c r="L25">
-        <v>0.6604330708661418</v>
+        <v>-156.6</v>
       </c>
       <c r="M25">
-        <v>70.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N25">
-        <v>0.07711688027166175</v>
+        <v>-0</v>
       </c>
       <c r="O25">
-        <v>0.3497267759562842</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>70.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q25">
-        <v>0.07711688027166175</v>
+        <v>-0</v>
       </c>
       <c r="R25">
-        <v>0.3497267759562842</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
       <c r="U25">
-        <v>161.8</v>
+        <v>20.4</v>
       </c>
       <c r="V25">
-        <v>0.1772373753970862</v>
+        <v>0.1364548494983278</v>
       </c>
       <c r="W25">
-        <v>0.1664737016209064</v>
+        <v>-0.3668306394940267</v>
       </c>
       <c r="X25">
-        <v>0.08717370225196334</v>
+        <v>0.05930144559429518</v>
       </c>
       <c r="Y25">
-        <v>0.07929999936894304</v>
+        <v>-0.4261320850883219</v>
       </c>
       <c r="Z25">
-        <v>0.07688039146446048</v>
+        <v>0</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.05895728017123679</v>
+        <v>0.0527622285526349</v>
       </c>
       <c r="AC25">
-        <v>-0.05895728017123679</v>
+        <v>-0.0527622285526349</v>
       </c>
       <c r="AD25">
-        <v>3728.7</v>
+        <v>100.8</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>3728.7</v>
+        <v>100.8</v>
       </c>
       <c r="AG25">
-        <v>3566.9</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AH25">
-        <v>0.8033221302998966</v>
+        <v>0.4027167399121054</v>
       </c>
       <c r="AI25">
-        <v>0.7270688713828874</v>
+        <v>0.2713324360699865</v>
       </c>
       <c r="AJ25">
-        <v>0.7962185811866601</v>
+        <v>0.3497172683775555</v>
       </c>
       <c r="AK25">
-        <v>0.7181774252003382</v>
+        <v>0.2289945884363429</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3492,7 +3600,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VCREDIT Holdings Limited (SEHK:2003)</t>
+          <t>Haosen Fintech Group Limited (SEHK:3848)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3500,104 +3608,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D26">
+        <v>0.0725</v>
+      </c>
+      <c r="E26">
+        <v>0.0139</v>
+      </c>
       <c r="G26">
-        <v>0.03545721141029059</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>0.003024049731342952</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>0.002184974480001984</v>
       </c>
       <c r="K26">
-        <v>108.9</v>
+        <v>3.88</v>
       </c>
       <c r="L26">
-        <v>0.2903225806451613</v>
+        <v>0.3527272727272727</v>
       </c>
       <c r="M26">
-        <v>8.57</v>
+        <v>0.453</v>
       </c>
       <c r="N26">
-        <v>0.04698464912280702</v>
+        <v>0.003685923515052889</v>
       </c>
       <c r="O26">
-        <v>0.07869605142332414</v>
+        <v>0.1167525773195876</v>
       </c>
       <c r="P26">
-        <v>6.03</v>
+        <v>0.453</v>
       </c>
       <c r="Q26">
-        <v>0.03305921052631579</v>
+        <v>0.003685923515052889</v>
       </c>
       <c r="R26">
-        <v>0.05537190082644628</v>
+        <v>0.1167525773195876</v>
       </c>
       <c r="S26">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>0.2963827304550758</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>275.1</v>
+        <v>2.93</v>
       </c>
       <c r="V26">
-        <v>1.508223684210526</v>
+        <v>0.02384052074857608</v>
       </c>
       <c r="W26">
-        <v>0.2279673435210383</v>
+        <v>0.04737484737484737</v>
       </c>
       <c r="X26">
-        <v>0.09395668969015894</v>
+        <v>0.05350648701944484</v>
       </c>
       <c r="Y26">
-        <v>0.1340106538308794</v>
+        <v>-0.006131639644597467</v>
       </c>
       <c r="Z26">
-        <v>0.2869492044063647</v>
+        <v>0.1159864341980388</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>0.0002534273987491442</v>
       </c>
       <c r="AB26">
-        <v>0.0592433471881823</v>
+        <v>0.05308045821226546</v>
       </c>
       <c r="AC26">
-        <v>-0.0592433471881823</v>
+        <v>-0.05282703081351631</v>
       </c>
       <c r="AD26">
-        <v>880.1</v>
+        <v>17.8</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>0.03867726477613763</v>
       </c>
       <c r="AF26">
-        <v>880.1</v>
+        <v>17.83867726477614</v>
       </c>
       <c r="AG26">
-        <v>605</v>
+        <v>14.90867726477614</v>
       </c>
       <c r="AH26">
-        <v>0.8283294117647059</v>
+        <v>0.1267503547103521</v>
       </c>
       <c r="AI26">
-        <v>0.6171376481312671</v>
+        <v>0.183641344180056</v>
       </c>
       <c r="AJ26">
-        <v>0.7683515367030734</v>
+        <v>0.108183878988488</v>
       </c>
       <c r="AK26">
-        <v>0.525629887054735</v>
+        <v>0.1582516355990742</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
         <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>434.1463414634146</v>
+      </c>
+      <c r="AP26">
+        <v>363.6262747506375</v>
       </c>
     </row>
     <row r="27">
@@ -3608,7 +3728,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gome Finance Technology Co., Ltd. (SEHK:628)</t>
+          <t>Oshidori International Holdings Limited (SEHK:622)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3616,6 +3736,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D27">
+        <v>-0.298</v>
+      </c>
       <c r="G27">
         <v>0</v>
       </c>
@@ -3629,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>-20</v>
+        <v>-3.81</v>
       </c>
       <c r="L27">
-        <v>-2.212389380530974</v>
+        <v>-0.5450643776824035</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3656,55 +3779,55 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>33.4</v>
+        <v>62.8</v>
       </c>
       <c r="V27">
-        <v>0.4751066856330014</v>
+        <v>0.3974683544303798</v>
       </c>
       <c r="W27">
-        <v>-0.07572889057175312</v>
+        <v>-0.005521739130434783</v>
       </c>
       <c r="X27">
-        <v>0.06692460133560967</v>
+        <v>0.05401713869514442</v>
       </c>
       <c r="Y27">
-        <v>-0.1426534919073628</v>
+        <v>-0.05953887782557921</v>
       </c>
       <c r="Z27">
-        <v>0.02484881803188565</v>
+        <v>0.01041884036369057</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.0592947601776672</v>
+        <v>0.05303549733505208</v>
       </c>
       <c r="AC27">
-        <v>-0.0592947601776672</v>
+        <v>-0.05303549733505208</v>
       </c>
       <c r="AD27">
-        <v>131.7</v>
+        <v>30.3</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>131.7</v>
+        <v>30.3</v>
       </c>
       <c r="AG27">
-        <v>98.29999999999998</v>
+        <v>-32.5</v>
       </c>
       <c r="AH27">
-        <v>0.6519801980198019</v>
+        <v>0.1609134360063728</v>
       </c>
       <c r="AI27">
-        <v>0.3558497703323426</v>
+        <v>0.04564627899969871</v>
       </c>
       <c r="AJ27">
-        <v>0.5830367734282326</v>
+        <v>-0.2589641434262948</v>
       </c>
       <c r="AK27">
-        <v>0.2919512919512919</v>
+        <v>-0.0540765391014975</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3721,7 +3844,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>China Properties Investment Holdings Limited (SEHK:736)</t>
+          <t>AEON Credit Service (Asia) Company Limited (SEHK:900)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3730,7 +3853,13 @@
         </is>
       </c>
       <c r="D28">
-        <v>-0.485</v>
+        <v>0.0158</v>
+      </c>
+      <c r="E28">
+        <v>-0.0196</v>
+      </c>
+      <c r="F28">
+        <v>0.053</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3745,82 +3874,85 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>-9.890000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="L28">
-        <v>-32.21498371335505</v>
+        <v>0.3335579514824798</v>
       </c>
       <c r="M28">
-        <v>-0</v>
+        <v>23.5</v>
       </c>
       <c r="N28">
-        <v>-0</v>
+        <v>0.08042436687200548</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>0.4747474747474748</v>
       </c>
       <c r="P28">
-        <v>-0</v>
+        <v>23.5</v>
       </c>
       <c r="Q28">
-        <v>-0</v>
+        <v>0.08042436687200548</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>0.4747474747474748</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
       <c r="U28">
-        <v>1.16</v>
+        <v>44.2</v>
       </c>
       <c r="V28">
-        <v>0.1611111111111111</v>
+        <v>0.1512662559890486</v>
       </c>
       <c r="W28">
-        <v>-0.116903073286052</v>
+        <v>0.1035998325659272</v>
       </c>
       <c r="X28">
-        <v>0.07177270459580326</v>
+        <v>0.06516694627522189</v>
       </c>
       <c r="Y28">
-        <v>-0.1886757778818553</v>
+        <v>0.03843288629070528</v>
       </c>
       <c r="Z28">
-        <v>0.002934345220458217</v>
+        <v>0.2450138687095496</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.06008590563725386</v>
+        <v>0.05306612234648268</v>
       </c>
       <c r="AC28">
-        <v>-0.06008590563725386</v>
+        <v>-0.05306612234648268</v>
       </c>
       <c r="AD28">
-        <v>17.3</v>
+        <v>353.5</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>17.3</v>
+        <v>353.5</v>
       </c>
       <c r="AG28">
-        <v>16.14</v>
+        <v>309.3</v>
       </c>
       <c r="AH28">
-        <v>0.7061224489795919</v>
+        <v>0.5474678643332817</v>
       </c>
       <c r="AI28">
-        <v>0.1787190082644628</v>
+        <v>0.412004662004662</v>
       </c>
       <c r="AJ28">
-        <v>0.6915167095115682</v>
+        <v>0.514214463840399</v>
       </c>
       <c r="AK28">
-        <v>0.1687578419071518</v>
+        <v>0.3800688129761612</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3837,7 +3969,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aceso Life Science Group Limited (SEHK:474)</t>
+          <t>Litu Holdings Limited (SEHK:1008)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3846,112 +3978,118 @@
         </is>
       </c>
       <c r="D29">
-        <v>-0.0533</v>
+        <v>-0.0682</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>0.167070895522388</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>0.1119402985074627</v>
       </c>
       <c r="I29">
-        <v>0.004882066335114467</v>
+        <v>0.001902985074626866</v>
       </c>
       <c r="J29">
-        <v>0.004882066335114467</v>
+        <v>0.001902985074626866</v>
       </c>
       <c r="K29">
-        <v>-43.1</v>
+        <v>-7.88</v>
       </c>
       <c r="L29">
-        <v>-2.023474178403756</v>
+        <v>-0.07350746268656716</v>
       </c>
       <c r="M29">
-        <v>0.764</v>
+        <v>7.839500000000001</v>
       </c>
       <c r="N29">
-        <v>0.006725352112676056</v>
+        <v>0.2079442970822281</v>
       </c>
       <c r="O29">
-        <v>-0.01772621809744779</v>
+        <v>-0.9948604060913707</v>
       </c>
       <c r="P29">
-        <v>-0</v>
+        <v>7.839500000000001</v>
       </c>
       <c r="Q29">
-        <v>-0</v>
+        <v>0.2079442970822281</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>-0.9948604060913707</v>
       </c>
       <c r="S29">
-        <v>0.764</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>34.8</v>
+        <v>43.3</v>
       </c>
       <c r="V29">
-        <v>0.3063380281690141</v>
+        <v>1.148541114058355</v>
       </c>
       <c r="W29">
-        <v>-0.1544802867383513</v>
+        <v>-0.02398052343274498</v>
       </c>
       <c r="X29">
-        <v>0.07782419308461461</v>
+        <v>0.05673933821417378</v>
       </c>
       <c r="Y29">
-        <v>-0.2323044798229659</v>
+        <v>-0.08071986164691874</v>
       </c>
       <c r="Z29">
-        <v>0.03275310314450209</v>
+        <v>0.468941382327209</v>
       </c>
       <c r="AA29">
-        <v>0.0001599028222323054</v>
+        <v>0.0008923884514435693</v>
       </c>
       <c r="AB29">
-        <v>0.06078419655412031</v>
+        <v>0.05404218036076749</v>
       </c>
       <c r="AC29">
-        <v>-0.060624293731888</v>
+        <v>-0.05314979190932392</v>
       </c>
       <c r="AD29">
-        <v>347.9</v>
+        <v>16.6</v>
       </c>
       <c r="AE29">
-        <v>0.1200599353103094</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>348.0200599353103</v>
+        <v>16.6</v>
       </c>
       <c r="AG29">
-        <v>313.2200599353103</v>
+        <v>-26.7</v>
       </c>
       <c r="AH29">
-        <v>0.7539101744930247</v>
+        <v>0.3057090239410681</v>
       </c>
       <c r="AI29">
-        <v>0.5033409935602263</v>
+        <v>0.05426610003269042</v>
       </c>
       <c r="AJ29">
-        <v>0.7338456865939773</v>
+        <v>-2.427272727272725</v>
       </c>
       <c r="AK29">
-        <v>0.4770187191146254</v>
+        <v>-0.1016755521706016</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>0.871</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="AN29">
-        <v>2717.96875</v>
+        <v>1.106666666666667</v>
+      </c>
+      <c r="AO29">
+        <v>0.2342135476463834</v>
       </c>
       <c r="AP29">
-        <v>2447.031718244612</v>
+        <v>-1.78</v>
+      </c>
+      <c r="AQ29">
+        <v>1.805309734513274</v>
       </c>
     </row>
     <row r="30">
@@ -3962,7 +4100,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Styland Holdings Limited (SEHK:211)</t>
+          <t>Sun Hung Kai &amp; Co. Limited (SEHK:86)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3971,10 +4109,10 @@
         </is>
       </c>
       <c r="D30">
-        <v>-0.243</v>
-      </c>
-      <c r="E30">
-        <v>0.05889999999999999</v>
+        <v>-0.0546</v>
+      </c>
+      <c r="F30">
+        <v>0.04</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3983,88 +4121,91 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0.005141812348592668</v>
+        <v>0.0002131075748665872</v>
       </c>
       <c r="J30">
-        <v>0.005141812348592668</v>
+        <v>0.0002131075748665872</v>
       </c>
       <c r="K30">
-        <v>1.12</v>
+        <v>-181.3</v>
       </c>
       <c r="L30">
-        <v>0.4725738396624473</v>
+        <v>-0.6196172248803827</v>
       </c>
       <c r="M30">
-        <v>-0</v>
+        <v>80.69999999999999</v>
       </c>
       <c r="N30">
-        <v>-0</v>
+        <v>0.1314760508308895</v>
       </c>
       <c r="O30">
-        <v>-0</v>
+        <v>-0.4451185879757307</v>
       </c>
       <c r="P30">
-        <v>-0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q30">
-        <v>-0</v>
+        <v>0.1272401433691756</v>
       </c>
       <c r="R30">
-        <v>-0</v>
+        <v>-0.4307777164920021</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>2.599999999999994</v>
+      </c>
+      <c r="T30">
+        <v>0.03221809169764554</v>
       </c>
       <c r="U30">
-        <v>5.88</v>
+        <v>846.5</v>
       </c>
       <c r="V30">
-        <v>0.8609077598828697</v>
+        <v>1.379113717823395</v>
       </c>
       <c r="W30">
-        <v>0.01961471103327496</v>
+        <v>-0.0594543188824031</v>
       </c>
       <c r="X30">
-        <v>0.09014671505484201</v>
+        <v>0.08682042926236397</v>
       </c>
       <c r="Y30">
-        <v>-0.07053200402156705</v>
+        <v>-0.1462747481447671</v>
       </c>
       <c r="Z30">
-        <v>0.03100711521406154</v>
+        <v>0.06826602303138266</v>
       </c>
       <c r="AA30">
-        <v>0.0001594327679018972</v>
+        <v>1.454800661400454e-05</v>
       </c>
       <c r="AB30">
-        <v>0.06167870272574415</v>
+        <v>0.05351474308522295</v>
       </c>
       <c r="AC30">
-        <v>-0.06151926995784226</v>
+        <v>-0.05350019507860895</v>
       </c>
       <c r="AD30">
-        <v>30.1</v>
+        <v>1956</v>
       </c>
       <c r="AE30">
-        <v>0.01406952366917688</v>
+        <v>0.07322361797018295</v>
       </c>
       <c r="AF30">
-        <v>30.11406952366918</v>
+        <v>1956.07322361797</v>
       </c>
       <c r="AG30">
-        <v>24.23406952366918</v>
+        <v>1109.57322361797</v>
       </c>
       <c r="AH30">
-        <v>0.8151259434041456</v>
+        <v>0.7611555331372074</v>
       </c>
       <c r="AI30">
-        <v>0.3417623279285716</v>
+        <v>0.3803611737636005</v>
       </c>
       <c r="AJ30">
-        <v>0.7801318338282787</v>
+        <v>0.6438380313746452</v>
       </c>
       <c r="AK30">
-        <v>0.2946962209707251</v>
+        <v>0.2582701315482704</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -4073,10 +4214,10 @@
         <v>0</v>
       </c>
       <c r="AN30">
-        <v>2006.666666666667</v>
+        <v>25402.5974025974</v>
       </c>
       <c r="AP30">
-        <v>1615.604634911279</v>
+        <v>14410.04186516844</v>
       </c>
     </row>
     <row r="31">
@@ -4087,7 +4228,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>China Everbright Limited (SEHK:165)</t>
+          <t>VCREDIT Holdings Limited (SEHK:2003)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4096,118 +4237,106 @@
         </is>
       </c>
       <c r="D31">
-        <v>-0.407</v>
+        <v>0.188</v>
       </c>
       <c r="G31">
-        <v>10.76017130620985</v>
+        <v>0.03930817610062893</v>
       </c>
       <c r="H31">
-        <v>10.76017130620985</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>-1.693790149892933</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>-1.693790149892933</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>-226</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L31">
-        <v>-4.839400428265525</v>
+        <v>0.1831761006289308</v>
       </c>
       <c r="M31">
-        <v>135.9</v>
+        <v>14.928</v>
       </c>
       <c r="N31">
-        <v>0.1082264872182846</v>
+        <v>0.1047578947368421</v>
       </c>
       <c r="O31">
-        <v>-0.6013274336283186</v>
+        <v>0.2135622317596566</v>
       </c>
       <c r="P31">
-        <v>135.9</v>
+        <v>14.5</v>
       </c>
       <c r="Q31">
-        <v>0.1082264872182846</v>
+        <v>0.1017543859649123</v>
       </c>
       <c r="R31">
-        <v>-0.6013274336283186</v>
+        <v>0.2074391988555079</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>0.4280000000000008</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>0.02867095391211152</v>
       </c>
       <c r="U31">
-        <v>1319.4</v>
+        <v>173.9</v>
       </c>
       <c r="V31">
-        <v>1.050728677231823</v>
+        <v>1.220350877192983</v>
       </c>
       <c r="W31">
-        <v>-0.03579290793620626</v>
+        <v>0.1281393217231897</v>
       </c>
       <c r="X31">
-        <v>0.08371487560484642</v>
+        <v>0.09258316346666851</v>
       </c>
       <c r="Y31">
-        <v>-0.1195077835410527</v>
+        <v>0.03555615825652123</v>
       </c>
       <c r="Z31">
-        <v>0.004818854412811755</v>
+        <v>0.3316818774445893</v>
       </c>
       <c r="AA31">
-        <v>-0.008162128138188646</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.05371325642863657</v>
+        <v>0.05357072334684498</v>
       </c>
       <c r="AC31">
-        <v>-0.06187538456682522</v>
+        <v>-0.05357072334684498</v>
       </c>
       <c r="AD31">
-        <v>4654.6</v>
+        <v>529.1</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>4654.6</v>
+        <v>529.1</v>
       </c>
       <c r="AG31">
-        <v>3335.2</v>
+        <v>355.2</v>
       </c>
       <c r="AH31">
-        <v>0.7875403955805966</v>
+        <v>0.7878201310303752</v>
       </c>
       <c r="AI31">
-        <v>0.4462532597024083</v>
+        <v>0.4843907351460221</v>
       </c>
       <c r="AJ31">
-        <v>0.7264806464963297</v>
+        <v>0.7136829415310428</v>
       </c>
       <c r="AK31">
-        <v>0.3660630007683021</v>
+        <v>0.3867595818815331</v>
       </c>
       <c r="AL31">
-        <v>120.1</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>120.1</v>
-      </c>
-      <c r="AN31">
-        <v>-61.08398950131234</v>
-      </c>
-      <c r="AO31">
-        <v>-0.6586178184845961</v>
-      </c>
-      <c r="AP31">
-        <v>-43.76902887139108</v>
-      </c>
-      <c r="AQ31">
-        <v>-0.6586178184845961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4218,7 +4347,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lerado Financial Group Company Limited (SEHK:1225)</t>
+          <t>Allied Group Limited (SEHK:373)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4227,115 +4356,106 @@
         </is>
       </c>
       <c r="D32">
-        <v>-0.0204</v>
+        <v>0.144</v>
       </c>
       <c r="G32">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>-0.01472</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>-0.01472</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>-20.2</v>
+        <v>-99.40000000000001</v>
       </c>
       <c r="L32">
-        <v>-0.8079999999999999</v>
+        <v>-0.08815964523281597</v>
       </c>
       <c r="M32">
-        <v>-0</v>
+        <v>56.1</v>
       </c>
       <c r="N32">
-        <v>-0</v>
+        <v>0.07607811228641172</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>-0.5643863179074446</v>
       </c>
       <c r="P32">
-        <v>-0</v>
+        <v>56.1</v>
       </c>
       <c r="Q32">
-        <v>-0</v>
+        <v>0.07607811228641172</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>-0.5643863179074446</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
       <c r="U32">
-        <v>20</v>
+        <v>1788.2</v>
       </c>
       <c r="V32">
-        <v>3.5650623885918</v>
+        <v>2.425006780580418</v>
       </c>
       <c r="W32">
-        <v>-0.1416549789621318</v>
+        <v>-0.01760226669027802</v>
       </c>
       <c r="X32">
-        <v>0.2154626832364991</v>
+        <v>0.09740657785283421</v>
       </c>
       <c r="Y32">
-        <v>-0.3571176621986309</v>
+        <v>-0.1150088445431122</v>
       </c>
       <c r="Z32">
-        <v>0.1137915339098771</v>
+        <v>0.1410732830349211</v>
       </c>
       <c r="AA32">
-        <v>-0.001675011379153391</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.06060799889205788</v>
+        <v>0.05360879080091502</v>
       </c>
       <c r="AC32">
-        <v>-0.06228301027121127</v>
+        <v>-0.05360879080091502</v>
       </c>
       <c r="AD32">
-        <v>101.5</v>
+        <v>3062.7</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>101.5</v>
+        <v>3062.7</v>
       </c>
       <c r="AG32">
-        <v>81.5</v>
+        <v>1274.5</v>
       </c>
       <c r="AH32">
-        <v>0.9476239380076557</v>
+        <v>0.8059524749348701</v>
       </c>
       <c r="AI32">
-        <v>0.4527207850133809</v>
+        <v>0.2661828611159395</v>
       </c>
       <c r="AJ32">
-        <v>0.9355986683503617</v>
+        <v>0.6334807893036434</v>
       </c>
       <c r="AK32">
-        <v>0.3991185112634672</v>
+        <v>0.1311510835785877</v>
       </c>
       <c r="AL32">
-        <v>6.88</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>6.795</v>
-      </c>
-      <c r="AN32">
-        <v>2360.46511627907</v>
-      </c>
-      <c r="AO32">
-        <v>-0.05348837209302326</v>
-      </c>
-      <c r="AP32">
-        <v>1895.348837209302</v>
-      </c>
-      <c r="AQ32">
-        <v>-0.05415746872700515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4346,7 +4466,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Far East Horizon Limited (SEHK:3360)</t>
+          <t>Zhong Ji Longevity Science Group Limited (SEHK:767)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4355,10 +4475,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.165</v>
-      </c>
-      <c r="E33">
-        <v>0.142</v>
+        <v>-0.118</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4373,85 +4490,82 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>913.1</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="L33">
-        <v>0.184841798416972</v>
+        <v>-0.05639344262295082</v>
       </c>
       <c r="M33">
-        <v>1082.8</v>
+        <v>-0</v>
       </c>
       <c r="N33">
-        <v>0.3207250970054205</v>
+        <v>-0</v>
       </c>
       <c r="O33">
-        <v>1.185850399737159</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>278.2</v>
+        <v>-0</v>
       </c>
       <c r="Q33">
-        <v>0.0824027724297266</v>
+        <v>-0</v>
       </c>
       <c r="R33">
-        <v>0.304676377176651</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>804.5999999999999</v>
-      </c>
-      <c r="T33">
-        <v>0.7430735131141485</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2052.8</v>
+        <v>7.49</v>
       </c>
       <c r="V33">
-        <v>0.6080388614081337</v>
+        <v>0.951715374841169</v>
       </c>
       <c r="W33">
-        <v>0.1294497923075833</v>
+        <v>-0.01278810408921933</v>
       </c>
       <c r="X33">
-        <v>0.1563947875416113</v>
+        <v>0.05605003401142138</v>
       </c>
       <c r="Y33">
-        <v>-0.02694499523402807</v>
+        <v>-0.06883813810064071</v>
       </c>
       <c r="Z33">
-        <v>0.1204824272578718</v>
+        <v>0.2234432234432235</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.06483917756479511</v>
+        <v>0.05382162257023641</v>
       </c>
       <c r="AC33">
-        <v>-0.06483917756479511</v>
+        <v>-0.05382162257023641</v>
       </c>
       <c r="AD33">
-        <v>39307.6</v>
+        <v>2.97</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>39307.6</v>
+        <v>2.97</v>
       </c>
       <c r="AG33">
-        <v>37254.8</v>
+        <v>-4.52</v>
       </c>
       <c r="AH33">
-        <v>0.9209042327633266</v>
+        <v>0.2739852398523985</v>
       </c>
       <c r="AI33">
-        <v>0.841864937857536</v>
+        <v>0.05259429785726935</v>
       </c>
       <c r="AJ33">
-        <v>0.9169080675052731</v>
+        <v>-1.349253731343283</v>
       </c>
       <c r="AK33">
-        <v>0.8345927152243701</v>
+        <v>-0.09228256431196405</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -4468,7 +4582,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kingkey Financial International (Holdings) Limited (SEHK:1468)</t>
+          <t>Gome Finance Technology Co., Ltd. (SEHK:628)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4477,34 +4591,34 @@
         </is>
       </c>
       <c r="D34">
-        <v>-0.00044</v>
+        <v>0.0213</v>
       </c>
       <c r="G34">
-        <v>-0.08235294117647059</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>-0.08235294117647059</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>-0.128921568627451</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>-0.128921568627451</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>-7.29</v>
+        <v>-1.46</v>
       </c>
       <c r="L34">
-        <v>-0.3573529411764706</v>
+        <v>-0.1506707946336429</v>
       </c>
       <c r="M34">
-        <v>0.59</v>
+        <v>-0</v>
       </c>
       <c r="N34">
-        <v>0.0007436349886564154</v>
+        <v>-0</v>
       </c>
       <c r="O34">
-        <v>-0.08093278463648834</v>
+        <v>0</v>
       </c>
       <c r="P34">
         <v>-0</v>
@@ -4516,79 +4630,64 @@
         <v>0</v>
       </c>
       <c r="S34">
-        <v>0.59</v>
-      </c>
-      <c r="T34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>17.8</v>
+        <v>30.4</v>
       </c>
       <c r="V34">
-        <v>0.0224350894882783</v>
+        <v>0.3318777292576419</v>
       </c>
       <c r="W34">
-        <v>-0.06597285067873303</v>
+        <v>-0.006124161073825503</v>
       </c>
       <c r="X34">
-        <v>0.0501648727239653</v>
+        <v>0.0554440319814743</v>
       </c>
       <c r="Y34">
-        <v>-0.1161377234026983</v>
+        <v>-0.0615681930552998</v>
       </c>
       <c r="Z34">
-        <v>0.184115523465704</v>
+        <v>0.02877932877932877</v>
       </c>
       <c r="AA34">
-        <v>-0.02373646209386282</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.05037502783538275</v>
+        <v>0.05415326457833942</v>
       </c>
       <c r="AC34">
-        <v>-0.07411148992924557</v>
+        <v>-0.05415326457833942</v>
       </c>
       <c r="AD34">
-        <v>34.4</v>
+        <v>29.5</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>34.4</v>
+        <v>29.5</v>
       </c>
       <c r="AG34">
-        <v>16.6</v>
+        <v>-0.8999999999999986</v>
       </c>
       <c r="AH34">
-        <v>0.04155593138439236</v>
+        <v>0.2436003303055326</v>
       </c>
       <c r="AI34">
-        <v>0.2273628552544613</v>
+        <v>0.1140316969462698</v>
       </c>
       <c r="AJ34">
-        <v>0.02049382716049383</v>
+        <v>-0.009922822491730966</v>
       </c>
       <c r="AK34">
-        <v>0.1243445692883895</v>
+        <v>-0.00394218134034165</v>
       </c>
       <c r="AL34">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>1.281</v>
-      </c>
-      <c r="AN34">
-        <v>-18.01047120418848</v>
-      </c>
-      <c r="AO34">
-        <v>-1.502857142857143</v>
-      </c>
-      <c r="AP34">
-        <v>-8.69109947643979</v>
-      </c>
-      <c r="AQ34">
-        <v>-2.053083528493364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4599,7 +4698,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capital Industrial Financial Services Group Limited (SEHK:730)</t>
+          <t>China Rongzhong Financial Holdings Company Limited (SEHK:3963)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4608,7 +4707,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>0.715</v>
+        <v>-0.194</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4623,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>3.21</v>
+        <v>-13.1</v>
       </c>
       <c r="L35">
-        <v>0.02820738137082601</v>
+        <v>-1.468609865470852</v>
       </c>
       <c r="M35">
         <v>-0</v>
@@ -4635,7 +4734,7 @@
         <v>-0</v>
       </c>
       <c r="O35">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P35">
         <v>-0</v>
@@ -4644,61 +4743,61 @@
         <v>-0</v>
       </c>
       <c r="R35">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="U35">
-        <v>58.5</v>
+        <v>1.95</v>
       </c>
       <c r="V35">
-        <v>0.8810240963855421</v>
+        <v>0.06132075471698113</v>
       </c>
       <c r="W35">
-        <v>0.01712913553895411</v>
+        <v>0.1568862275449102</v>
       </c>
       <c r="X35">
-        <v>0.055367486657525</v>
+        <v>0.05563646987736311</v>
       </c>
       <c r="Y35">
-        <v>-0.03823835111857089</v>
+        <v>0.1012497576675471</v>
       </c>
       <c r="Z35">
-        <v>0.6070304582066464</v>
+        <v>1.101234567901234</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.0856330977327877</v>
+        <v>0.05424434798284396</v>
       </c>
       <c r="AC35">
-        <v>-0.0856330977327877</v>
+        <v>-0.05424434798284396</v>
       </c>
       <c r="AD35">
-        <v>40.6</v>
+        <v>10.8</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>40.6</v>
+        <v>10.8</v>
       </c>
       <c r="AG35">
-        <v>-17.9</v>
+        <v>8.850000000000001</v>
       </c>
       <c r="AH35">
-        <v>0.3794392523364486</v>
+        <v>0.2535211267605634</v>
       </c>
       <c r="AI35">
-        <v>0.1483918128654971</v>
+        <v>1.320293398533007</v>
       </c>
       <c r="AJ35">
-        <v>-0.3690721649484535</v>
+        <v>0.2177121771217712</v>
       </c>
       <c r="AK35">
-        <v>-0.08321710832171082</v>
+        <v>1.420545746388443</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -4715,7 +4814,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>China Ever Grand Financial Leasing Group Co., Ltd. (SEHK:379)</t>
+          <t>China Properties Investment Holdings Limited (SEHK:736)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4723,26 +4822,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D36">
-        <v>-0.09789999999999999</v>
-      </c>
-      <c r="G36">
-        <v>-0.5633540372670807</v>
-      </c>
-      <c r="H36">
-        <v>-0.5633540372670807</v>
-      </c>
-      <c r="I36">
-        <v>-0.4770186335403726</v>
-      </c>
-      <c r="J36">
-        <v>-0.4770186335403726</v>
-      </c>
       <c r="K36">
-        <v>-6.97</v>
-      </c>
-      <c r="L36">
-        <v>-0.432919254658385</v>
+        <v>-13.3</v>
       </c>
       <c r="M36">
         <v>-0</v>
@@ -4766,73 +4847,61 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>0.161</v>
       </c>
       <c r="V36">
-        <v>0.1220338983050847</v>
+        <v>0.01811023622047244</v>
       </c>
       <c r="W36">
-        <v>-0.1011611030478955</v>
+        <v>-0.1672955974842767</v>
       </c>
       <c r="X36">
-        <v>0.06917057643095924</v>
+        <v>0.0686719729852954</v>
       </c>
       <c r="Y36">
-        <v>-0.1703316794788547</v>
+        <v>-0.2359675704695721</v>
       </c>
       <c r="Z36">
-        <v>0.1357504215851602</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>-0.06475548060708262</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>0.05969466550670617</v>
+        <v>0.0561209897972871</v>
       </c>
       <c r="AC36">
-        <v>-0.1244501461137888</v>
+        <v>-0.0561209897972871</v>
       </c>
       <c r="AD36">
-        <v>50</v>
+        <v>13.6</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>50</v>
+        <v>13.6</v>
       </c>
       <c r="AG36">
-        <v>47.12</v>
+        <v>13.439</v>
       </c>
       <c r="AH36">
-        <v>0.6793478260869565</v>
+        <v>0.6047132058692751</v>
       </c>
       <c r="AI36">
-        <v>0.4668534080298786</v>
+        <v>0.1752577319587629</v>
       </c>
       <c r="AJ36">
-        <v>0.666289592760181</v>
+        <v>0.6018630480541001</v>
       </c>
       <c r="AK36">
-        <v>0.4521205142966801</v>
+        <v>0.1735430467852116</v>
       </c>
       <c r="AL36">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AM36">
-        <v>-0.333</v>
-      </c>
-      <c r="AN36">
-        <v>-6.544502617801047</v>
-      </c>
-      <c r="AO36">
-        <v>-1536</v>
-      </c>
-      <c r="AP36">
-        <v>-6.167539267015707</v>
-      </c>
-      <c r="AQ36">
-        <v>23.06306306306306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4843,7 +4912,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>China Smartpay Group Holdings Limited (SEHK:8325)</t>
+          <t>Styland Holdings Limited (SEHK:211)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4852,25 +4921,25 @@
         </is>
       </c>
       <c r="D37">
-        <v>-0.102</v>
+        <v>-0.305</v>
       </c>
       <c r="G37">
-        <v>-0.1889150943396226</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>-0.1889150943396226</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>-0.1011218111799636</v>
+        <v>0.007866495826815102</v>
       </c>
       <c r="J37">
-        <v>-0.1011218111799636</v>
+        <v>0.007866495826815102</v>
       </c>
       <c r="K37">
-        <v>-3.36</v>
+        <v>-9.01</v>
       </c>
       <c r="L37">
-        <v>-0.07924528301886792</v>
+        <v>-6.723880597014925</v>
       </c>
       <c r="M37">
         <v>-0</v>
@@ -4894,73 +4963,67 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>2</v>
+        <v>4.47</v>
       </c>
       <c r="V37">
-        <v>0.1290322580645161</v>
+        <v>0.2829113924050632</v>
       </c>
       <c r="W37">
-        <v>-0.16</v>
+        <v>-0.1553448275862069</v>
       </c>
       <c r="X37">
-        <v>0.06524962907330287</v>
+        <v>0.07376094115239915</v>
       </c>
       <c r="Y37">
-        <v>-0.2252496290733029</v>
+        <v>-0.229105768738606</v>
       </c>
       <c r="Z37">
-        <v>0.7530705746212204</v>
+        <v>0.01629530111626817</v>
       </c>
       <c r="AA37">
-        <v>-0.07615186045203372</v>
+        <v>0.0001281869182278191</v>
       </c>
       <c r="AB37">
-        <v>0.05695539872026534</v>
+        <v>0.05654742163477704</v>
       </c>
       <c r="AC37">
-        <v>-0.1331072591722991</v>
+        <v>-0.05641923471654922</v>
       </c>
       <c r="AD37">
-        <v>26.2</v>
+        <v>31.5</v>
       </c>
       <c r="AE37">
-        <v>0.002823970152276329</v>
+        <v>0.01229447796033881</v>
       </c>
       <c r="AF37">
-        <v>26.20282397015228</v>
+        <v>31.51229447796034</v>
       </c>
       <c r="AG37">
-        <v>24.20282397015228</v>
+        <v>27.04229447796034</v>
       </c>
       <c r="AH37">
-        <v>0.6283225325197707</v>
+        <v>0.6660487474907781</v>
       </c>
       <c r="AI37">
-        <v>0.6150489927266346</v>
+        <v>0.3909117670205492</v>
       </c>
       <c r="AJ37">
-        <v>0.6095995586698677</v>
+        <v>0.6312055600073404</v>
       </c>
       <c r="AK37">
-        <v>0.5960872078243653</v>
+        <v>0.355154709525963</v>
       </c>
       <c r="AL37">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AM37">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AN37">
-        <v>-7.203739345614517</v>
-      </c>
-      <c r="AO37">
-        <v>-1.397394136807818</v>
+        <v>2423.076923076923</v>
       </c>
       <c r="AP37">
-        <v>-6.654612034685806</v>
-      </c>
-      <c r="AQ37">
-        <v>-2.166666666666667</v>
+        <v>2080.176498304641</v>
       </c>
     </row>
     <row r="38">
@@ -4971,7 +5034,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Finet Group Limited (SEHK:8317)</t>
+          <t>CSSC (Hong Kong) Shipping Company Limited (SEHK:3877)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4979,116 +5042,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D38">
-        <v>0.202</v>
-      </c>
       <c r="G38">
-        <v>-1.269387755102041</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>-1.269387755102041</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>0.198</v>
+        <v>242.1</v>
       </c>
       <c r="L38">
-        <v>0.08081632653061224</v>
+        <v>0.7358662613981762</v>
       </c>
       <c r="M38">
-        <v>-0</v>
+        <v>70.5</v>
       </c>
       <c r="N38">
-        <v>-0</v>
+        <v>0.06063472950890169</v>
       </c>
       <c r="O38">
-        <v>-0</v>
+        <v>0.2912019826517968</v>
       </c>
       <c r="P38">
-        <v>-0</v>
+        <v>70.5</v>
       </c>
       <c r="Q38">
-        <v>-0</v>
+        <v>0.06063472950890169</v>
       </c>
       <c r="R38">
-        <v>-0</v>
+        <v>0.2912019826517968</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
       <c r="U38">
-        <v>1.37</v>
+        <v>143.4</v>
       </c>
       <c r="V38">
-        <v>0.04335443037974684</v>
+        <v>0.1233336200223617</v>
       </c>
       <c r="W38">
-        <v>0.04016227180527384</v>
+        <v>0.1747509744478129</v>
       </c>
       <c r="X38">
-        <v>0.0503126477332142</v>
+        <v>0.08482603873445932</v>
       </c>
       <c r="Y38">
-        <v>-0.01015037592794036</v>
+        <v>0.08992493571335358</v>
       </c>
       <c r="Z38">
-        <v>0.2428146679881071</v>
+        <v>0.06643377824445207</v>
       </c>
       <c r="AA38">
-        <v>-0.2081268582755203</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>0.05041015099176915</v>
+        <v>0.05713314095420147</v>
       </c>
       <c r="AC38">
-        <v>-0.2585370092672895</v>
+        <v>-0.05713314095420147</v>
       </c>
       <c r="AD38">
-        <v>1.88</v>
+        <v>3493.6</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.88</v>
+        <v>3493.6</v>
       </c>
       <c r="AG38">
-        <v>0.5099999999999998</v>
+        <v>3350.2</v>
       </c>
       <c r="AH38">
-        <v>0.05615292712066905</v>
+        <v>0.7502952988424285</v>
       </c>
       <c r="AI38">
-        <v>0.29375</v>
+        <v>0.6909673463736872</v>
       </c>
       <c r="AJ38">
-        <v>0.01588290252257863</v>
+        <v>0.7423607879633939</v>
       </c>
       <c r="AK38">
-        <v>0.1013916500994036</v>
+        <v>0.6819467909703422</v>
       </c>
       <c r="AL38">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AM38">
-        <v>0.08</v>
-      </c>
-      <c r="AN38">
-        <v>-0.9353233830845772</v>
-      </c>
-      <c r="AO38">
-        <v>-26.25</v>
-      </c>
-      <c r="AP38">
-        <v>-0.253731343283582</v>
-      </c>
-      <c r="AQ38">
-        <v>-26.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -5099,7 +5150,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>China Success Finance Group Holdings Limited (SEHK:3623)</t>
+          <t>Hong Kong Finance Group Limited (SEHK:1273)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5108,115 +5159,109 @@
         </is>
       </c>
       <c r="D39">
-        <v>-0.0178</v>
+        <v>0.0403</v>
+      </c>
+      <c r="E39">
+        <v>-0.00473</v>
       </c>
       <c r="G39">
-        <v>-0.5590909090909092</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>-0.5776859504132231</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>-1.975206611570248</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>-1.975206611570248</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>-21.2</v>
+        <v>6.71</v>
       </c>
       <c r="L39">
-        <v>-1.752066115702479</v>
+        <v>0.4042168674698795</v>
       </c>
       <c r="M39">
-        <v>-0</v>
+        <v>1.38</v>
       </c>
       <c r="N39">
-        <v>-0</v>
+        <v>0.07624309392265192</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>0.2056631892697466</v>
       </c>
       <c r="P39">
-        <v>-0</v>
+        <v>1.38</v>
       </c>
       <c r="Q39">
-        <v>-0</v>
+        <v>0.07624309392265192</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>0.2056631892697466</v>
       </c>
       <c r="S39">
         <v>0</v>
       </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
       <c r="U39">
-        <v>5.13</v>
+        <v>5.33</v>
       </c>
       <c r="V39">
-        <v>0.09063604240282686</v>
+        <v>0.294475138121547</v>
       </c>
       <c r="W39">
-        <v>-0.2742561448900388</v>
+        <v>0.06946169772256729</v>
       </c>
       <c r="X39">
-        <v>0.05462192071176206</v>
+        <v>0.07418480424391086</v>
       </c>
       <c r="Y39">
-        <v>-0.3288780656018009</v>
+        <v>-0.00472310652134357</v>
       </c>
       <c r="Z39">
-        <v>0.1235198040016333</v>
+        <v>0.1192528735632184</v>
       </c>
       <c r="AA39">
-        <v>-0.2439771335238873</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>0.05482981268821586</v>
+        <v>0.05807090749183551</v>
       </c>
       <c r="AC39">
-        <v>-0.2988069462121032</v>
+        <v>-0.05807090749183551</v>
       </c>
       <c r="AD39">
-        <v>30</v>
+        <v>36.8</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>30</v>
+        <v>36.8</v>
       </c>
       <c r="AG39">
-        <v>24.87</v>
+        <v>31.47</v>
       </c>
       <c r="AH39">
-        <v>0.3464203233256351</v>
+        <v>0.6703096539162112</v>
       </c>
       <c r="AI39">
-        <v>0.3640776699029126</v>
+        <v>0.2647482014388489</v>
       </c>
       <c r="AJ39">
-        <v>0.3052657419909169</v>
+        <v>0.6348597942303813</v>
       </c>
       <c r="AK39">
-        <v>0.3218584185324188</v>
+        <v>0.2354305378918231</v>
       </c>
       <c r="AL39">
-        <v>0.997</v>
+        <v>0</v>
       </c>
       <c r="AM39">
-        <v>0.997</v>
-      </c>
-      <c r="AN39">
-        <v>-1.310043668122271</v>
-      </c>
-      <c r="AO39">
-        <v>-23.97191574724172</v>
-      </c>
-      <c r="AP39">
-        <v>-1.086026200873363</v>
-      </c>
-      <c r="AQ39">
-        <v>-23.97191574724172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -5227,7 +5272,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Greater China Financial Holdings Limited (SEHK:431)</t>
+          <t>Aceso Life Science Group Limited (SEHK:474)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5236,34 +5281,34 @@
         </is>
       </c>
       <c r="D40">
-        <v>0.162</v>
+        <v>-0.0248</v>
       </c>
       <c r="G40">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>-0.5822368421052632</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>-0.5822368421052632</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>-23.4</v>
+        <v>-53.6</v>
       </c>
       <c r="L40">
-        <v>-0.7697368421052632</v>
+        <v>-2.118577075098814</v>
       </c>
       <c r="M40">
-        <v>-0</v>
+        <v>1.02</v>
       </c>
       <c r="N40">
-        <v>-0</v>
+        <v>0.009640831758034027</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>-0.01902985074626866</v>
       </c>
       <c r="P40">
         <v>-0</v>
@@ -5275,76 +5320,67 @@
         <v>0</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
       </c>
       <c r="U40">
-        <v>5.18</v>
+        <v>16.6</v>
       </c>
       <c r="V40">
-        <v>0.03936170212765958</v>
+        <v>0.1568998109640832</v>
       </c>
       <c r="W40">
-        <v>-0.6964285714285714</v>
+        <v>-0.25</v>
       </c>
       <c r="X40">
-        <v>0.05384580207513867</v>
+        <v>0.08920491581988375</v>
       </c>
       <c r="Y40">
-        <v>-0.7502743735037101</v>
+        <v>-0.3392049158198838</v>
       </c>
       <c r="Z40">
-        <v>0.9145607701564379</v>
+        <v>0.04796208530805687</v>
       </c>
       <c r="AA40">
-        <v>-0.5324909747292418</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>0.05131131617426461</v>
+        <v>0.05901335884948097</v>
       </c>
       <c r="AC40">
-        <v>-0.5838022909035064</v>
+        <v>-0.05901335884948097</v>
       </c>
       <c r="AD40">
-        <v>58.6</v>
+        <v>360.2</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>58.6</v>
+        <v>360.2</v>
       </c>
       <c r="AG40">
-        <v>53.42</v>
+        <v>343.6</v>
       </c>
       <c r="AH40">
-        <v>0.3080967402733965</v>
+        <v>0.7729613733905579</v>
       </c>
       <c r="AI40">
-        <v>0.6362649294245386</v>
+        <v>0.5581035017043694</v>
       </c>
       <c r="AJ40">
-        <v>0.2887255431845206</v>
+        <v>0.7645749888740543</v>
       </c>
       <c r="AK40">
-        <v>0.6145881270133456</v>
+        <v>0.5464376590330788</v>
       </c>
       <c r="AL40">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AM40">
-        <v>-0.05999999999999961</v>
-      </c>
-      <c r="AN40">
-        <v>-3.573170731707318</v>
-      </c>
-      <c r="AO40">
-        <v>-4.254807692307692</v>
-      </c>
-      <c r="AP40">
-        <v>-3.257317073170732</v>
-      </c>
-      <c r="AQ40">
-        <v>295.0000000000019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -5355,7 +5391,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Metalpha Technology Holding Limited (NasdaqCM:MATH)</t>
+          <t>Alliance International Education Leasing Holdings Limited (SEHK:1563)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5363,26 +5399,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D41">
-        <v>-0.108</v>
-      </c>
       <c r="G41">
-        <v>-6.157635467980296</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>-6.157635467980296</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>-6.124579860655265</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>-6.124579860655265</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>-14.4</v>
+        <v>27.2</v>
       </c>
       <c r="L41">
-        <v>-7.093596059113302</v>
+        <v>0.3285024154589372</v>
       </c>
       <c r="M41">
         <v>-0</v>
@@ -5391,7 +5424,7 @@
         <v>-0</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P41">
         <v>-0</v>
@@ -5400,73 +5433,67 @@
         <v>-0</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S41">
         <v>0</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>34.2</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>0.1410891089108911</v>
+      </c>
+      <c r="W41">
+        <v>0.1379310344827586</v>
       </c>
       <c r="X41">
-        <v>0.04994663712715092</v>
+        <v>0.05324063374650796</v>
+      </c>
+      <c r="Y41">
+        <v>0.08469040073625067</v>
       </c>
       <c r="Z41">
-        <v>7.532870431999445</v>
+        <v>0.3205574912891986</v>
       </c>
       <c r="AA41">
-        <v>-46.13566654074933</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>0.05022840827314789</v>
+        <v>0.05924391459185307</v>
       </c>
       <c r="AC41">
-        <v>-46.18589494902248</v>
+        <v>-0.05924391459185307</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="AE41">
-        <v>0.2694855856509373</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>0.2694855856509373</v>
+        <v>29.3</v>
       </c>
       <c r="AG41">
-        <v>0.2694855856509373</v>
+        <v>-4.900000000000002</v>
       </c>
       <c r="AH41">
-        <v>0.0191539046691073</v>
+        <v>0.1078395288921605</v>
       </c>
       <c r="AI41">
-        <v>1</v>
+        <v>0.06992840095465394</v>
       </c>
       <c r="AJ41">
-        <v>0.0191539046691073</v>
+        <v>-0.02063157894736843</v>
       </c>
       <c r="AK41">
-        <v>1</v>
+        <v>-0.01273388773388774</v>
       </c>
       <c r="AL41">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM41">
-        <v>1.762</v>
-      </c>
-      <c r="AN41">
-        <v>-0</v>
-      </c>
-      <c r="AO41">
-        <v>-6.345177664974619</v>
-      </c>
-      <c r="AP41">
-        <v>-0.02176957635115416</v>
-      </c>
-      <c r="AQ41">
-        <v>-7.094211123723042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -5477,7 +5504,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BC Technology Group Limited (SEHK:863)</t>
+          <t>Far East Horizon Limited (SEHK:3360)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5486,106 +5513,109 @@
         </is>
       </c>
       <c r="D42">
-        <v>0.0189</v>
+        <v>0.132</v>
+      </c>
+      <c r="E42">
+        <v>0.0998</v>
       </c>
       <c r="G42">
-        <v>-1.336666666666667</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>-1.336666666666667</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>-2.253333333333333</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>-2.253333333333333</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>-66.8</v>
+        <v>901.7</v>
       </c>
       <c r="L42">
-        <v>-2.226666666666667</v>
+        <v>0.1861439689519209</v>
       </c>
       <c r="M42">
-        <v>-0</v>
+        <v>714.9000000000001</v>
       </c>
       <c r="N42">
-        <v>-0</v>
+        <v>0.210785469984668</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>0.792835754685594</v>
       </c>
       <c r="P42">
-        <v>-0</v>
+        <v>272.1</v>
       </c>
       <c r="Q42">
-        <v>-0</v>
+        <v>0.08022762118174313</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>0.301763335921038</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>442.8000000000001</v>
+      </c>
+      <c r="T42">
+        <v>0.619387326898867</v>
       </c>
       <c r="U42">
-        <v>129.9</v>
+        <v>2948.4</v>
       </c>
       <c r="V42">
-        <v>0.7405929304446979</v>
+        <v>0.8693242127609389</v>
       </c>
       <c r="W42">
-        <v>-0.387695879280325</v>
+        <v>0.1331217243670185</v>
       </c>
       <c r="X42">
-        <v>0.05131851590306034</v>
+        <v>0.1716339817530568</v>
       </c>
       <c r="Y42">
-        <v>-0.4390143951833853</v>
+        <v>-0.03851225738603831</v>
+      </c>
+      <c r="Z42">
+        <v>0.1101620330888624</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>0.05325010480373187</v>
+        <v>0.06135951049172754</v>
+      </c>
+      <c r="AC42">
+        <v>-0.06135951049172754</v>
       </c>
       <c r="AD42">
-        <v>29.7</v>
+        <v>37072.2</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>29.7</v>
+        <v>37072.2</v>
       </c>
       <c r="AG42">
-        <v>-100.2</v>
+        <v>34123.8</v>
       </c>
       <c r="AH42">
-        <v>0.1448074110190151</v>
+        <v>0.9161818712033967</v>
       </c>
       <c r="AI42">
-        <v>0.2069686411149826</v>
+        <v>0.8264400537700328</v>
       </c>
       <c r="AJ42">
-        <v>-1.332446808510638</v>
+        <v>0.9095944598751446</v>
       </c>
       <c r="AK42">
-        <v>-7.367647058823533</v>
+        <v>0.8142297771616324</v>
       </c>
       <c r="AL42">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AM42">
-        <v>2.942</v>
-      </c>
-      <c r="AN42">
-        <v>-0.4541284403669724</v>
-      </c>
-      <c r="AO42">
-        <v>-20.8</v>
-      </c>
-      <c r="AP42">
-        <v>1.532110091743119</v>
-      </c>
-      <c r="AQ42">
-        <v>-22.97756628144119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5596,7 +5626,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Temir Corp. (OTCPK:TMRR)</t>
+          <t>Changyou Alliance Group Limited (SEHK:1039)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5604,23 +5634,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D43">
+        <v>0.383</v>
+      </c>
       <c r="G43">
-        <v>0</v>
+        <v>-0.01139601139601139</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>-0.05726495726495726</v>
       </c>
       <c r="I43">
-        <v>-0.7565579827529731</v>
+        <v>-0.01424501424501425</v>
       </c>
       <c r="J43">
-        <v>-0.7565579827529731</v>
+        <v>-0.01424501424501425</v>
       </c>
       <c r="K43">
-        <v>-0.283</v>
+        <v>-5.09</v>
       </c>
       <c r="L43">
-        <v>-0.9248366013071895</v>
+        <v>-0.145014245014245</v>
       </c>
       <c r="M43">
         <v>-0</v>
@@ -5644,58 +5677,2445 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>0.014</v>
+        <v>3.25</v>
       </c>
       <c r="V43">
-        <v>0.01494130202774813</v>
+        <v>0.1079734219269103</v>
       </c>
       <c r="W43">
-        <v>0.7389033942558746</v>
+        <v>-0.1162100456621005</v>
       </c>
       <c r="X43">
-        <v>0.0537118820574379</v>
+        <v>0.06010383401297366</v>
       </c>
       <c r="Y43">
-        <v>0.6851915121984367</v>
+        <v>-0.1763138796750741</v>
+      </c>
+      <c r="Z43">
+        <v>0.4906346100083869</v>
+      </c>
+      <c r="AA43">
+        <v>-0.00698909700866648</v>
       </c>
       <c r="AB43">
-        <v>0.05416647550852007</v>
+        <v>0.05489070951316735</v>
+      </c>
+      <c r="AC43">
+        <v>-0.06187980652183383</v>
       </c>
       <c r="AD43">
-        <v>0.336</v>
+        <v>22.5</v>
       </c>
       <c r="AE43">
-        <v>0.06753371361204902</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>0.403533713612049</v>
+        <v>22.5</v>
       </c>
       <c r="AG43">
-        <v>0.389533713612049</v>
+        <v>19.25</v>
       </c>
       <c r="AH43">
-        <v>0.3010246661568348</v>
+        <v>0.4277566539923954</v>
       </c>
       <c r="AI43">
-        <v>-1.531633208728082</v>
+        <v>5.769230769230771</v>
       </c>
       <c r="AJ43">
-        <v>0.29364780526488</v>
+        <v>0.3900709219858156</v>
       </c>
       <c r="AK43">
-        <v>-1.40389565407383</v>
+        <v>29.61538461538468</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AM43">
-        <v>0</v>
+        <v>4.465000000000001</v>
       </c>
       <c r="AN43">
-        <v>4.666666666666667</v>
+        <v>-52.32558139534884</v>
+      </c>
+      <c r="AO43">
+        <v>-0.1116071428571428</v>
       </c>
       <c r="AP43">
-        <v>5.410190466834015</v>
+        <v>-44.76744186046512</v>
+      </c>
+      <c r="AQ43">
+        <v>-0.1119820828667413</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>China Everbright Limited (SEHK:165)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K44">
+        <v>-559.7</v>
+      </c>
+      <c r="M44">
+        <v>43.7</v>
+      </c>
+      <c r="N44">
+        <v>0.04384468746864653</v>
+      </c>
+      <c r="O44">
+        <v>-0.07807754154011078</v>
+      </c>
+      <c r="P44">
+        <v>43.7</v>
+      </c>
+      <c r="Q44">
+        <v>0.04384468746864653</v>
+      </c>
+      <c r="R44">
+        <v>-0.07807754154011078</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>1327.9</v>
+      </c>
+      <c r="V44">
+        <v>1.332296578709742</v>
+      </c>
+      <c r="W44">
+        <v>-0.0997113945699423</v>
+      </c>
+      <c r="X44">
+        <v>0.1004419949492286</v>
+      </c>
+      <c r="Y44">
+        <v>-0.2001533895191709</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>-0.05102588172187207</v>
+      </c>
+      <c r="AB44">
+        <v>0.05362958163832419</v>
+      </c>
+      <c r="AC44">
+        <v>-0.1046554633601963</v>
+      </c>
+      <c r="AD44">
+        <v>4415.9</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>4415.9</v>
+      </c>
+      <c r="AG44">
+        <v>3088</v>
+      </c>
+      <c r="AH44">
+        <v>0.8158555962014559</v>
+      </c>
+      <c r="AI44">
+        <v>0.4866809941037086</v>
+      </c>
+      <c r="AJ44">
+        <v>0.7559918721081107</v>
+      </c>
+      <c r="AK44">
+        <v>0.3986779590993595</v>
+      </c>
+      <c r="AL44">
+        <v>178.9</v>
+      </c>
+      <c r="AM44">
+        <v>178.9</v>
+      </c>
+      <c r="AN44">
+        <v>-9.705274725274725</v>
+      </c>
+      <c r="AO44">
+        <v>-2.552263834544438</v>
+      </c>
+      <c r="AP44">
+        <v>-6.786813186813186</v>
+      </c>
+      <c r="AQ44">
+        <v>-2.552263834544438</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>China Success Finance Group Holdings Limited (SEHK:3623)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>-0.0518</v>
+      </c>
+      <c r="G45">
+        <v>-1.873382352941177</v>
+      </c>
+      <c r="H45">
+        <v>-1.897058823529412</v>
+      </c>
+      <c r="I45">
+        <v>-0.9161764705882354</v>
+      </c>
+      <c r="J45">
+        <v>-0.9161764705882354</v>
+      </c>
+      <c r="K45">
+        <v>-5.58</v>
+      </c>
+      <c r="L45">
+        <v>-0.8205882352941177</v>
+      </c>
+      <c r="M45">
+        <v>-0</v>
+      </c>
+      <c r="N45">
+        <v>-0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>-0</v>
+      </c>
+      <c r="Q45">
+        <v>-0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>3.18</v>
+      </c>
+      <c r="V45">
+        <v>0.06611226611226612</v>
+      </c>
+      <c r="W45">
+        <v>-0.1021978021978022</v>
+      </c>
+      <c r="X45">
+        <v>0.05797364290427261</v>
+      </c>
+      <c r="Y45">
+        <v>-0.1601714451020748</v>
+      </c>
+      <c r="Z45">
+        <v>0.08556688058386812</v>
+      </c>
+      <c r="AA45">
+        <v>-0.07839436265257331</v>
+      </c>
+      <c r="AB45">
+        <v>0.05518604818816883</v>
+      </c>
+      <c r="AC45">
+        <v>-0.1335804108407421</v>
+      </c>
+      <c r="AD45">
+        <v>26.6</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>26.6</v>
+      </c>
+      <c r="AG45">
+        <v>23.42</v>
+      </c>
+      <c r="AH45">
+        <v>0.356091030789826</v>
+      </c>
+      <c r="AI45">
+        <v>0.3906020558002937</v>
+      </c>
+      <c r="AJ45">
+        <v>0.3274608501118568</v>
+      </c>
+      <c r="AK45">
+        <v>0.3607516943930992</v>
+      </c>
+      <c r="AL45">
+        <v>1.06</v>
+      </c>
+      <c r="AM45">
+        <v>1.06</v>
+      </c>
+      <c r="AN45">
+        <v>-4.845173041894354</v>
+      </c>
+      <c r="AO45">
+        <v>-5.877358490566038</v>
+      </c>
+      <c r="AP45">
+        <v>-4.265938069216758</v>
+      </c>
+      <c r="AQ45">
+        <v>-5.877358490566038</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>eprint Group Limited (SEHK:1884)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>-0.0499</v>
+      </c>
+      <c r="G46">
+        <v>0.01755555555555555</v>
+      </c>
+      <c r="H46">
+        <v>0.01755555555555555</v>
+      </c>
+      <c r="I46">
+        <v>-0.04469135802469136</v>
+      </c>
+      <c r="J46">
+        <v>-0.04469135802469136</v>
+      </c>
+      <c r="K46">
+        <v>-3.1</v>
+      </c>
+      <c r="L46">
+        <v>-0.07654320987654321</v>
+      </c>
+      <c r="M46">
+        <v>0.632</v>
+      </c>
+      <c r="N46">
+        <v>0.02846846846846847</v>
+      </c>
+      <c r="O46">
+        <v>-0.2038709677419355</v>
+      </c>
+      <c r="P46">
+        <v>0.632</v>
+      </c>
+      <c r="Q46">
+        <v>0.02846846846846847</v>
+      </c>
+      <c r="R46">
+        <v>-0.2038709677419355</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>14.9</v>
+      </c>
+      <c r="V46">
+        <v>0.6711711711711712</v>
+      </c>
+      <c r="W46">
+        <v>-0.1006493506493507</v>
+      </c>
+      <c r="X46">
+        <v>0.05783702139277312</v>
+      </c>
+      <c r="Y46">
+        <v>-0.1584863720421238</v>
+      </c>
+      <c r="Z46">
+        <v>2.100622406639004</v>
+      </c>
+      <c r="AA46">
+        <v>-0.09387966804979253</v>
+      </c>
+      <c r="AB46">
+        <v>0.05729306560742731</v>
+      </c>
+      <c r="AC46">
+        <v>-0.1511727336572198</v>
+      </c>
+      <c r="AD46">
+        <v>12</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>12</v>
+      </c>
+      <c r="AG46">
+        <v>-2.9</v>
+      </c>
+      <c r="AH46">
+        <v>0.3508771929824561</v>
+      </c>
+      <c r="AI46">
+        <v>0.2797202797202797</v>
+      </c>
+      <c r="AJ46">
+        <v>-0.150259067357513</v>
+      </c>
+      <c r="AK46">
+        <v>-0.1035714285714286</v>
+      </c>
+      <c r="AL46">
+        <v>0.31</v>
+      </c>
+      <c r="AM46">
+        <v>-0.326</v>
+      </c>
+      <c r="AN46">
+        <v>-27.02702702702703</v>
+      </c>
+      <c r="AO46">
+        <v>-5.838709677419355</v>
+      </c>
+      <c r="AP46">
+        <v>6.531531531531532</v>
+      </c>
+      <c r="AQ46">
+        <v>5.552147239263804</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EDICO Holdings Limited (SEHK:8450)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>-0.125</v>
+      </c>
+      <c r="G47">
+        <v>-0.1654882154882155</v>
+      </c>
+      <c r="H47">
+        <v>-0.1654882154882155</v>
+      </c>
+      <c r="I47">
+        <v>-0.1835016835016835</v>
+      </c>
+      <c r="J47">
+        <v>-0.1835016835016835</v>
+      </c>
+      <c r="K47">
+        <v>-0.981</v>
+      </c>
+      <c r="L47">
+        <v>-0.1651515151515151</v>
+      </c>
+      <c r="M47">
+        <v>-0</v>
+      </c>
+      <c r="N47">
+        <v>-0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>-0</v>
+      </c>
+      <c r="Q47">
+        <v>-0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>1.48</v>
+      </c>
+      <c r="V47">
+        <v>0.1836228287841191</v>
+      </c>
+      <c r="W47">
+        <v>-0.1181927710843373</v>
+      </c>
+      <c r="X47">
+        <v>0.05395506070312366</v>
+      </c>
+      <c r="Y47">
+        <v>-0.172147831787461</v>
+      </c>
+      <c r="Z47">
+        <v>0.7644787644787644</v>
+      </c>
+      <c r="AA47">
+        <v>-0.1402831402831403</v>
+      </c>
+      <c r="AB47">
+        <v>0.05300762033200659</v>
+      </c>
+      <c r="AC47">
+        <v>-0.1932907606151469</v>
+      </c>
+      <c r="AD47">
+        <v>1.5</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>1.5</v>
+      </c>
+      <c r="AG47">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="AH47">
+        <v>0.1569037656903766</v>
+      </c>
+      <c r="AI47">
+        <v>0.169683257918552</v>
+      </c>
+      <c r="AJ47">
+        <v>0.002475247524752477</v>
+      </c>
+      <c r="AK47">
+        <v>0.002717391304347829</v>
+      </c>
+      <c r="AL47">
+        <v>0.1</v>
+      </c>
+      <c r="AM47">
+        <v>-0.07999999999999999</v>
+      </c>
+      <c r="AN47">
+        <v>-1.525940996948118</v>
+      </c>
+      <c r="AO47">
+        <v>-10.9</v>
+      </c>
+      <c r="AP47">
+        <v>-0.02034587995930826</v>
+      </c>
+      <c r="AQ47">
+        <v>13.625</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Lerado Financial Group Company Limited (SEHK:1225)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>-0.0217</v>
+      </c>
+      <c r="G48">
+        <v>-1.065693430656934</v>
+      </c>
+      <c r="H48">
+        <v>-1.065693430656934</v>
+      </c>
+      <c r="I48">
+        <v>-1.054744525547445</v>
+      </c>
+      <c r="J48">
+        <v>-1.054744525547445</v>
+      </c>
+      <c r="K48">
+        <v>-36.6</v>
+      </c>
+      <c r="L48">
+        <v>-1.335766423357664</v>
+      </c>
+      <c r="M48">
+        <v>-0</v>
+      </c>
+      <c r="N48">
+        <v>-0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>-0</v>
+      </c>
+      <c r="Q48">
+        <v>-0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>21.8</v>
+      </c>
+      <c r="V48">
+        <v>2.738693467336684</v>
+      </c>
+      <c r="W48">
+        <v>-0.2982885085574572</v>
+      </c>
+      <c r="X48">
+        <v>0.1885477073225094</v>
+      </c>
+      <c r="Y48">
+        <v>-0.4868362158799666</v>
+      </c>
+      <c r="Z48">
+        <v>0.1341821743388834</v>
+      </c>
+      <c r="AA48">
+        <v>-0.1415279138099902</v>
+      </c>
+      <c r="AB48">
+        <v>0.05835324254668799</v>
+      </c>
+      <c r="AC48">
+        <v>-0.1998811563566782</v>
+      </c>
+      <c r="AD48">
+        <v>99.3</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>99.3</v>
+      </c>
+      <c r="AG48">
+        <v>77.5</v>
+      </c>
+      <c r="AH48">
+        <v>0.9257878053328361</v>
+      </c>
+      <c r="AI48">
+        <v>0.5390879478827362</v>
+      </c>
+      <c r="AJ48">
+        <v>0.906857009127077</v>
+      </c>
+      <c r="AK48">
+        <v>0.4772167487684729</v>
+      </c>
+      <c r="AL48">
+        <v>9.83</v>
+      </c>
+      <c r="AM48">
+        <v>9.727</v>
+      </c>
+      <c r="AN48">
+        <v>-3.496478873239437</v>
+      </c>
+      <c r="AO48">
+        <v>-2.93997965412004</v>
+      </c>
+      <c r="AP48">
+        <v>-2.72887323943662</v>
+      </c>
+      <c r="AQ48">
+        <v>-2.971111339570268</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Neway Group Holdings Limited (SEHK:55)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>-0.0655</v>
+      </c>
+      <c r="G49">
+        <v>-0.1494186046511628</v>
+      </c>
+      <c r="H49">
+        <v>-0.1494186046511628</v>
+      </c>
+      <c r="I49">
+        <v>-0.2848837209302325</v>
+      </c>
+      <c r="J49">
+        <v>-0.2848837209302325</v>
+      </c>
+      <c r="K49">
+        <v>-12.4</v>
+      </c>
+      <c r="L49">
+        <v>-0.2403100775193799</v>
+      </c>
+      <c r="M49">
+        <v>0.013</v>
+      </c>
+      <c r="N49">
+        <v>0.001542111506524318</v>
+      </c>
+      <c r="O49">
+        <v>-0.001048387096774193</v>
+      </c>
+      <c r="P49">
+        <v>-0</v>
+      </c>
+      <c r="Q49">
+        <v>-0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0.013</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+      <c r="U49">
+        <v>20.2</v>
+      </c>
+      <c r="V49">
+        <v>2.396204033214709</v>
+      </c>
+      <c r="W49">
+        <v>-0.1144967682363804</v>
+      </c>
+      <c r="X49">
+        <v>0.07855092778336489</v>
+      </c>
+      <c r="Y49">
+        <v>-0.1930476960197453</v>
+      </c>
+      <c r="Z49">
+        <v>0.5139442231075697</v>
+      </c>
+      <c r="AA49">
+        <v>-0.1464143426294821</v>
+      </c>
+      <c r="AB49">
+        <v>0.05684330532342848</v>
+      </c>
+      <c r="AC49">
+        <v>-0.2032576479529105</v>
+      </c>
+      <c r="AD49">
+        <v>20.5</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>20.5</v>
+      </c>
+      <c r="AG49">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="AH49">
+        <v>0.708606982371241</v>
+      </c>
+      <c r="AI49">
+        <v>0.1835273052820054</v>
+      </c>
+      <c r="AJ49">
+        <v>0.03436426116838496</v>
+      </c>
+      <c r="AK49">
+        <v>0.003278688524590172</v>
+      </c>
+      <c r="AL49">
+        <v>0.708</v>
+      </c>
+      <c r="AM49">
+        <v>0.08499999999999996</v>
+      </c>
+      <c r="AN49">
+        <v>-1.694214876033058</v>
+      </c>
+      <c r="AO49">
+        <v>-20.76271186440678</v>
+      </c>
+      <c r="AP49">
+        <v>-0.02479338842975213</v>
+      </c>
+      <c r="AQ49">
+        <v>-172.9411764705883</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>China Ever Grand Financial Leasing Group Co., Ltd. (SEHK:379)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>-0.227</v>
+      </c>
+      <c r="G50">
+        <v>-2.328358208955224</v>
+      </c>
+      <c r="H50">
+        <v>-2.328358208955224</v>
+      </c>
+      <c r="I50">
+        <v>-2.283582089552239</v>
+      </c>
+      <c r="J50">
+        <v>-2.280742401979739</v>
+      </c>
+      <c r="K50">
+        <v>2.81</v>
+      </c>
+      <c r="L50">
+        <v>0.4194029850746269</v>
+      </c>
+      <c r="M50">
+        <v>-0</v>
+      </c>
+      <c r="N50">
+        <v>-0</v>
+      </c>
+      <c r="O50">
+        <v>-0</v>
+      </c>
+      <c r="P50">
+        <v>-0</v>
+      </c>
+      <c r="Q50">
+        <v>-0</v>
+      </c>
+      <c r="R50">
+        <v>-0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>4.63</v>
+      </c>
+      <c r="V50">
+        <v>0.2436842105263158</v>
+      </c>
+      <c r="W50">
+        <v>0.04722689075630252</v>
+      </c>
+      <c r="X50">
+        <v>0.06263866830482445</v>
+      </c>
+      <c r="Y50">
+        <v>-0.01541177754852193</v>
+      </c>
+      <c r="Z50">
+        <v>0.06482198142414861</v>
+      </c>
+      <c r="AA50">
+        <v>-0.1478422416143987</v>
+      </c>
+      <c r="AB50">
+        <v>0.05645844932223573</v>
+      </c>
+      <c r="AC50">
+        <v>-0.2043006909366344</v>
+      </c>
+      <c r="AD50">
+        <v>18.6</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>18.6</v>
+      </c>
+      <c r="AG50">
+        <v>13.97</v>
+      </c>
+      <c r="AH50">
+        <v>0.4946808510638298</v>
+      </c>
+      <c r="AI50">
+        <v>0.225181598062954</v>
+      </c>
+      <c r="AJ50">
+        <v>0.4237185319987868</v>
+      </c>
+      <c r="AK50">
+        <v>0.1791714762087983</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-0.36</v>
+      </c>
+      <c r="AN50">
+        <v>-1.223684210526316</v>
+      </c>
+      <c r="AP50">
+        <v>-0.9190789473684212</v>
+      </c>
+      <c r="AQ50">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kingkey Financial International (Holdings) Limited (SEHK:1468)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>0.273</v>
+      </c>
+      <c r="G51">
+        <v>-0.0196969696969697</v>
+      </c>
+      <c r="H51">
+        <v>-0.0196969696969697</v>
+      </c>
+      <c r="I51">
+        <v>-0.2181818181818182</v>
+      </c>
+      <c r="J51">
+        <v>-0.2181818181818182</v>
+      </c>
+      <c r="K51">
+        <v>-138.5</v>
+      </c>
+      <c r="L51">
+        <v>-2.098484848484849</v>
+      </c>
+      <c r="M51">
+        <v>-0</v>
+      </c>
+      <c r="N51">
+        <v>-0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>-0</v>
+      </c>
+      <c r="Q51">
+        <v>-0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>11.9</v>
+      </c>
+      <c r="V51">
+        <v>0.02436527436527437</v>
+      </c>
+      <c r="W51">
+        <v>-1.393360160965795</v>
+      </c>
+      <c r="X51">
+        <v>0.05243253660075418</v>
+      </c>
+      <c r="Y51">
+        <v>-1.445792697566549</v>
+      </c>
+      <c r="Z51">
+        <v>0.9116022099447513</v>
+      </c>
+      <c r="AA51">
+        <v>-0.1988950276243094</v>
+      </c>
+      <c r="AB51">
+        <v>0.05232967010385746</v>
+      </c>
+      <c r="AC51">
+        <v>-0.2512246977281669</v>
+      </c>
+      <c r="AD51">
+        <v>23</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>23</v>
+      </c>
+      <c r="AG51">
+        <v>11.1</v>
+      </c>
+      <c r="AH51">
+        <v>0.0449745795854517</v>
+      </c>
+      <c r="AI51">
+        <v>0.1362559241706161</v>
+      </c>
+      <c r="AJ51">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="AK51">
+        <v>0.07074569789674952</v>
+      </c>
+      <c r="AL51">
+        <v>1.82</v>
+      </c>
+      <c r="AM51">
+        <v>1.399</v>
+      </c>
+      <c r="AN51">
+        <v>-2.601809954751131</v>
+      </c>
+      <c r="AO51">
+        <v>-7.912087912087912</v>
+      </c>
+      <c r="AP51">
+        <v>-1.255656108597285</v>
+      </c>
+      <c r="AQ51">
+        <v>-10.29306647605432</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Smart Globe Holdings Limited (SEHK:1481)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>-0.0196</v>
+      </c>
+      <c r="G52">
+        <v>-0.125</v>
+      </c>
+      <c r="H52">
+        <v>-0.125</v>
+      </c>
+      <c r="I52">
+        <v>-0.1977941176470588</v>
+      </c>
+      <c r="J52">
+        <v>-0.1977941176470588</v>
+      </c>
+      <c r="K52">
+        <v>-2.51</v>
+      </c>
+      <c r="L52">
+        <v>-0.1845588235294117</v>
+      </c>
+      <c r="M52">
+        <v>-0</v>
+      </c>
+      <c r="N52">
+        <v>-0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>-0</v>
+      </c>
+      <c r="Q52">
+        <v>-0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>6.91</v>
+      </c>
+      <c r="V52">
+        <v>0.1957507082152975</v>
+      </c>
+      <c r="W52">
+        <v>-0.1530487804878049</v>
+      </c>
+      <c r="X52">
+        <v>0.05197446590460268</v>
+      </c>
+      <c r="Y52">
+        <v>-0.2050232463924075</v>
+      </c>
+      <c r="Z52">
+        <v>1.114571381740698</v>
+      </c>
+      <c r="AA52">
+        <v>-0.2204556630060646</v>
+      </c>
+      <c r="AB52">
+        <v>0.05196487844219463</v>
+      </c>
+      <c r="AC52">
+        <v>-0.2724205414482592</v>
+      </c>
+      <c r="AD52">
+        <v>0.186</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0.186</v>
+      </c>
+      <c r="AG52">
+        <v>-6.724</v>
+      </c>
+      <c r="AH52">
+        <v>0.005241503691596687</v>
+      </c>
+      <c r="AI52">
+        <v>0.01156284968295412</v>
+      </c>
+      <c r="AJ52">
+        <v>-0.2353023516237402</v>
+      </c>
+      <c r="AK52">
+        <v>-0.7327811682650393</v>
+      </c>
+      <c r="AL52">
+        <v>0.016</v>
+      </c>
+      <c r="AM52">
+        <v>-0.001000000000000001</v>
+      </c>
+      <c r="AN52">
+        <v>-0.0916256157635468</v>
+      </c>
+      <c r="AO52">
+        <v>-168.125</v>
+      </c>
+      <c r="AP52">
+        <v>3.312315270935961</v>
+      </c>
+      <c r="AQ52">
+        <v>2689.999999999998</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Finet Group Limited (SEHK:8317)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>-0.133</v>
+      </c>
+      <c r="G53">
+        <v>-1.407079646017699</v>
+      </c>
+      <c r="H53">
+        <v>-1.407079646017699</v>
+      </c>
+      <c r="I53">
+        <v>-1.787610619469027</v>
+      </c>
+      <c r="J53">
+        <v>-1.787610619469027</v>
+      </c>
+      <c r="K53">
+        <v>-2.4</v>
+      </c>
+      <c r="L53">
+        <v>-2.123893805309735</v>
+      </c>
+      <c r="M53">
+        <v>-0</v>
+      </c>
+      <c r="N53">
+        <v>-0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>-0</v>
+      </c>
+      <c r="Q53">
+        <v>-0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>1.47</v>
+      </c>
+      <c r="V53">
+        <v>0.09018404907975459</v>
+      </c>
+      <c r="W53">
+        <v>-0.4633204633204633</v>
+      </c>
+      <c r="X53">
+        <v>0.05197588590815058</v>
+      </c>
+      <c r="Y53">
+        <v>-0.5152963492286139</v>
+      </c>
+      <c r="Z53">
+        <v>0.1985940246045694</v>
+      </c>
+      <c r="AA53">
+        <v>-0.3550087873462215</v>
+      </c>
+      <c r="AB53">
+        <v>0.05196605617979337</v>
+      </c>
+      <c r="AC53">
+        <v>-0.4069748435260149</v>
+      </c>
+      <c r="AD53">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AG53">
+        <v>-1.382</v>
+      </c>
+      <c r="AH53">
+        <v>0.005369782767878935</v>
+      </c>
+      <c r="AI53">
+        <v>0.01384083044982699</v>
+      </c>
+      <c r="AJ53">
+        <v>-0.09263976404343745</v>
+      </c>
+      <c r="AK53">
+        <v>-0.2827332242225859</v>
+      </c>
+      <c r="AL53">
+        <v>0.033</v>
+      </c>
+      <c r="AM53">
+        <v>0.03</v>
+      </c>
+      <c r="AN53">
+        <v>-0.04444444444444444</v>
+      </c>
+      <c r="AO53">
+        <v>-61.21212121212121</v>
+      </c>
+      <c r="AP53">
+        <v>0.6979797979797979</v>
+      </c>
+      <c r="AQ53">
+        <v>-67.33333333333333</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Magnus Concordia Group Limited (SEHK:1172)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>0.154</v>
+      </c>
+      <c r="G54">
+        <v>-0.7787456445993032</v>
+      </c>
+      <c r="H54">
+        <v>-0.7787456445993032</v>
+      </c>
+      <c r="I54">
+        <v>-0.5069686411149826</v>
+      </c>
+      <c r="J54">
+        <v>-0.5069686411149826</v>
+      </c>
+      <c r="K54">
+        <v>-30</v>
+      </c>
+      <c r="L54">
+        <v>-0.5226480836236934</v>
+      </c>
+      <c r="M54">
+        <v>-0</v>
+      </c>
+      <c r="N54">
+        <v>-0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>-0</v>
+      </c>
+      <c r="Q54">
+        <v>-0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>5.37</v>
+      </c>
+      <c r="V54">
+        <v>0.1512676056338028</v>
+      </c>
+      <c r="W54">
+        <v>-0.5347593582887701</v>
+      </c>
+      <c r="X54">
+        <v>0.05873506730005215</v>
+      </c>
+      <c r="Y54">
+        <v>-0.5934944255888223</v>
+      </c>
+      <c r="Z54">
+        <v>0.775151924375422</v>
+      </c>
+      <c r="AA54">
+        <v>-0.3929777177582714</v>
+      </c>
+      <c r="AB54">
+        <v>0.05543934920646062</v>
+      </c>
+      <c r="AC54">
+        <v>-0.448417066964732</v>
+      </c>
+      <c r="AD54">
+        <v>22.1</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>22.1</v>
+      </c>
+      <c r="AG54">
+        <v>16.73</v>
+      </c>
+      <c r="AH54">
+        <v>0.3836805555555556</v>
+      </c>
+      <c r="AI54">
+        <v>0.4547325102880659</v>
+      </c>
+      <c r="AJ54">
+        <v>0.3203139957878613</v>
+      </c>
+      <c r="AK54">
+        <v>0.386999768679158</v>
+      </c>
+      <c r="AL54">
+        <v>0.879</v>
+      </c>
+      <c r="AM54">
+        <v>0.821</v>
+      </c>
+      <c r="AN54">
+        <v>-0.7754385964912281</v>
+      </c>
+      <c r="AO54">
+        <v>-33.10580204778157</v>
+      </c>
+      <c r="AP54">
+        <v>-0.5870175438596491</v>
+      </c>
+      <c r="AQ54">
+        <v>-35.44457978075518</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NOIZ Group Limited (SEHK:8163)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>-0.546</v>
+      </c>
+      <c r="G55">
+        <v>-1.476923076923077</v>
+      </c>
+      <c r="H55">
+        <v>-1.476923076923077</v>
+      </c>
+      <c r="I55">
+        <v>-1.961538461538461</v>
+      </c>
+      <c r="J55">
+        <v>-1.961538461538461</v>
+      </c>
+      <c r="K55">
+        <v>-4.12</v>
+      </c>
+      <c r="L55">
+        <v>-3.169230769230769</v>
+      </c>
+      <c r="M55">
+        <v>-0</v>
+      </c>
+      <c r="N55">
+        <v>-0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>-0</v>
+      </c>
+      <c r="Q55">
+        <v>-0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>1.14</v>
+      </c>
+      <c r="V55">
+        <v>0.06745562130177515</v>
+      </c>
+      <c r="W55">
+        <v>1.229850746268657</v>
+      </c>
+      <c r="X55">
+        <v>0.05839751990148897</v>
+      </c>
+      <c r="Y55">
+        <v>1.171453226367168</v>
+      </c>
+      <c r="Z55">
+        <v>0.2505299672383889</v>
+      </c>
+      <c r="AA55">
+        <v>-0.4914241665060705</v>
+      </c>
+      <c r="AB55">
+        <v>0.05761284611080071</v>
+      </c>
+      <c r="AC55">
+        <v>-0.5490370126168712</v>
+      </c>
+      <c r="AD55">
+        <v>10</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>10</v>
+      </c>
+      <c r="AG55">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AH55">
+        <v>0.3717472118959108</v>
+      </c>
+      <c r="AI55">
+        <v>1.642036124794745</v>
+      </c>
+      <c r="AJ55">
+        <v>0.343944099378882</v>
+      </c>
+      <c r="AK55">
+        <v>1.78989898989899</v>
+      </c>
+      <c r="AL55">
+        <v>1.67</v>
+      </c>
+      <c r="AM55">
+        <v>1.67</v>
+      </c>
+      <c r="AN55">
+        <v>-4.545454545454545</v>
+      </c>
+      <c r="AO55">
+        <v>-1.526946107784431</v>
+      </c>
+      <c r="AP55">
+        <v>-4.027272727272726</v>
+      </c>
+      <c r="AQ55">
+        <v>-1.526946107784431</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Greater China Financial Holdings Limited (SEHK:431)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>-0.0281</v>
+      </c>
+      <c r="G56">
+        <v>-1.8125</v>
+      </c>
+      <c r="H56">
+        <v>-1.8125</v>
+      </c>
+      <c r="I56">
+        <v>-2.118055555555555</v>
+      </c>
+      <c r="J56">
+        <v>-2.118055555555555</v>
+      </c>
+      <c r="K56">
+        <v>-41.7</v>
+      </c>
+      <c r="L56">
+        <v>-2.895833333333333</v>
+      </c>
+      <c r="M56">
+        <v>-0</v>
+      </c>
+      <c r="N56">
+        <v>-0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>-0</v>
+      </c>
+      <c r="Q56">
+        <v>-0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>4.74</v>
+      </c>
+      <c r="V56">
+        <v>0.04176211453744494</v>
+      </c>
+      <c r="W56">
+        <v>-4.582417582417583</v>
+      </c>
+      <c r="X56">
+        <v>0.05796716291187697</v>
+      </c>
+      <c r="Y56">
+        <v>-4.64038474532946</v>
+      </c>
+      <c r="Z56">
+        <v>0.337869544814641</v>
+      </c>
+      <c r="AA56">
+        <v>-0.715626466447677</v>
+      </c>
+      <c r="AB56">
+        <v>0.0526638262812857</v>
+      </c>
+      <c r="AC56">
+        <v>-0.7682902927289628</v>
+      </c>
+      <c r="AD56">
+        <v>62.7</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>62.7</v>
+      </c>
+      <c r="AG56">
+        <v>57.96</v>
+      </c>
+      <c r="AH56">
+        <v>0.3558456299659478</v>
+      </c>
+      <c r="AI56">
+        <v>1.334042553191489</v>
+      </c>
+      <c r="AJ56">
+        <v>0.3380380263618337</v>
+      </c>
+      <c r="AK56">
+        <v>1.371509701845717</v>
+      </c>
+      <c r="AL56">
+        <v>4.65</v>
+      </c>
+      <c r="AM56">
+        <v>1.77</v>
+      </c>
+      <c r="AN56">
+        <v>-2.139931740614335</v>
+      </c>
+      <c r="AO56">
+        <v>-6.559139784946236</v>
+      </c>
+      <c r="AP56">
+        <v>-1.978156996587031</v>
+      </c>
+      <c r="AQ56">
+        <v>-17.23163841807909</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Universe Printshop Holdings Limited (SEHK:8448)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>-0.116</v>
+      </c>
+      <c r="G57">
+        <v>-0.2398058252427185</v>
+      </c>
+      <c r="H57">
+        <v>-0.2398058252427185</v>
+      </c>
+      <c r="I57">
+        <v>-0.2640776699029126</v>
+      </c>
+      <c r="J57">
+        <v>-0.2640776699029126</v>
+      </c>
+      <c r="K57">
+        <v>-2.64</v>
+      </c>
+      <c r="L57">
+        <v>-0.2563106796116505</v>
+      </c>
+      <c r="M57">
+        <v>-0</v>
+      </c>
+      <c r="N57">
+        <v>-0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>-0</v>
+      </c>
+      <c r="Q57">
+        <v>-0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0.321</v>
+      </c>
+      <c r="V57">
+        <v>0.08381201044386423</v>
+      </c>
+      <c r="W57">
+        <v>-1.955555555555555</v>
+      </c>
+      <c r="X57">
+        <v>0.06787364903782131</v>
+      </c>
+      <c r="Y57">
+        <v>-2.023429204593377</v>
+      </c>
+      <c r="Z57">
+        <v>4.291666666666667</v>
+      </c>
+      <c r="AA57">
+        <v>-1.133333333333334</v>
+      </c>
+      <c r="AB57">
+        <v>0.05736099626271789</v>
+      </c>
+      <c r="AC57">
+        <v>-1.190694329596051</v>
+      </c>
+      <c r="AD57">
+        <v>5.58</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>5.58</v>
+      </c>
+      <c r="AG57">
+        <v>5.259</v>
+      </c>
+      <c r="AH57">
+        <v>0.5929861849096706</v>
+      </c>
+      <c r="AI57">
+        <v>1.17079311791859</v>
+      </c>
+      <c r="AJ57">
+        <v>0.5786115084167676</v>
+      </c>
+      <c r="AK57">
+        <v>1.183127109111361</v>
+      </c>
+      <c r="AL57">
+        <v>0.11</v>
+      </c>
+      <c r="AM57">
+        <v>0.109</v>
+      </c>
+      <c r="AN57">
+        <v>-2.364406779661017</v>
+      </c>
+      <c r="AO57">
+        <v>-24.72727272727273</v>
+      </c>
+      <c r="AP57">
+        <v>-2.228389830508475</v>
+      </c>
+      <c r="AQ57">
+        <v>-24.95412844036698</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BC Technology Group Limited (SEHK:863)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>0.0614</v>
+      </c>
+      <c r="G58">
+        <v>-2.465201465201465</v>
+      </c>
+      <c r="H58">
+        <v>-2.465201465201465</v>
+      </c>
+      <c r="I58">
+        <v>-1.311355311355311</v>
+      </c>
+      <c r="J58">
+        <v>-1.311355311355311</v>
+      </c>
+      <c r="K58">
+        <v>-42</v>
+      </c>
+      <c r="L58">
+        <v>-1.538461538461538</v>
+      </c>
+      <c r="M58">
+        <v>-0</v>
+      </c>
+      <c r="N58">
+        <v>-0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>-0</v>
+      </c>
+      <c r="Q58">
+        <v>-0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>60.1</v>
+      </c>
+      <c r="V58">
+        <v>0.08805860805860806</v>
+      </c>
+      <c r="W58">
+        <v>-0.3639514731369151</v>
+      </c>
+      <c r="X58">
+        <v>0.05212858429514875</v>
+      </c>
+      <c r="Y58">
+        <v>-0.4160800574320638</v>
+      </c>
+      <c r="Z58">
+        <v>1.975397973950797</v>
+      </c>
+      <c r="AA58">
+        <v>-2.590448625180899</v>
+      </c>
+      <c r="AB58">
+        <v>0.05242891812732345</v>
+      </c>
+      <c r="AC58">
+        <v>-2.642877543308222</v>
+      </c>
+      <c r="AD58">
+        <v>13.2</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>13.2</v>
+      </c>
+      <c r="AG58">
+        <v>-46.90000000000001</v>
+      </c>
+      <c r="AH58">
+        <v>0.01897369555843036</v>
+      </c>
+      <c r="AI58">
+        <v>0.1565836298932384</v>
+      </c>
+      <c r="AJ58">
+        <v>-0.07378854625550661</v>
+      </c>
+      <c r="AK58">
+        <v>-1.938016528925621</v>
+      </c>
+      <c r="AL58">
+        <v>2.35</v>
+      </c>
+      <c r="AM58">
+        <v>1.885</v>
+      </c>
+      <c r="AN58">
+        <v>-0.3905325443786982</v>
+      </c>
+      <c r="AO58">
+        <v>-15.23404255319149</v>
+      </c>
+      <c r="AP58">
+        <v>1.387573964497042</v>
+      </c>
+      <c r="AQ58">
+        <v>-18.9920424403183</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AGBA Group Holding Limited (NasdaqCM:AGBA)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G59">
+        <v>-0.5215759849906192</v>
+      </c>
+      <c r="H59">
+        <v>-0.5215759849906192</v>
+      </c>
+      <c r="I59">
+        <v>-1.075046904315197</v>
+      </c>
+      <c r="J59">
+        <v>-1.075046904315197</v>
+      </c>
+      <c r="K59">
+        <v>-66.40000000000001</v>
+      </c>
+      <c r="L59">
+        <v>-1.24577861163227</v>
+      </c>
+      <c r="M59">
+        <v>-0</v>
+      </c>
+      <c r="N59">
+        <v>-0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>-0</v>
+      </c>
+      <c r="Q59">
+        <v>-0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>1.62</v>
+      </c>
+      <c r="V59">
+        <v>0.04939024390243903</v>
+      </c>
+      <c r="W59">
+        <v>-2.075</v>
+      </c>
+      <c r="X59">
+        <v>0.05582358963564929</v>
+      </c>
+      <c r="Y59">
+        <v>-2.13082358963565</v>
+      </c>
+      <c r="Z59">
+        <v>3.172619047619047</v>
+      </c>
+      <c r="AA59">
+        <v>-3.410714285714286</v>
+      </c>
+      <c r="AB59">
+        <v>0.05594536370072779</v>
+      </c>
+      <c r="AC59">
+        <v>-3.466659649415013</v>
+      </c>
+      <c r="AD59">
+        <v>11.7</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>11.7</v>
+      </c>
+      <c r="AG59">
+        <v>10.08</v>
+      </c>
+      <c r="AH59">
+        <v>0.2629213483146067</v>
+      </c>
+      <c r="AI59">
+        <v>1.335616438356164</v>
+      </c>
+      <c r="AJ59">
+        <v>0.2350746268656716</v>
+      </c>
+      <c r="AK59">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AL59">
+        <v>0.926</v>
+      </c>
+      <c r="AM59">
+        <v>-0.02199999999999991</v>
+      </c>
+      <c r="AN59">
+        <v>-0.2052631578947368</v>
+      </c>
+      <c r="AO59">
+        <v>-61.87904967602591</v>
+      </c>
+      <c r="AP59">
+        <v>-0.1768421052631579</v>
+      </c>
+      <c r="AQ59">
+        <v>2604.545454545465</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SV Vision Limited (SEHK:8429)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>-0.0926</v>
+      </c>
+      <c r="G60">
+        <v>-0.05194630872483221</v>
+      </c>
+      <c r="H60">
+        <v>-0.05194630872483221</v>
+      </c>
+      <c r="I60">
+        <v>-0.1565025670094667</v>
+      </c>
+      <c r="J60">
+        <v>-0.1565025670094667</v>
+      </c>
+      <c r="K60">
+        <v>-1.32</v>
+      </c>
+      <c r="L60">
+        <v>-0.1771812080536913</v>
+      </c>
+      <c r="M60">
+        <v>-0</v>
+      </c>
+      <c r="N60">
+        <v>-0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>-0</v>
+      </c>
+      <c r="Q60">
+        <v>-0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0.05358622436398203</v>
+      </c>
+      <c r="Z60">
+        <v>187.5600077035587</v>
+      </c>
+      <c r="AA60">
+        <v>-29.35362267392228</v>
+      </c>
+      <c r="AB60">
+        <v>0.05283633448395423</v>
+      </c>
+      <c r="AC60">
+        <v>-29.40645900840624</v>
+      </c>
+      <c r="AD60">
+        <v>0.288</v>
+      </c>
+      <c r="AE60">
+        <v>0.03972062110263309</v>
+      </c>
+      <c r="AF60">
+        <v>0.3277206211026331</v>
+      </c>
+      <c r="AG60">
+        <v>0.3277206211026331</v>
+      </c>
+      <c r="AH60">
+        <v>0.1322669788964307</v>
+      </c>
+      <c r="AI60">
+        <v>0.04591390424188484</v>
+      </c>
+      <c r="AJ60">
+        <v>0.1322669788964307</v>
+      </c>
+      <c r="AK60">
+        <v>0.04591390424188484</v>
+      </c>
+      <c r="AL60">
+        <v>0.018</v>
+      </c>
+      <c r="AM60">
+        <v>-0.007000000000000003</v>
+      </c>
+      <c r="AN60">
+        <v>-0.2774566473988439</v>
+      </c>
+      <c r="AO60">
+        <v>-66.66666666666667</v>
+      </c>
+      <c r="AP60">
+        <v>-0.3157231417173729</v>
+      </c>
+      <c r="AQ60">
+        <v>171.4285714285714</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cornerstone Technologies Holdings Limited (SEHK:8391)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G61">
+        <v>-1.337746478873239</v>
+      </c>
+      <c r="H61">
+        <v>-1.366197183098592</v>
+      </c>
+      <c r="I61">
+        <v>-1.591549295774648</v>
+      </c>
+      <c r="J61">
+        <v>-1.591549295774648</v>
+      </c>
+      <c r="K61">
+        <v>-22</v>
+      </c>
+      <c r="L61">
+        <v>-1.549295774647887</v>
+      </c>
+      <c r="M61">
+        <v>-0</v>
+      </c>
+      <c r="N61">
+        <v>-0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>-0</v>
+      </c>
+      <c r="Q61">
+        <v>-0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0.05191675589446192</v>
+      </c>
+      <c r="AB61">
+        <v>0.05191675589446192</v>
+      </c>
+      <c r="AD61">
+        <v>0</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
+      <c r="AH61">
+        <v>0</v>
+      </c>
+      <c r="AJ61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
+        <v>0.372</v>
+      </c>
+      <c r="AM61">
+        <v>0.347</v>
+      </c>
+      <c r="AN61">
+        <v>-0</v>
+      </c>
+      <c r="AO61">
+        <v>-60.75268817204302</v>
+      </c>
+      <c r="AP61">
+        <v>-0</v>
+      </c>
+      <c r="AQ61">
+        <v>-65.12968299711817</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Prosperous Printing Company Limited (SEHK:8385)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>-0.178</v>
+      </c>
+      <c r="G62">
+        <v>-0.3594202898550725</v>
+      </c>
+      <c r="H62">
+        <v>-0.3594202898550725</v>
+      </c>
+      <c r="I62">
+        <v>-0.3884057971014492</v>
+      </c>
+      <c r="J62">
+        <v>-0.3884057971014492</v>
+      </c>
+      <c r="K62">
+        <v>-7.74</v>
+      </c>
+      <c r="L62">
+        <v>-0.3739130434782609</v>
+      </c>
+      <c r="M62">
+        <v>-0</v>
+      </c>
+      <c r="N62">
+        <v>-0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>-0</v>
+      </c>
+      <c r="Q62">
+        <v>-0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0.1339594019420918</v>
+      </c>
+      <c r="AB62">
+        <v>0.06001651560517954</v>
+      </c>
+      <c r="AD62">
+        <v>20.3</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>20.3</v>
+      </c>
+      <c r="AG62">
+        <v>20.3</v>
+      </c>
+      <c r="AH62">
+        <v>0.8822251195132551</v>
+      </c>
+      <c r="AI62">
+        <v>0.6403785488958991</v>
+      </c>
+      <c r="AJ62">
+        <v>0.8822251195132551</v>
+      </c>
+      <c r="AK62">
+        <v>0.6403785488958991</v>
+      </c>
+      <c r="AL62">
+        <v>1.23</v>
+      </c>
+      <c r="AM62">
+        <v>1.207</v>
+      </c>
+      <c r="AN62">
+        <v>-2.758152173913043</v>
+      </c>
+      <c r="AO62">
+        <v>-6.536585365853658</v>
+      </c>
+      <c r="AP62">
+        <v>-2.758152173913043</v>
+      </c>
+      <c r="AQ62">
+        <v>-6.661143330571664</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.10225</v>
+        <v>0.03055</v>
       </c>
       <c r="E2">
-        <v>0.12865</v>
+        <v>-0.06304999999999999</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.00510555640671687</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>-0.01116308755472989</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-0.04108504304939003</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-0.03622409037888346</v>
       </c>
       <c r="K2">
-        <v>1001.2</v>
+        <v>420.307</v>
       </c>
       <c r="L2">
-        <v>0.186888673187486</v>
+        <v>0.05393201881519885</v>
       </c>
       <c r="M2">
-        <v>511.6</v>
+        <v>734.9300000000001</v>
       </c>
       <c r="N2">
-        <v>0.1116713596577391</v>
+        <v>0.06377126236607845</v>
       </c>
       <c r="O2">
-        <v>0.5109868158210148</v>
+        <v>1.748555222730052</v>
       </c>
       <c r="P2">
-        <v>359.3</v>
+        <v>580.0700000000001</v>
       </c>
       <c r="Q2">
-        <v>0.07842752057276318</v>
+        <v>0.05033376806048348</v>
       </c>
       <c r="R2">
-        <v>0.3588693567718738</v>
+        <v>1.380110252743828</v>
       </c>
       <c r="S2">
-        <v>152.3</v>
+        <v>154.86</v>
       </c>
       <c r="T2">
-        <v>0.2976935105551212</v>
+        <v>0.2107139455458343</v>
       </c>
       <c r="U2">
-        <v>3336.9</v>
+        <v>8272.513999999999</v>
       </c>
       <c r="V2">
-        <v>0.7283740423024032</v>
+        <v>0.7178216438586763</v>
       </c>
       <c r="W2">
-        <v>0.1415106590919489</v>
+        <v>0.003974187292205394</v>
       </c>
       <c r="X2">
-        <v>0.1311061038722057</v>
+        <v>0.06127807825795339</v>
       </c>
       <c r="Y2">
-        <v>0.01040455521974323</v>
+        <v>-0.05730389096574799</v>
       </c>
       <c r="Z2">
-        <v>0.1167840567483492</v>
+        <v>0.1096648900802449</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06253859564132157</v>
+        <v>0.05936575554903833</v>
       </c>
       <c r="AC2">
-        <v>-0.06253859564132157</v>
+        <v>-0.06085912022172051</v>
       </c>
       <c r="AD2">
-        <v>40356.6</v>
+        <v>50981.389</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.2299889284601957</v>
       </c>
       <c r="AF2">
-        <v>40356.6</v>
+        <v>50981.61898892846</v>
       </c>
       <c r="AG2">
-        <v>37019.7</v>
+        <v>42709.10498892846</v>
       </c>
       <c r="AH2">
-        <v>0.8980526459847923</v>
+        <v>0.815626442376817</v>
       </c>
       <c r="AI2">
-        <v>0.8033850123026206</v>
+        <v>0.6067638283416367</v>
       </c>
       <c r="AJ2">
-        <v>0.8898752433835725</v>
+        <v>0.7875030365902917</v>
       </c>
       <c r="AK2">
-        <v>0.7893948989579135</v>
+        <v>0.5638190610502476</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>233.443</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>205.753</v>
+      </c>
+      <c r="AN2">
+        <v>-175.7191224623444</v>
+      </c>
+      <c r="AO2">
+        <v>-1.372215058922307</v>
+      </c>
+      <c r="AP2">
+        <v>-147.2067865747371</v>
+      </c>
+      <c r="AQ2">
+        <v>-1.556886169338965</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CSSC (Hong Kong) Shipping Company Limited (SEHK:3877)</t>
+          <t>G-Resources Group Limited (SEHK:1051)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.121</v>
+        <v>0.187</v>
       </c>
       <c r="E3">
-        <v>0.232</v>
+        <v>0.0398</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1.000936329588015</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.000936329588015</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1.043071161048689</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1.043071161048689</v>
       </c>
       <c r="K3">
-        <v>274.5</v>
+        <v>52.8</v>
       </c>
       <c r="L3">
-        <v>0.764837001950404</v>
+        <v>0.4943820224719101</v>
       </c>
       <c r="M3">
-        <v>81.3</v>
+        <v>6.9</v>
       </c>
       <c r="N3">
-        <v>0.05694074800392212</v>
+        <v>0.03859060402684564</v>
       </c>
       <c r="O3">
-        <v>0.2961748633879781</v>
+        <v>0.1306818181818182</v>
       </c>
       <c r="P3">
-        <v>81.3</v>
+        <v>6.9</v>
       </c>
       <c r="Q3">
-        <v>0.05694074800392212</v>
+        <v>0.03859060402684564</v>
       </c>
       <c r="R3">
-        <v>0.2961748633879781</v>
+        <v>0.1306818181818182</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,61 +770,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>179.4</v>
+        <v>80.3</v>
       </c>
       <c r="V3">
-        <v>0.125647849838913</v>
+        <v>0.4491051454138702</v>
       </c>
       <c r="W3">
-        <v>0.1775434965396805</v>
+        <v>0.03470259612224778</v>
       </c>
       <c r="X3">
-        <v>0.08489008089556663</v>
+        <v>0.05808734646071462</v>
       </c>
       <c r="Y3">
-        <v>0.09265341564411386</v>
+        <v>-0.02338475033846685</v>
       </c>
       <c r="Z3">
-        <v>0.07330024712538039</v>
+        <v>0.1036893203883495</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.1081553398058252</v>
       </c>
       <c r="AB3">
-        <v>0.06048215728472439</v>
+        <v>0.05808734646071462</v>
       </c>
       <c r="AC3">
-        <v>-0.06048215728472439</v>
+        <v>0.05006799334511062</v>
       </c>
       <c r="AD3">
-        <v>3727.4</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3727.4</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>3548</v>
+        <v>-80.3</v>
       </c>
       <c r="AH3">
-        <v>0.7230369335816264</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.680468079668474</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.7130511676514329</v>
+        <v>-0.815228426395939</v>
       </c>
       <c r="AK3">
-        <v>0.6696487552611214</v>
+        <v>-0.05383119930280887</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>-0.7163247100802854</v>
       </c>
     </row>
     <row r="4">
@@ -823,118 +841,5233 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Yue Da International Holdings Limited (SEHK:629)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.297</v>
+      </c>
+      <c r="G4">
+        <v>0.55</v>
+      </c>
+      <c r="H4">
+        <v>0.55</v>
+      </c>
+      <c r="I4">
+        <v>0.4944444444444444</v>
+      </c>
+      <c r="J4">
+        <v>0.3414021164021164</v>
+      </c>
+      <c r="K4">
+        <v>2.32</v>
+      </c>
+      <c r="L4">
+        <v>0.2148148148148148</v>
+      </c>
+      <c r="M4">
+        <v>1.85</v>
+      </c>
+      <c r="N4">
+        <v>0.04731457800511509</v>
+      </c>
+      <c r="O4">
+        <v>0.7974137931034484</v>
+      </c>
+      <c r="P4">
+        <v>1.85</v>
+      </c>
+      <c r="Q4">
+        <v>0.04731457800511509</v>
+      </c>
+      <c r="R4">
+        <v>0.7974137931034484</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1.52</v>
+      </c>
+      <c r="V4">
+        <v>0.03887468030690537</v>
+      </c>
+      <c r="W4">
+        <v>0.0380327868852459</v>
+      </c>
+      <c r="X4">
+        <v>0.06506725061004794</v>
+      </c>
+      <c r="Y4">
+        <v>-0.02703446372480204</v>
+      </c>
+      <c r="Z4">
+        <v>0.144675150703282</v>
+      </c>
+      <c r="AA4">
+        <v>0.04939240264089561</v>
+      </c>
+      <c r="AB4">
+        <v>0.07115643366125449</v>
+      </c>
+      <c r="AC4">
+        <v>-0.02176403102035888</v>
+      </c>
+      <c r="AD4">
+        <v>26.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>26.6</v>
+      </c>
+      <c r="AG4">
+        <v>25.08</v>
+      </c>
+      <c r="AH4">
+        <v>0.4048706240487062</v>
+      </c>
+      <c r="AI4">
+        <v>0.3026166097838453</v>
+      </c>
+      <c r="AJ4">
+        <v>0.3907759426612652</v>
+      </c>
+      <c r="AK4">
+        <v>0.2903449872655708</v>
+      </c>
+      <c r="AL4">
+        <v>2.04</v>
+      </c>
+      <c r="AM4">
+        <v>2.003</v>
+      </c>
+      <c r="AN4">
+        <v>4.971962616822431</v>
+      </c>
+      <c r="AO4">
+        <v>2.617647058823529</v>
+      </c>
+      <c r="AP4">
+        <v>4.68785046728972</v>
+      </c>
+      <c r="AQ4">
+        <v>2.666000998502247</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Joyas International Holdings Limited (Catalist:E9L)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0861</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0.1145374449339207</v>
+      </c>
+      <c r="J5">
+        <v>0.1145374449339207</v>
+      </c>
+      <c r="K5">
+        <v>-0.045</v>
+      </c>
+      <c r="L5">
+        <v>-0.09911894273127753</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1.3</v>
+      </c>
+      <c r="V5">
+        <v>0.4012345679012346</v>
+      </c>
+      <c r="W5">
+        <v>-0.03488372093023256</v>
+      </c>
+      <c r="X5">
+        <v>0.06407230813262103</v>
+      </c>
+      <c r="Y5">
+        <v>-0.09895602906285358</v>
+      </c>
+      <c r="Z5">
+        <v>0.250828729281768</v>
+      </c>
+      <c r="AA5">
+        <v>0.0287292817679558</v>
+      </c>
+      <c r="AB5">
+        <v>0.06007411694652443</v>
+      </c>
+      <c r="AC5">
+        <v>-0.03134483517856863</v>
+      </c>
+      <c r="AD5">
+        <v>1.89</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1.89</v>
+      </c>
+      <c r="AG5">
+        <v>0.5899999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="AI5">
+        <v>0.5779816513761469</v>
+      </c>
+      <c r="AJ5">
+        <v>0.1540469973890339</v>
+      </c>
+      <c r="AK5">
+        <v>0.299492385786802</v>
+      </c>
+      <c r="AL5">
+        <v>0.173</v>
+      </c>
+      <c r="AM5">
+        <v>0.116</v>
+      </c>
+      <c r="AO5">
+        <v>0.3005780346820809</v>
+      </c>
+      <c r="AQ5">
+        <v>0.4482758620689655</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>China Financial Services Holdings Limited (SEHK:605)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.32</v>
+      </c>
+      <c r="G6">
+        <v>0.2203947368421053</v>
+      </c>
+      <c r="H6">
+        <v>0.2203947368421053</v>
+      </c>
+      <c r="I6">
+        <v>0.2013157894736842</v>
+      </c>
+      <c r="J6">
+        <v>0.2013157894736842</v>
+      </c>
+      <c r="K6">
+        <v>-7.84</v>
+      </c>
+      <c r="L6">
+        <v>-0.5157894736842106</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>41.1</v>
+      </c>
+      <c r="V6">
+        <v>1.004889975550122</v>
+      </c>
+      <c r="W6">
+        <v>-0.0937799043062201</v>
+      </c>
+      <c r="X6">
+        <v>0.09064821373337069</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1844281180395908</v>
+      </c>
+      <c r="Z6">
+        <v>0.1050449205252246</v>
+      </c>
+      <c r="AA6">
+        <v>0.02114720110573601</v>
+      </c>
+      <c r="AB6">
+        <v>0.06218791836807436</v>
+      </c>
+      <c r="AC6">
+        <v>-0.04104071726233836</v>
+      </c>
+      <c r="AD6">
+        <v>129.8</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>129.8</v>
+      </c>
+      <c r="AG6">
+        <v>88.70000000000002</v>
+      </c>
+      <c r="AH6">
+        <v>0.760398359695372</v>
+      </c>
+      <c r="AI6">
+        <v>0.6000924641701341</v>
+      </c>
+      <c r="AJ6">
+        <v>0.6844135802469136</v>
+      </c>
+      <c r="AK6">
+        <v>0.5062785388127854</v>
+      </c>
+      <c r="AL6">
+        <v>4.89</v>
+      </c>
+      <c r="AM6">
+        <v>4.89</v>
+      </c>
+      <c r="AN6">
+        <v>39.69418960244649</v>
+      </c>
+      <c r="AO6">
+        <v>0.6257668711656442</v>
+      </c>
+      <c r="AP6">
+        <v>27.12538226299695</v>
+      </c>
+      <c r="AQ6">
+        <v>0.6257668711656442</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dingyi Group Investment Limited (SEHK:508)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.242</v>
+      </c>
+      <c r="G7">
+        <v>0.1301775147928994</v>
+      </c>
+      <c r="H7">
+        <v>0.1301775147928994</v>
+      </c>
+      <c r="I7">
+        <v>0.03879966187658496</v>
+      </c>
+      <c r="J7">
+        <v>0.01939983093829248</v>
+      </c>
+      <c r="K7">
+        <v>-4.99</v>
+      </c>
+      <c r="L7">
+        <v>-0.04218089602704988</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>9.5</v>
+      </c>
+      <c r="V7">
+        <v>0.1926977687626775</v>
+      </c>
+      <c r="W7">
+        <v>-0.03184428844926612</v>
+      </c>
+      <c r="X7">
+        <v>0.08439273580857799</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1162370242578441</v>
+      </c>
+      <c r="Z7">
+        <v>0.4631949882537196</v>
+      </c>
+      <c r="AA7">
+        <v>0.00898590446358653</v>
+      </c>
+      <c r="AB7">
+        <v>0.0619668716243221</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05298096716073557</v>
+      </c>
+      <c r="AD7">
+        <v>126.4</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>126.4</v>
+      </c>
+      <c r="AG7">
+        <v>116.9</v>
+      </c>
+      <c r="AH7">
+        <v>0.7194080819578829</v>
+      </c>
+      <c r="AI7">
+        <v>0.4321367521367522</v>
+      </c>
+      <c r="AJ7">
+        <v>0.7033694344163659</v>
+      </c>
+      <c r="AK7">
+        <v>0.4130742049469965</v>
+      </c>
+      <c r="AL7">
+        <v>0.014</v>
+      </c>
+      <c r="AM7">
+        <v>-0.006</v>
+      </c>
+      <c r="AN7">
+        <v>26.77966101694916</v>
+      </c>
+      <c r="AO7">
+        <v>327.8571428571428</v>
+      </c>
+      <c r="AP7">
+        <v>24.76694915254237</v>
+      </c>
+      <c r="AQ7">
+        <v>-765</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tong Tong AI Social Group Limited (SEHK:628)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.22</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="L8">
+        <v>0.6040816326530614</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>26.7</v>
+      </c>
+      <c r="V8">
+        <v>0.1266002844950213</v>
+      </c>
+      <c r="W8">
+        <v>0.0387434554973822</v>
+      </c>
+      <c r="X8">
+        <v>0.05808924374586158</v>
+      </c>
+      <c r="Y8">
+        <v>-0.01934578824847938</v>
+      </c>
+      <c r="Z8">
+        <v>0.06438896189224705</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.05808834349704807</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05808834349704807</v>
+      </c>
+      <c r="AD8">
+        <v>0.039</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0.039</v>
+      </c>
+      <c r="AG8">
+        <v>-26.661</v>
+      </c>
+      <c r="AH8">
+        <v>0.0001848875741328062</v>
+      </c>
+      <c r="AI8">
+        <v>0.0001163696257373806</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.1447087750150619</v>
+      </c>
+      <c r="AK8">
+        <v>-0.08643848540554208</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Global International Credit Group Limited (SEHK:1669)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.064</v>
+      </c>
+      <c r="E9">
+        <v>-0.08019999999999999</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>6.09</v>
+      </c>
+      <c r="L9">
+        <v>0.5691588785046729</v>
+      </c>
+      <c r="M9">
+        <v>2.56</v>
+      </c>
+      <c r="N9">
+        <v>0.08561872909698998</v>
+      </c>
+      <c r="O9">
+        <v>0.4203612479474549</v>
+      </c>
+      <c r="P9">
+        <v>2.56</v>
+      </c>
+      <c r="Q9">
+        <v>0.08561872909698998</v>
+      </c>
+      <c r="R9">
+        <v>0.4203612479474549</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>16.1</v>
+      </c>
+      <c r="V9">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="W9">
+        <v>0.05346795434591747</v>
+      </c>
+      <c r="X9">
+        <v>0.05829357457145418</v>
+      </c>
+      <c r="Y9">
+        <v>-0.00482562022553671</v>
+      </c>
+      <c r="Z9">
+        <v>0.1064433015329825</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.05809488655156627</v>
+      </c>
+      <c r="AC9">
+        <v>-0.05809488655156627</v>
+      </c>
+      <c r="AD9">
+        <v>0.601</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0.601</v>
+      </c>
+      <c r="AG9">
+        <v>-15.499</v>
+      </c>
+      <c r="AH9">
+        <v>0.01970427199108226</v>
+      </c>
+      <c r="AI9">
+        <v>0.005075970642139846</v>
+      </c>
+      <c r="AJ9">
+        <v>-1.076244705228804</v>
+      </c>
+      <c r="AK9">
+        <v>-0.1515038953675918</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Oi Wah Pawnshop Credit Holdings Limited (SEHK:1319)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>-0.0599</v>
+      </c>
+      <c r="E10">
+        <v>-0.08749999999999999</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="L10">
+        <v>0.4853932584269663</v>
+      </c>
+      <c r="M10">
+        <v>4.45</v>
+      </c>
+      <c r="N10">
+        <v>0.08120437956204381</v>
+      </c>
+      <c r="O10">
+        <v>0.5150462962962963</v>
+      </c>
+      <c r="P10">
+        <v>4.45</v>
+      </c>
+      <c r="Q10">
+        <v>0.08120437956204381</v>
+      </c>
+      <c r="R10">
+        <v>0.5150462962962963</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>24.1</v>
+      </c>
+      <c r="V10">
+        <v>0.4397810218978103</v>
+      </c>
+      <c r="W10">
+        <v>0.06376383763837638</v>
+      </c>
+      <c r="X10">
+        <v>0.05973867165194136</v>
+      </c>
+      <c r="Y10">
+        <v>0.004025165986435028</v>
+      </c>
+      <c r="Z10">
+        <v>0.1299270072992701</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.05814039715908442</v>
+      </c>
+      <c r="AC10">
+        <v>-0.05814039715908442</v>
+      </c>
+      <c r="AD10">
+        <v>8.82</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>8.82</v>
+      </c>
+      <c r="AG10">
+        <v>-15.28</v>
+      </c>
+      <c r="AH10">
+        <v>0.1386356491669286</v>
+      </c>
+      <c r="AI10">
+        <v>0.05906777390838468</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.3866396761133604</v>
+      </c>
+      <c r="AK10">
+        <v>-0.1220252355853698</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Capital Industrial Financial Services Group Limited (SEHK:730)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.248</v>
+      </c>
+      <c r="E11">
+        <v>0.351</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>3.54</v>
+      </c>
+      <c r="L11">
+        <v>0.1346007604562738</v>
+      </c>
+      <c r="M11">
+        <v>1.767</v>
+      </c>
+      <c r="N11">
+        <v>0.03333962264150944</v>
+      </c>
+      <c r="O11">
+        <v>0.4991525423728813</v>
+      </c>
+      <c r="P11">
+        <v>1.53</v>
+      </c>
+      <c r="Q11">
+        <v>0.02886792452830189</v>
+      </c>
+      <c r="R11">
+        <v>0.4322033898305085</v>
+      </c>
+      <c r="S11">
+        <v>0.2369999999999999</v>
+      </c>
+      <c r="T11">
+        <v>0.1341256366723259</v>
+      </c>
+      <c r="U11">
+        <v>55.2</v>
+      </c>
+      <c r="V11">
+        <v>1.041509433962264</v>
+      </c>
+      <c r="W11">
+        <v>0.02007941009642655</v>
+      </c>
+      <c r="X11">
+        <v>0.05851129468911813</v>
+      </c>
+      <c r="Y11">
+        <v>-0.03843188459269158</v>
+      </c>
+      <c r="Z11">
+        <v>0.2086970322171084</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.05821849895965218</v>
+      </c>
+      <c r="AC11">
+        <v>-0.05821849895965218</v>
+      </c>
+      <c r="AD11">
+        <v>2.19</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>2.19</v>
+      </c>
+      <c r="AG11">
+        <v>-53.01000000000001</v>
+      </c>
+      <c r="AH11">
+        <v>0.03968110164884943</v>
+      </c>
+      <c r="AI11">
+        <v>0.009694984284386206</v>
+      </c>
+      <c r="AJ11">
+        <v>5300.999999997289</v>
+      </c>
+      <c r="AK11">
+        <v>-0.3105630089636183</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DL Holdings Group Limited (SEHK:1709)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>-0.044</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>13</v>
+      </c>
+      <c r="L12">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="M12">
+        <v>1.93</v>
+      </c>
+      <c r="N12">
+        <v>0.001841778795686611</v>
+      </c>
+      <c r="O12">
+        <v>0.1484615384615385</v>
+      </c>
+      <c r="P12">
+        <v>1.93</v>
+      </c>
+      <c r="Q12">
+        <v>0.001841778795686611</v>
+      </c>
+      <c r="R12">
+        <v>0.1484615384615385</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>5.81</v>
+      </c>
+      <c r="V12">
+        <v>0.005544422177688709</v>
+      </c>
+      <c r="W12">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="X12">
+        <v>0.05835170205376435</v>
+      </c>
+      <c r="Y12">
+        <v>0.1797435360414737</v>
+      </c>
+      <c r="Z12">
+        <v>0.2992052360916316</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.05822280268378128</v>
+      </c>
+      <c r="AC12">
+        <v>-0.05822280268378128</v>
+      </c>
+      <c r="AD12">
+        <v>27</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>27</v>
+      </c>
+      <c r="AG12">
+        <v>21.19</v>
+      </c>
+      <c r="AH12">
+        <v>0.02511861568518001</v>
+      </c>
+      <c r="AI12">
+        <v>0.2244389027431422</v>
+      </c>
+      <c r="AJ12">
+        <v>0.01982059508554004</v>
+      </c>
+      <c r="AK12">
+        <v>0.1850816665210936</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-0.22</v>
+      </c>
+      <c r="AQ12">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Upbest Group Limited (SEHK:335)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>-0.13</v>
+      </c>
+      <c r="E13">
+        <v>-0.236</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>7.79</v>
+      </c>
+      <c r="L13">
+        <v>1.128985507246377</v>
+      </c>
+      <c r="M13">
+        <v>6.9</v>
+      </c>
+      <c r="N13">
+        <v>0.02594960511470478</v>
+      </c>
+      <c r="O13">
+        <v>0.8857509627727856</v>
+      </c>
+      <c r="P13">
+        <v>6.9</v>
+      </c>
+      <c r="Q13">
+        <v>0.02594960511470478</v>
+      </c>
+      <c r="R13">
+        <v>0.8857509627727856</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>51.3</v>
+      </c>
+      <c r="V13">
+        <v>0.1929296728093268</v>
+      </c>
+      <c r="W13">
+        <v>0.02211811470755253</v>
+      </c>
+      <c r="X13">
+        <v>0.05865069749758026</v>
+      </c>
+      <c r="Y13">
+        <v>-0.03653258279002773</v>
+      </c>
+      <c r="Z13">
+        <v>0.02243683543068969</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.0582593798871285</v>
+      </c>
+      <c r="AC13">
+        <v>-0.0582593798871285</v>
+      </c>
+      <c r="AD13">
+        <v>14.6</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>14.6</v>
+      </c>
+      <c r="AG13">
+        <v>-36.7</v>
+      </c>
+      <c r="AH13">
+        <v>0.05204991087344028</v>
+      </c>
+      <c r="AI13">
+        <v>0.03940620782726046</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.1601221640488656</v>
+      </c>
+      <c r="AK13">
+        <v>-0.1149749373433584</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AEON Credit Service (Asia) Company Limited (SEHK:900)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.0406</v>
+      </c>
+      <c r="E14">
+        <v>0.0014</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>49.5</v>
+      </c>
+      <c r="L14">
+        <v>0.299636803874092</v>
+      </c>
+      <c r="M14">
+        <v>25.8</v>
+      </c>
+      <c r="N14">
+        <v>0.08193077167354716</v>
+      </c>
+      <c r="O14">
+        <v>0.5212121212121212</v>
+      </c>
+      <c r="P14">
+        <v>25.8</v>
+      </c>
+      <c r="Q14">
+        <v>0.08193077167354716</v>
+      </c>
+      <c r="R14">
+        <v>0.5212121212121212</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>27.5</v>
+      </c>
+      <c r="V14">
+        <v>0.08732931089234679</v>
+      </c>
+      <c r="W14">
+        <v>0.09803921568627451</v>
+      </c>
+      <c r="X14">
+        <v>0.07234503857681268</v>
+      </c>
+      <c r="Y14">
+        <v>0.02569417710946183</v>
+      </c>
+      <c r="Z14">
+        <v>0.1923681544534625</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.05830987565430115</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05830987565430115</v>
+      </c>
+      <c r="AD14">
+        <v>437.6</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>437.6</v>
+      </c>
+      <c r="AG14">
+        <v>410.1</v>
+      </c>
+      <c r="AH14">
+        <v>0.5815282392026578</v>
+      </c>
+      <c r="AI14">
+        <v>0.4515995872033024</v>
+      </c>
+      <c r="AJ14">
+        <v>0.5656551724137932</v>
+      </c>
+      <c r="AK14">
+        <v>0.4355815188528944</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sun Hung Kai &amp; Co. Limited (SEHK:86)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>-0.0447</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.0003197276197277622</v>
+      </c>
+      <c r="J15">
+        <v>0.0001598638098638811</v>
+      </c>
+      <c r="K15">
+        <v>-13.9</v>
+      </c>
+      <c r="L15">
+        <v>-0.05373018940858137</v>
+      </c>
+      <c r="M15">
+        <v>64.06100000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.09309838686237466</v>
+      </c>
+      <c r="O15">
+        <v>-4.608705035971224</v>
+      </c>
+      <c r="P15">
+        <v>63.1</v>
+      </c>
+      <c r="Q15">
+        <v>0.09170178753088214</v>
+      </c>
+      <c r="R15">
+        <v>-4.539568345323741</v>
+      </c>
+      <c r="S15">
+        <v>0.9610000000000056</v>
+      </c>
+      <c r="T15">
+        <v>0.01500132686033633</v>
+      </c>
+      <c r="U15">
+        <v>695.2</v>
+      </c>
+      <c r="V15">
+        <v>1.010318267693649</v>
+      </c>
+      <c r="W15">
+        <v>-0.005025670692024007</v>
+      </c>
+      <c r="X15">
+        <v>0.08536163102362214</v>
+      </c>
+      <c r="Y15">
+        <v>-0.09038730171564614</v>
+      </c>
+      <c r="Z15">
+        <v>0.07244070856994453</v>
+      </c>
+      <c r="AA15">
+        <v>1.158064766123043E-05</v>
+      </c>
+      <c r="AB15">
+        <v>0.05836540879893189</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05835382815127066</v>
+      </c>
+      <c r="AD15">
+        <v>1829.1</v>
+      </c>
+      <c r="AE15">
+        <v>0.09643232388213957</v>
+      </c>
+      <c r="AF15">
+        <v>1829.196432323882</v>
+      </c>
+      <c r="AG15">
+        <v>1133.996432323882</v>
+      </c>
+      <c r="AH15">
+        <v>0.7266511837206356</v>
+      </c>
+      <c r="AI15">
+        <v>0.3705229610739348</v>
+      </c>
+      <c r="AJ15">
+        <v>0.6223580773261245</v>
+      </c>
+      <c r="AK15">
+        <v>0.2673513264208846</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>17932.35294117647</v>
+      </c>
+      <c r="AP15">
+        <v>11117.61208160669</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Allied Group Limited (SEHK:373)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.0509</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>-22.5</v>
+      </c>
+      <c r="L16">
+        <v>-0.02835538752362949</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1622.1</v>
+      </c>
+      <c r="V16">
+        <v>2.473090410123494</v>
+      </c>
+      <c r="W16">
+        <v>-0.004105464829851291</v>
+      </c>
+      <c r="X16">
+        <v>0.1046645386483788</v>
+      </c>
+      <c r="Y16">
+        <v>-0.1087700034782301</v>
+      </c>
+      <c r="Z16">
+        <v>0.1177701589563204</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.0584009329740095</v>
+      </c>
+      <c r="AC16">
+        <v>-0.0584009329740095</v>
+      </c>
+      <c r="AD16">
+        <v>2977.6</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>2977.6</v>
+      </c>
+      <c r="AG16">
+        <v>1355.5</v>
+      </c>
+      <c r="AH16">
+        <v>0.8194853447089583</v>
+      </c>
+      <c r="AI16">
+        <v>0.257486531593466</v>
+      </c>
+      <c r="AJ16">
+        <v>0.6739087202943224</v>
+      </c>
+      <c r="AK16">
+        <v>0.1363407765037216</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Doyen International Holdings Limited (SEHK:668)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.545</v>
+      </c>
+      <c r="E17">
+        <v>-0.0926</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>2.18</v>
+      </c>
+      <c r="L17">
+        <v>0.2096153846153846</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>-0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>18.5</v>
+      </c>
+      <c r="V17">
+        <v>0.336976320582878</v>
+      </c>
+      <c r="W17">
+        <v>0.02344086021505376</v>
+      </c>
+      <c r="X17">
+        <v>0.05815219522574668</v>
+      </c>
+      <c r="Y17">
+        <v>-0.03471133501069291</v>
+      </c>
+      <c r="Z17">
+        <v>0.1276026649325792</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.05844008507047221</v>
+      </c>
+      <c r="AC17">
+        <v>-0.05844008507047221</v>
+      </c>
+      <c r="AD17">
+        <v>0.347</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0.347</v>
+      </c>
+      <c r="AG17">
+        <v>-18.153</v>
+      </c>
+      <c r="AH17">
+        <v>0.006280884029902076</v>
+      </c>
+      <c r="AI17">
+        <v>0.002941999372599557</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.493999510164095</v>
+      </c>
+      <c r="AK17">
+        <v>-0.1825394431204561</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-0.221</v>
+      </c>
+      <c r="AQ17">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Oshidori International Holdings Limited (SEHK:622)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K18">
+        <v>-26.6</v>
+      </c>
+      <c r="M18">
+        <v>-0</v>
+      </c>
+      <c r="N18">
+        <v>-0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>34.4</v>
+      </c>
+      <c r="V18">
+        <v>0.2588412340105342</v>
+      </c>
+      <c r="W18">
+        <v>-0.04198895027624309</v>
+      </c>
+      <c r="X18">
+        <v>0.05888251066865575</v>
+      </c>
+      <c r="Y18">
+        <v>-0.1008714609448988</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.05847522653261505</v>
+      </c>
+      <c r="AC18">
+        <v>-0.05847522653261505</v>
+      </c>
+      <c r="AD18">
+        <v>10.3</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>10.3</v>
+      </c>
+      <c r="AG18">
+        <v>-24.1</v>
+      </c>
+      <c r="AH18">
+        <v>0.07192737430167598</v>
+      </c>
+      <c r="AI18">
+        <v>0.02471802255819535</v>
+      </c>
+      <c r="AJ18">
+        <v>-0.2215073529411764</v>
+      </c>
+      <c r="AK18">
+        <v>-0.06303949777661523</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Zhong Ji Longevity Science Group Limited (SEHK:767)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>-0.111</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-0.063</v>
+      </c>
+      <c r="L19">
+        <v>-0.00671641791044776</v>
+      </c>
+      <c r="M19">
+        <v>-0</v>
+      </c>
+      <c r="N19">
+        <v>-0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>10.1</v>
+      </c>
+      <c r="V19">
+        <v>0.6392405063291139</v>
+      </c>
+      <c r="W19">
+        <v>-0.00125</v>
+      </c>
+      <c r="X19">
+        <v>0.05949646401891031</v>
+      </c>
+      <c r="Y19">
+        <v>-0.06074646401891031</v>
+      </c>
+      <c r="Z19">
+        <v>0.2044463818657367</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.0587385472487736</v>
+      </c>
+      <c r="AC19">
+        <v>-0.0587385472487736</v>
+      </c>
+      <c r="AD19">
+        <v>2.17</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>2.17</v>
+      </c>
+      <c r="AG19">
+        <v>-7.93</v>
+      </c>
+      <c r="AH19">
+        <v>0.120756816917084</v>
+      </c>
+      <c r="AI19">
+        <v>0.03775883069427528</v>
+      </c>
+      <c r="AJ19">
+        <v>-1.007623888182973</v>
+      </c>
+      <c r="AK19">
+        <v>-0.1674055309267469</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Haosen Fintech Group Limited (SEHK:3848)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>-0.0882</v>
+      </c>
+      <c r="E20">
+        <v>-0.154</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0.001393419480187056</v>
+      </c>
+      <c r="J20">
+        <v>0.001215464703199312</v>
+      </c>
+      <c r="K20">
+        <v>1.45</v>
+      </c>
+      <c r="L20">
+        <v>0.2262090483619345</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>0.007880220646178092</v>
+      </c>
+      <c r="O20">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>0.007880220646178092</v>
+      </c>
+      <c r="R20">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>2.19</v>
+      </c>
+      <c r="V20">
+        <v>0.01725768321513002</v>
+      </c>
+      <c r="W20">
+        <v>0.01828499369482976</v>
+      </c>
+      <c r="X20">
+        <v>0.06019838178068471</v>
+      </c>
+      <c r="Y20">
+        <v>-0.04191338808585494</v>
+      </c>
+      <c r="Z20">
+        <v>0.06806091312008382</v>
+      </c>
+      <c r="AA20">
+        <v>8.272563756497682E-05</v>
+      </c>
+      <c r="AB20">
+        <v>0.05900757356357043</v>
+      </c>
+      <c r="AC20">
+        <v>-0.05892484792600545</v>
+      </c>
+      <c r="AD20">
+        <v>26.1</v>
+      </c>
+      <c r="AE20">
+        <v>0.01034090566000484</v>
+      </c>
+      <c r="AF20">
+        <v>26.11034090566001</v>
+      </c>
+      <c r="AG20">
+        <v>23.92034090566001</v>
+      </c>
+      <c r="AH20">
+        <v>0.1706442894716416</v>
+      </c>
+      <c r="AI20">
+        <v>0.2484088690102803</v>
+      </c>
+      <c r="AJ20">
+        <v>0.1586015570712871</v>
+      </c>
+      <c r="AK20">
+        <v>0.2324160675641964</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>2372.727272727273</v>
+      </c>
+      <c r="AP20">
+        <v>2174.576445969091</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hao Wen Holdings Limited (SEHK:8019)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>-0.288</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-3.2</v>
+      </c>
+      <c r="L21">
+        <v>-1.904761904761905</v>
+      </c>
+      <c r="M21">
+        <v>-0</v>
+      </c>
+      <c r="N21">
+        <v>-0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0.249</v>
+      </c>
+      <c r="V21">
+        <v>0.007980769230769231</v>
+      </c>
+      <c r="W21">
+        <v>-0.07511737089201878</v>
+      </c>
+      <c r="X21">
+        <v>0.06078386765355158</v>
+      </c>
+      <c r="Y21">
+        <v>-0.1359012385455703</v>
+      </c>
+      <c r="Z21">
+        <v>0.03311062496304618</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.05920967728627361</v>
+      </c>
+      <c r="AC21">
+        <v>-0.05920967728627361</v>
+      </c>
+      <c r="AD21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG21">
+        <v>7.951</v>
+      </c>
+      <c r="AH21">
+        <v>0.2081218274111675</v>
+      </c>
+      <c r="AI21">
+        <v>0.1719077568134172</v>
+      </c>
+      <c r="AJ21">
+        <v>0.2030854895149549</v>
+      </c>
+      <c r="AK21">
+        <v>0.1675623274535837</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ziyuanyuan Holdings Group Limited (SEHK:8223)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.578</v>
+      </c>
+      <c r="E22">
+        <v>-0.0459</v>
+      </c>
+      <c r="G22">
+        <v>0.006563421828908555</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1.99</v>
+      </c>
+      <c r="L22">
+        <v>0.02935103244837758</v>
+      </c>
+      <c r="M22">
+        <v>1.24</v>
+      </c>
+      <c r="N22">
+        <v>0.01409090909090909</v>
+      </c>
+      <c r="O22">
+        <v>0.6231155778894473</v>
+      </c>
+      <c r="P22">
+        <v>1.24</v>
+      </c>
+      <c r="Q22">
+        <v>0.01409090909090909</v>
+      </c>
+      <c r="R22">
+        <v>0.6231155778894473</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>3.31</v>
+      </c>
+      <c r="V22">
+        <v>0.03761363636363636</v>
+      </c>
+      <c r="W22">
+        <v>0.04606481481481481</v>
+      </c>
+      <c r="X22">
+        <v>0.06146846117146694</v>
+      </c>
+      <c r="Y22">
+        <v>-0.01540364635665213</v>
+      </c>
+      <c r="Z22">
+        <v>0.9735784032165422</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.05942398936386627</v>
+      </c>
+      <c r="AC22">
+        <v>-0.05942398936386627</v>
+      </c>
+      <c r="AD22">
+        <v>29</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>29</v>
+      </c>
+      <c r="AG22">
+        <v>25.69</v>
+      </c>
+      <c r="AH22">
+        <v>0.2478632478632479</v>
+      </c>
+      <c r="AI22">
+        <v>0.3684879288437103</v>
+      </c>
+      <c r="AJ22">
+        <v>0.2259653443574633</v>
+      </c>
+      <c r="AK22">
+        <v>0.340761374187558</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quam Plus International Financial Limited (SEHK:952)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>-0.207</v>
+      </c>
+      <c r="E23">
+        <v>-0.305</v>
+      </c>
+      <c r="G23">
+        <v>0.003883495145631068</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>2.49</v>
+      </c>
+      <c r="L23">
+        <v>0.08058252427184467</v>
+      </c>
+      <c r="M23">
+        <v>8.73</v>
+      </c>
+      <c r="N23">
+        <v>0.05382244143033293</v>
+      </c>
+      <c r="O23">
+        <v>3.506024096385542</v>
+      </c>
+      <c r="P23">
+        <v>8.73</v>
+      </c>
+      <c r="Q23">
+        <v>0.05382244143033293</v>
+      </c>
+      <c r="R23">
+        <v>3.506024096385542</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>21.1</v>
+      </c>
+      <c r="V23">
+        <v>0.1300863131935882</v>
+      </c>
+      <c r="W23">
+        <v>0.009198374584410788</v>
+      </c>
+      <c r="X23">
+        <v>0.06500742544862967</v>
+      </c>
+      <c r="Y23">
+        <v>-0.05580905086421888</v>
+      </c>
+      <c r="Z23">
+        <v>0.08800911421247506</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.06025950148480692</v>
+      </c>
+      <c r="AC23">
+        <v>-0.06025950148480692</v>
+      </c>
+      <c r="AD23">
+        <v>109.4</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>109.4</v>
+      </c>
+      <c r="AG23">
+        <v>88.30000000000001</v>
+      </c>
+      <c r="AH23">
+        <v>0.4027982326951399</v>
+      </c>
+      <c r="AI23">
+        <v>0.2915778251599147</v>
+      </c>
+      <c r="AJ23">
+        <v>0.35249500998004</v>
+      </c>
+      <c r="AK23">
+        <v>0.2493645862750636</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CSSC (Hong Kong) Shipping Company Limited (SEHK:3877)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.121</v>
+      </c>
+      <c r="E24">
+        <v>0.232</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>274.5</v>
+      </c>
+      <c r="L24">
+        <v>0.764837001950404</v>
+      </c>
+      <c r="M24">
+        <v>81.3</v>
+      </c>
+      <c r="N24">
+        <v>0.05694074800392212</v>
+      </c>
+      <c r="O24">
+        <v>0.2961748633879781</v>
+      </c>
+      <c r="P24">
+        <v>81.3</v>
+      </c>
+      <c r="Q24">
+        <v>0.05694074800392212</v>
+      </c>
+      <c r="R24">
+        <v>0.2961748633879781</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>179.4</v>
+      </c>
+      <c r="V24">
+        <v>0.125647849838913</v>
+      </c>
+      <c r="W24">
+        <v>0.1775434965396805</v>
+      </c>
+      <c r="X24">
+        <v>0.08487182544240149</v>
+      </c>
+      <c r="Y24">
+        <v>0.092671671097279</v>
+      </c>
+      <c r="Z24">
+        <v>0.07330024712538039</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.06047710119843693</v>
+      </c>
+      <c r="AC24">
+        <v>-0.06047710119843693</v>
+      </c>
+      <c r="AD24">
+        <v>3727.4</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>3727.4</v>
+      </c>
+      <c r="AG24">
+        <v>3548</v>
+      </c>
+      <c r="AH24">
+        <v>0.7230369335816264</v>
+      </c>
+      <c r="AI24">
+        <v>0.680468079668474</v>
+      </c>
+      <c r="AJ24">
+        <v>0.7130511676514329</v>
+      </c>
+      <c r="AK24">
+        <v>0.6696487552611214</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Styland Holdings Limited (SEHK:211)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K25">
+        <v>-8.77</v>
+      </c>
+      <c r="M25">
+        <v>-0</v>
+      </c>
+      <c r="N25">
+        <v>-0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>-0</v>
+      </c>
+      <c r="Q25">
+        <v>-0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>2.78</v>
+      </c>
+      <c r="V25">
+        <v>0.1336538461538462</v>
+      </c>
+      <c r="W25">
+        <v>-0.1786150712830957</v>
+      </c>
+      <c r="X25">
+        <v>0.07254004236622488</v>
+      </c>
+      <c r="Y25">
+        <v>-0.2511551136493206</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.0612411392450041</v>
+      </c>
+      <c r="AC25">
+        <v>-0.0612411392450041</v>
+      </c>
+      <c r="AD25">
+        <v>29.3</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>29.3</v>
+      </c>
+      <c r="AG25">
+        <v>26.52</v>
+      </c>
+      <c r="AH25">
+        <v>0.5848303393213573</v>
+      </c>
+      <c r="AI25">
+        <v>0.4173789173789174</v>
+      </c>
+      <c r="AJ25">
+        <v>0.5604395604395604</v>
+      </c>
+      <c r="AK25">
+        <v>0.3933550875111243</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hong Kong Finance Group Limited (SEHK:1273)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.0319</v>
+      </c>
+      <c r="E26">
+        <v>-0.014</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>5.96</v>
+      </c>
+      <c r="L26">
+        <v>0.3656441717791411</v>
+      </c>
+      <c r="M26">
+        <v>1.39</v>
+      </c>
+      <c r="N26">
+        <v>0.07853107344632768</v>
+      </c>
+      <c r="O26">
+        <v>0.2332214765100671</v>
+      </c>
+      <c r="P26">
+        <v>1.39</v>
+      </c>
+      <c r="Q26">
+        <v>0.07853107344632768</v>
+      </c>
+      <c r="R26">
+        <v>0.2332214765100671</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>4.12</v>
+      </c>
+      <c r="V26">
+        <v>0.2327683615819209</v>
+      </c>
+      <c r="W26">
+        <v>0.05831702544031311</v>
+      </c>
+      <c r="X26">
+        <v>0.07686824313575266</v>
+      </c>
+      <c r="Y26">
+        <v>-0.01855121769543955</v>
+      </c>
+      <c r="Z26">
+        <v>0.1219420962070771</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.06157481697986067</v>
+      </c>
+      <c r="AC26">
+        <v>-0.06157481697986067</v>
+      </c>
+      <c r="AD26">
+        <v>32.4</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>32.4</v>
+      </c>
+      <c r="AG26">
+        <v>28.28</v>
+      </c>
+      <c r="AH26">
+        <v>0.6467065868263473</v>
+      </c>
+      <c r="AI26">
+        <v>0.2315939957112223</v>
+      </c>
+      <c r="AJ26">
+        <v>0.6150500217485864</v>
+      </c>
+      <c r="AK26">
+        <v>0.2082780969214906</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>China Properties Investment Holdings Limited (SEHK:736)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K27">
+        <v>-4.3</v>
+      </c>
+      <c r="M27">
+        <v>-0</v>
+      </c>
+      <c r="N27">
+        <v>-0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>-0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0.201</v>
+      </c>
+      <c r="V27">
+        <v>0.03059360730593607</v>
+      </c>
+      <c r="W27">
+        <v>-0.0671875</v>
+      </c>
+      <c r="X27">
+        <v>0.08026254691500583</v>
+      </c>
+      <c r="Y27">
+        <v>-0.1474500469150058</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.06177419340391213</v>
+      </c>
+      <c r="AC27">
+        <v>-0.06177419340391213</v>
+      </c>
+      <c r="AD27">
+        <v>14.2</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>14.2</v>
+      </c>
+      <c r="AG27">
+        <v>13.999</v>
+      </c>
+      <c r="AH27">
+        <v>0.6836783822821377</v>
+      </c>
+      <c r="AI27">
+        <v>0.1878306878306878</v>
+      </c>
+      <c r="AJ27">
+        <v>0.680587291555253</v>
+      </c>
+      <c r="AK27">
+        <v>0.1856655923818618</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aceso Life Science Group Limited (SEHK:474)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>-0.324</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-50.5</v>
+      </c>
+      <c r="L28">
+        <v>-23.05936073059361</v>
+      </c>
+      <c r="M28">
+        <v>-0</v>
+      </c>
+      <c r="N28">
+        <v>-0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>-0</v>
+      </c>
+      <c r="Q28">
+        <v>-0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>38.4</v>
+      </c>
+      <c r="V28">
+        <v>0.8084210526315789</v>
+      </c>
+      <c r="W28">
+        <v>-0.3109605911330049</v>
+      </c>
+      <c r="X28">
+        <v>0.127250103537807</v>
+      </c>
+      <c r="Y28">
+        <v>-0.4382106946708119</v>
+      </c>
+      <c r="Z28">
+        <v>0.004328063241106719</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.06278337749594121</v>
+      </c>
+      <c r="AC28">
+        <v>-0.06278337749594121</v>
+      </c>
+      <c r="AD28">
+        <v>320.2</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>320.2</v>
+      </c>
+      <c r="AG28">
+        <v>281.8</v>
+      </c>
+      <c r="AH28">
+        <v>0.8708186021212946</v>
+      </c>
+      <c r="AI28">
+        <v>0.6026726896292114</v>
+      </c>
+      <c r="AJ28">
+        <v>0.85575463103553</v>
+      </c>
+      <c r="AK28">
+        <v>0.5717184012984379</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>China Rongzhong Financial Holdings Company Limited (SEHK:3963)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>-0.018</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-1.63</v>
+      </c>
+      <c r="L29">
+        <v>-0.1613861386138614</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0.946</v>
+      </c>
+      <c r="V29">
+        <v>0.02766081871345029</v>
+      </c>
+      <c r="W29">
+        <v>0.4405405405405405</v>
+      </c>
+      <c r="X29">
+        <v>0.06005833383838004</v>
+      </c>
+      <c r="Y29">
+        <v>0.3804822067021604</v>
+      </c>
+      <c r="Z29">
+        <v>2.525</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.06328914641776862</v>
+      </c>
+      <c r="AC29">
+        <v>-0.06328914641776862</v>
+      </c>
+      <c r="AD29">
+        <v>6.57</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>6.57</v>
+      </c>
+      <c r="AG29">
+        <v>5.624000000000001</v>
+      </c>
+      <c r="AH29">
+        <v>0.1611479028697572</v>
+      </c>
+      <c r="AI29">
+        <v>0.761297798377752</v>
+      </c>
+      <c r="AJ29">
+        <v>0.1412213740458015</v>
+      </c>
+      <c r="AK29">
+        <v>0.7319104633003644</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Far East Horizon Limited (SEHK:3360)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D30">
         <v>0.08349999999999999</v>
       </c>
-      <c r="E4">
+      <c r="E30">
         <v>0.0253</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
         <v>726.7</v>
       </c>
-      <c r="L4">
+      <c r="L30">
         <v>0.1453894324070184</v>
       </c>
-      <c r="M4">
+      <c r="M30">
         <v>430.3</v>
       </c>
-      <c r="N4">
+      <c r="N30">
         <v>0.1364515617567782</v>
       </c>
-      <c r="O4">
+      <c r="O30">
         <v>0.592128801431127</v>
       </c>
-      <c r="P4">
+      <c r="P30">
         <v>278</v>
       </c>
-      <c r="Q4">
+      <c r="Q30">
         <v>0.08815601712383067</v>
       </c>
-      <c r="R4">
+      <c r="R30">
         <v>0.3825512591165542</v>
       </c>
-      <c r="S4">
+      <c r="S30">
         <v>152.3</v>
       </c>
-      <c r="T4">
+      <c r="T30">
         <v>0.3539391122472694</v>
       </c>
-      <c r="U4">
+      <c r="U30">
         <v>3157.5</v>
       </c>
-      <c r="V4">
+      <c r="V30">
         <v>1.001268431901062</v>
       </c>
-      <c r="W4">
+      <c r="W30">
         <v>0.1054778216442174</v>
       </c>
-      <c r="X4">
-        <v>0.1773221268488448</v>
-      </c>
-      <c r="Y4">
-        <v>-0.0718443052046274</v>
-      </c>
-      <c r="Z4">
+      <c r="X30">
+        <v>0.1772607047189371</v>
+      </c>
+      <c r="Y30">
+        <v>-0.07178288307471975</v>
+      </c>
+      <c r="Z30">
         <v>0.1219799689577415</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.06459503399791874</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06459503399791874</v>
-      </c>
-      <c r="AD4">
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.06459016518090371</v>
+      </c>
+      <c r="AC30">
+        <v>-0.06459016518090371</v>
+      </c>
+      <c r="AD30">
         <v>36629.2</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
         <v>36629.2</v>
       </c>
-      <c r="AG4">
+      <c r="AG30">
         <v>33471.7</v>
       </c>
-      <c r="AH4">
+      <c r="AH30">
         <v>0.9207318759159132</v>
       </c>
-      <c r="AI4">
+      <c r="AI30">
         <v>0.8184290198969958</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ30">
         <v>0.9138980811026288</v>
       </c>
-      <c r="AK4">
+      <c r="AK30">
         <v>0.8046468580220202</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AGTech Holdings Limited (SEHK:8279)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0.001907810499359795</v>
+      </c>
+      <c r="H31">
+        <v>0.001907810499359795</v>
+      </c>
+      <c r="I31">
+        <v>-0.03188220230473752</v>
+      </c>
+      <c r="J31">
+        <v>-0.03122858084518709</v>
+      </c>
+      <c r="K31">
+        <v>4.65</v>
+      </c>
+      <c r="L31">
+        <v>0.05953905249679899</v>
+      </c>
+      <c r="M31">
+        <v>-0</v>
+      </c>
+      <c r="N31">
+        <v>-0</v>
+      </c>
+      <c r="O31">
+        <v>-0</v>
+      </c>
+      <c r="P31">
+        <v>-0</v>
+      </c>
+      <c r="Q31">
+        <v>-0</v>
+      </c>
+      <c r="R31">
+        <v>-0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>188.8</v>
+      </c>
+      <c r="V31">
+        <v>0.6282861896838603</v>
+      </c>
+      <c r="W31">
+        <v>0.01381461675579323</v>
+      </c>
+      <c r="X31">
+        <v>0.05844926094831457</v>
+      </c>
+      <c r="Y31">
+        <v>-0.04463464419252134</v>
+      </c>
+      <c r="Z31">
+        <v>0.2269095557686162</v>
+      </c>
+      <c r="AA31">
+        <v>-0.00708606340686572</v>
+      </c>
+      <c r="AB31">
+        <v>0.05819996209915981</v>
+      </c>
+      <c r="AC31">
+        <v>-0.06528602550602554</v>
+      </c>
+      <c r="AD31">
+        <v>10.6</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>10.6</v>
+      </c>
+      <c r="AG31">
+        <v>-178.2</v>
+      </c>
+      <c r="AH31">
+        <v>0.03407264545162327</v>
+      </c>
+      <c r="AI31">
+        <v>0.02827420645505468</v>
+      </c>
+      <c r="AJ31">
+        <v>-1.457072771872445</v>
+      </c>
+      <c r="AK31">
+        <v>-0.9575497044599679</v>
+      </c>
+      <c r="AL31">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="AM31">
+        <v>-6.927</v>
+      </c>
+      <c r="AN31">
+        <v>10.29126213592233</v>
+      </c>
+      <c r="AO31">
+        <v>-2.668810289389068</v>
+      </c>
+      <c r="AP31">
+        <v>-173.0097087378641</v>
+      </c>
+      <c r="AQ31">
+        <v>0.3594629709831096</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hi Sun Technology (China) Limited (SEHK:818)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>-0.148</v>
+      </c>
+      <c r="E32">
+        <v>-0.226</v>
+      </c>
+      <c r="G32">
+        <v>0.179805942995755</v>
+      </c>
+      <c r="H32">
+        <v>0.04942389326864766</v>
+      </c>
+      <c r="I32">
+        <v>-0.02977562158884172</v>
+      </c>
+      <c r="J32">
+        <v>-0.02767099933999186</v>
+      </c>
+      <c r="K32">
+        <v>19.3</v>
+      </c>
+      <c r="L32">
+        <v>0.0585203153426319</v>
+      </c>
+      <c r="M32">
+        <v>1.28</v>
+      </c>
+      <c r="N32">
+        <v>0.01029766693483508</v>
+      </c>
+      <c r="O32">
+        <v>0.06632124352331606</v>
+      </c>
+      <c r="P32">
+        <v>-0</v>
+      </c>
+      <c r="Q32">
+        <v>-0</v>
+      </c>
+      <c r="R32">
+        <v>-0</v>
+      </c>
+      <c r="S32">
+        <v>1.28</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>441.4</v>
+      </c>
+      <c r="V32">
+        <v>3.551086082059533</v>
+      </c>
+      <c r="W32">
+        <v>0.02155942806076854</v>
+      </c>
+      <c r="X32">
+        <v>0.05860983547186048</v>
+      </c>
+      <c r="Y32">
+        <v>-0.03705040741109194</v>
+      </c>
+      <c r="Z32">
+        <v>0.6285017341921713</v>
+      </c>
+      <c r="AA32">
+        <v>-0.01739127107201531</v>
+      </c>
+      <c r="AB32">
+        <v>0.05824750630293895</v>
+      </c>
+      <c r="AC32">
+        <v>-0.07563877737495427</v>
+      </c>
+      <c r="AD32">
+        <v>6.33</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>6.33</v>
+      </c>
+      <c r="AG32">
+        <v>-435.07</v>
+      </c>
+      <c r="AH32">
+        <v>0.04845747531194979</v>
+      </c>
+      <c r="AI32">
+        <v>0.006406039691133758</v>
+      </c>
+      <c r="AJ32">
+        <v>1.399974257489462</v>
+      </c>
+      <c r="AK32">
+        <v>-0.7957675635139831</v>
+      </c>
+      <c r="AL32">
+        <v>0.32</v>
+      </c>
+      <c r="AM32">
+        <v>-15.38</v>
+      </c>
+      <c r="AN32">
+        <v>-3.617142857142857</v>
+      </c>
+      <c r="AO32">
+        <v>-30.6875</v>
+      </c>
+      <c r="AP32">
+        <v>248.6114285714286</v>
+      </c>
+      <c r="AQ32">
+        <v>0.6384915474642393</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alliance International Education Leasing Holdings Limited (SEHK:1563)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>15.5</v>
+      </c>
+      <c r="L33">
+        <v>0.1867469879518072</v>
+      </c>
+      <c r="M33">
+        <v>-0</v>
+      </c>
+      <c r="N33">
+        <v>-0</v>
+      </c>
+      <c r="O33">
+        <v>-0</v>
+      </c>
+      <c r="P33">
+        <v>-0</v>
+      </c>
+      <c r="Q33">
+        <v>-0</v>
+      </c>
+      <c r="R33">
+        <v>-0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>90.2</v>
+      </c>
+      <c r="V33">
+        <v>1.952380952380952</v>
+      </c>
+      <c r="W33">
+        <v>0.04508435136707388</v>
+      </c>
+      <c r="X33">
+        <v>0.06283978355825812</v>
+      </c>
+      <c r="Y33">
+        <v>-0.01775543219118424</v>
+      </c>
+      <c r="Z33">
+        <v>0.2385057471264368</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0.07586601780376254</v>
+      </c>
+      <c r="AC33">
+        <v>-0.07586601780376254</v>
+      </c>
+      <c r="AD33">
+        <v>21.4</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>21.4</v>
+      </c>
+      <c r="AG33">
+        <v>-68.80000000000001</v>
+      </c>
+      <c r="AH33">
+        <v>0.3165680473372781</v>
+      </c>
+      <c r="AI33">
+        <v>0.04904881961952785</v>
+      </c>
+      <c r="AJ33">
+        <v>3.044247787610619</v>
+      </c>
+      <c r="AK33">
+        <v>-0.1987864778965617</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Changyou International Group Limited (SEHK:1039)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.175</v>
+      </c>
+      <c r="G34">
+        <v>0.02771653543307086</v>
+      </c>
+      <c r="H34">
+        <v>-0.01834645669291339</v>
+      </c>
+      <c r="I34">
+        <v>-0.04881889763779527</v>
+      </c>
+      <c r="J34">
+        <v>-0.04881889763779527</v>
+      </c>
+      <c r="K34">
+        <v>-3.77</v>
+      </c>
+      <c r="L34">
+        <v>-0.1484251968503937</v>
+      </c>
+      <c r="M34">
+        <v>-0</v>
+      </c>
+      <c r="N34">
+        <v>-0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>-0</v>
+      </c>
+      <c r="Q34">
+        <v>-0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>1.78</v>
+      </c>
+      <c r="V34">
+        <v>0.1289855072463768</v>
+      </c>
+      <c r="W34">
+        <v>-0.109593023255814</v>
+      </c>
+      <c r="X34">
+        <v>0.07422072140237539</v>
+      </c>
+      <c r="Y34">
+        <v>-0.1838137446581893</v>
+      </c>
+      <c r="Z34">
+        <v>0.4734389561975769</v>
+      </c>
+      <c r="AA34">
+        <v>-0.02311276794035415</v>
+      </c>
+      <c r="AB34">
+        <v>0.06138370650618498</v>
+      </c>
+      <c r="AC34">
+        <v>-0.08449647444653913</v>
+      </c>
+      <c r="AD34">
+        <v>21.7</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>21.7</v>
+      </c>
+      <c r="AG34">
+        <v>19.92</v>
+      </c>
+      <c r="AH34">
+        <v>0.6112676056338028</v>
+      </c>
+      <c r="AI34">
+        <v>19.72727272727277</v>
+      </c>
+      <c r="AJ34">
+        <v>0.5907473309608541</v>
+      </c>
+      <c r="AK34">
+        <v>-29.29411764705868</v>
+      </c>
+      <c r="AL34">
+        <v>2.6</v>
+      </c>
+      <c r="AM34">
+        <v>2.6</v>
+      </c>
+      <c r="AN34">
+        <v>-18.23529411764706</v>
+      </c>
+      <c r="AO34">
+        <v>-0.4769230769230769</v>
+      </c>
+      <c r="AP34">
+        <v>-16.73949579831933</v>
+      </c>
+      <c r="AQ34">
+        <v>-0.4769230769230769</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>China Success Finance Group Holdings Limited (SEHK:3623)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>-0.0592</v>
+      </c>
+      <c r="G35">
+        <v>-0.4284158415841584</v>
+      </c>
+      <c r="H35">
+        <v>-0.4415841584158416</v>
+      </c>
+      <c r="I35">
+        <v>-0.202970297029703</v>
+      </c>
+      <c r="J35">
+        <v>-0.202970297029703</v>
+      </c>
+      <c r="K35">
+        <v>-1.95</v>
+      </c>
+      <c r="L35">
+        <v>-0.1930693069306931</v>
+      </c>
+      <c r="M35">
+        <v>-0</v>
+      </c>
+      <c r="N35">
+        <v>-0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>-0</v>
+      </c>
+      <c r="Q35">
+        <v>-0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>1.03</v>
+      </c>
+      <c r="V35">
+        <v>0.01663974151857835</v>
+      </c>
+      <c r="W35">
+        <v>-0.04323725055432372</v>
+      </c>
+      <c r="X35">
+        <v>0.06170069973412962</v>
+      </c>
+      <c r="Y35">
+        <v>-0.1049379502884533</v>
+      </c>
+      <c r="Z35">
+        <v>0.1474022183304145</v>
+      </c>
+      <c r="AA35">
+        <v>-0.02991827203736135</v>
+      </c>
+      <c r="AB35">
+        <v>0.05949188705675904</v>
+      </c>
+      <c r="AC35">
+        <v>-0.08941015909412039</v>
+      </c>
+      <c r="AD35">
+        <v>21.8</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>21.8</v>
+      </c>
+      <c r="AG35">
+        <v>20.77</v>
+      </c>
+      <c r="AH35">
+        <v>0.2604540023894862</v>
+      </c>
+      <c r="AI35">
+        <v>0.3676222596964587</v>
+      </c>
+      <c r="AJ35">
+        <v>0.2512398693601064</v>
+      </c>
+      <c r="AK35">
+        <v>0.3564441393512957</v>
+      </c>
+      <c r="AL35">
+        <v>0.978</v>
+      </c>
+      <c r="AM35">
+        <v>0.978</v>
+      </c>
+      <c r="AN35">
+        <v>-36.70033670033671</v>
+      </c>
+      <c r="AO35">
+        <v>-2.096114519427403</v>
+      </c>
+      <c r="AP35">
+        <v>-34.96632996632997</v>
+      </c>
+      <c r="AQ35">
+        <v>-2.096114519427403</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>China Everbright Limited (SEHK:165)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K36">
+        <v>-438.6</v>
+      </c>
+      <c r="M36">
+        <v>92</v>
+      </c>
+      <c r="N36">
+        <v>0.08000695712670666</v>
+      </c>
+      <c r="O36">
+        <v>-0.2097583219334245</v>
+      </c>
+      <c r="P36">
+        <v>92</v>
+      </c>
+      <c r="Q36">
+        <v>0.08000695712670666</v>
+      </c>
+      <c r="R36">
+        <v>-0.2097583219334245</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>1246.7</v>
+      </c>
+      <c r="V36">
+        <v>1.084181233150709</v>
+      </c>
+      <c r="W36">
+        <v>-0.09566393299598674</v>
+      </c>
+      <c r="X36">
+        <v>0.0957865154162347</v>
+      </c>
+      <c r="Y36">
+        <v>-0.1914504484122214</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>-0.03860389948910436</v>
+      </c>
+      <c r="AB36">
+        <v>0.06068543275482287</v>
+      </c>
+      <c r="AC36">
+        <v>-0.09928933224392722</v>
+      </c>
+      <c r="AD36">
+        <v>4225.2</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>4225.2</v>
+      </c>
+      <c r="AG36">
+        <v>2978.5</v>
+      </c>
+      <c r="AH36">
+        <v>0.7860690963889043</v>
+      </c>
+      <c r="AI36">
+        <v>0.5008712969878018</v>
+      </c>
+      <c r="AJ36">
+        <v>0.721465943222556</v>
+      </c>
+      <c r="AK36">
+        <v>0.4143135345666991</v>
+      </c>
+      <c r="AL36">
+        <v>212.1</v>
+      </c>
+      <c r="AM36">
+        <v>212.1</v>
+      </c>
+      <c r="AN36">
+        <v>-14.33242876526458</v>
+      </c>
+      <c r="AO36">
+        <v>-1.396511079679396</v>
+      </c>
+      <c r="AP36">
+        <v>-10.10345997286296</v>
+      </c>
+      <c r="AQ36">
+        <v>-1.396511079679396</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>China Ever Grand Financial Leasing Group Co., Ltd. (SEHK:379)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0.0292</v>
+      </c>
+      <c r="G37">
+        <v>-0.3762376237623762</v>
+      </c>
+      <c r="H37">
+        <v>-0.3762376237623762</v>
+      </c>
+      <c r="I37">
+        <v>-0.3524752475247525</v>
+      </c>
+      <c r="J37">
+        <v>-0.3524752475247525</v>
+      </c>
+      <c r="K37">
+        <v>-7.63</v>
+      </c>
+      <c r="L37">
+        <v>-0.7554455445544555</v>
+      </c>
+      <c r="M37">
+        <v>-0</v>
+      </c>
+      <c r="N37">
+        <v>-0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>-0</v>
+      </c>
+      <c r="Q37">
+        <v>-0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>2.21</v>
+      </c>
+      <c r="V37">
+        <v>0.3082287308228731</v>
+      </c>
+      <c r="W37">
+        <v>-0.126955074875208</v>
+      </c>
+      <c r="X37">
+        <v>0.05970432355318426</v>
+      </c>
+      <c r="Y37">
+        <v>-0.1866593984283922</v>
+      </c>
+      <c r="Z37">
+        <v>0.1426352210139811</v>
+      </c>
+      <c r="AA37">
+        <v>-0.05027538483265075</v>
+      </c>
+      <c r="AB37">
+        <v>0.0588215282564175</v>
+      </c>
+      <c r="AC37">
+        <v>-0.1090969130890682</v>
+      </c>
+      <c r="AD37">
+        <v>1.13</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>1.13</v>
+      </c>
+      <c r="AG37">
+        <v>-1.08</v>
+      </c>
+      <c r="AH37">
+        <v>0.136144578313253</v>
+      </c>
+      <c r="AI37">
+        <v>0.02167657778630347</v>
+      </c>
+      <c r="AJ37">
+        <v>-0.1773399014778325</v>
+      </c>
+      <c r="AK37">
+        <v>-0.02163461538461538</v>
+      </c>
+      <c r="AL37">
+        <v>0.018</v>
+      </c>
+      <c r="AM37">
+        <v>-0.244</v>
+      </c>
+      <c r="AN37">
+        <v>-0.3256484149855907</v>
+      </c>
+      <c r="AO37">
+        <v>-197.7777777777778</v>
+      </c>
+      <c r="AP37">
+        <v>0.3112391930835735</v>
+      </c>
+      <c r="AQ37">
+        <v>14.59016393442623</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TradeGo FinTech Limited (SEHK:8017)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="G38">
+        <v>0.2865555555555555</v>
+      </c>
+      <c r="H38">
+        <v>0.02655555555555555</v>
+      </c>
+      <c r="I38">
+        <v>-0.06177777777777779</v>
+      </c>
+      <c r="J38">
+        <v>-0.06177777777777779</v>
+      </c>
+      <c r="K38">
+        <v>0.675</v>
+      </c>
+      <c r="L38">
+        <v>0.07500000000000001</v>
+      </c>
+      <c r="M38">
+        <v>1.39</v>
+      </c>
+      <c r="N38">
+        <v>0.09455782312925169</v>
+      </c>
+      <c r="O38">
+        <v>2.059259259259259</v>
+      </c>
+      <c r="P38">
+        <v>1.39</v>
+      </c>
+      <c r="Q38">
+        <v>0.09455782312925169</v>
+      </c>
+      <c r="R38">
+        <v>2.059259259259259</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>13.6</v>
+      </c>
+      <c r="V38">
+        <v>0.9251700680272109</v>
+      </c>
+      <c r="W38">
+        <v>0.03994082840236687</v>
+      </c>
+      <c r="X38">
+        <v>0.05868898342411793</v>
+      </c>
+      <c r="Y38">
+        <v>-0.01874815502175106</v>
+      </c>
+      <c r="Z38">
+        <v>1.956521739130435</v>
+      </c>
+      <c r="AA38">
+        <v>-0.1208695652173913</v>
+      </c>
+      <c r="AB38">
+        <v>0.05867743939787468</v>
+      </c>
+      <c r="AC38">
+        <v>-0.179547004615266</v>
+      </c>
+      <c r="AD38">
+        <v>0.862</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0.862</v>
+      </c>
+      <c r="AG38">
+        <v>-12.738</v>
+      </c>
+      <c r="AH38">
+        <v>0.05539133787430921</v>
+      </c>
+      <c r="AI38">
+        <v>0.04694477725737937</v>
+      </c>
+      <c r="AJ38">
+        <v>-6.492354740061162</v>
+      </c>
+      <c r="AK38">
+        <v>-2.67492650146997</v>
+      </c>
+      <c r="AL38">
+        <v>0.05</v>
+      </c>
+      <c r="AM38">
+        <v>-0.346</v>
+      </c>
+      <c r="AN38">
+        <v>-1.799582463465553</v>
+      </c>
+      <c r="AO38">
+        <v>-11.12</v>
+      </c>
+      <c r="AP38">
+        <v>26.5929018789144</v>
+      </c>
+      <c r="AQ38">
+        <v>1.606936416184971</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Capital Finance Holdings Limited (SEHK:8239)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>-0.234</v>
+      </c>
+      <c r="G39">
+        <v>0.2221804511278195</v>
+      </c>
+      <c r="H39">
+        <v>0.2221804511278195</v>
+      </c>
+      <c r="I39">
+        <v>-0.8872180451127819</v>
+      </c>
+      <c r="J39">
+        <v>-0.8872180451127819</v>
+      </c>
+      <c r="K39">
+        <v>-3.03</v>
+      </c>
+      <c r="L39">
+        <v>-1.139097744360902</v>
+      </c>
+      <c r="M39">
+        <v>-0</v>
+      </c>
+      <c r="N39">
+        <v>-0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>-0</v>
+      </c>
+      <c r="Q39">
+        <v>-0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>11.3</v>
+      </c>
+      <c r="V39">
+        <v>1.701807228915663</v>
+      </c>
+      <c r="W39">
+        <v>-0.37875</v>
+      </c>
+      <c r="X39">
+        <v>0.07632036222538649</v>
+      </c>
+      <c r="Y39">
+        <v>-0.4550703622253864</v>
+      </c>
+      <c r="Z39">
+        <v>0.1641975308641976</v>
+      </c>
+      <c r="AA39">
+        <v>-0.145679012345679</v>
+      </c>
+      <c r="AB39">
+        <v>0.06153818270892162</v>
+      </c>
+      <c r="AC39">
+        <v>-0.2072171950546006</v>
+      </c>
+      <c r="AD39">
+        <v>11.8</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>11.8</v>
+      </c>
+      <c r="AG39">
+        <v>0.5</v>
+      </c>
+      <c r="AH39">
+        <v>0.6399132321041214</v>
+      </c>
+      <c r="AI39">
+        <v>0.5432780847145489</v>
+      </c>
+      <c r="AJ39">
+        <v>0.07002801120448179</v>
+      </c>
+      <c r="AK39">
+        <v>0.04798464491362764</v>
+      </c>
+      <c r="AL39">
+        <v>1.47</v>
+      </c>
+      <c r="AM39">
+        <v>1.326</v>
+      </c>
+      <c r="AN39">
+        <v>-5.064377682403434</v>
+      </c>
+      <c r="AO39">
+        <v>-1.605442176870748</v>
+      </c>
+      <c r="AP39">
+        <v>-0.2145922746781116</v>
+      </c>
+      <c r="AQ39">
+        <v>-1.779788838612368</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lerado Financial Group Company Limited (SEHK:1225)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>-0.0382</v>
+      </c>
+      <c r="G40">
+        <v>-0.9775280898876405</v>
+      </c>
+      <c r="H40">
+        <v>-0.9775280898876405</v>
+      </c>
+      <c r="I40">
+        <v>-0.9550561797752809</v>
+      </c>
+      <c r="J40">
+        <v>-0.9550561797752809</v>
+      </c>
+      <c r="K40">
+        <v>-37.7</v>
+      </c>
+      <c r="L40">
+        <v>-1.411985018726592</v>
+      </c>
+      <c r="M40">
+        <v>-0</v>
+      </c>
+      <c r="N40">
+        <v>-0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>-0</v>
+      </c>
+      <c r="Q40">
+        <v>-0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>17</v>
+      </c>
+      <c r="V40">
+        <v>3.563941299790357</v>
+      </c>
+      <c r="W40">
+        <v>-0.4440518256772674</v>
+      </c>
+      <c r="X40">
+        <v>0.2348937613504567</v>
+      </c>
+      <c r="Y40">
+        <v>-0.6789455870277241</v>
+      </c>
+      <c r="Z40">
+        <v>0.1644088669950739</v>
+      </c>
+      <c r="AA40">
+        <v>-0.1570197044334976</v>
+      </c>
+      <c r="AB40">
+        <v>0.06318424053705911</v>
+      </c>
+      <c r="AC40">
+        <v>-0.2202039449705567</v>
+      </c>
+      <c r="AD40">
+        <v>82.2</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>82.2</v>
+      </c>
+      <c r="AG40">
+        <v>65.2</v>
+      </c>
+      <c r="AH40">
+        <v>0.9451535012073129</v>
+      </c>
+      <c r="AI40">
+        <v>0.6208459214501511</v>
+      </c>
+      <c r="AJ40">
+        <v>0.9318279262541089</v>
+      </c>
+      <c r="AK40">
+        <v>0.5649913344887348</v>
+      </c>
+      <c r="AL40">
+        <v>4.53</v>
+      </c>
+      <c r="AM40">
+        <v>4.444</v>
+      </c>
+      <c r="AN40">
+        <v>-3.261904761904762</v>
+      </c>
+      <c r="AO40">
+        <v>-5.629139072847682</v>
+      </c>
+      <c r="AP40">
+        <v>-2.587301587301587</v>
+      </c>
+      <c r="AQ40">
+        <v>-5.738073807380738</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Finet Group Limited (SEHK:8317)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>-0.212</v>
+      </c>
+      <c r="G41">
+        <v>-0.9433962264150942</v>
+      </c>
+      <c r="H41">
+        <v>-0.9433962264150942</v>
+      </c>
+      <c r="I41">
+        <v>-0.9811320754716981</v>
+      </c>
+      <c r="J41">
+        <v>-0.9811320754716981</v>
+      </c>
+      <c r="K41">
+        <v>-1.16</v>
+      </c>
+      <c r="L41">
+        <v>-1.094339622641509</v>
+      </c>
+      <c r="M41">
+        <v>-0</v>
+      </c>
+      <c r="N41">
+        <v>-0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>-0</v>
+      </c>
+      <c r="Q41">
+        <v>-0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>2.36</v>
+      </c>
+      <c r="V41">
+        <v>0.2413087934560327</v>
+      </c>
+      <c r="W41">
+        <v>-0.1681159420289855</v>
+      </c>
+      <c r="X41">
+        <v>0.06108769534443984</v>
+      </c>
+      <c r="Y41">
+        <v>-0.2292036373734253</v>
+      </c>
+      <c r="Z41">
+        <v>0.1920985864443639</v>
+      </c>
+      <c r="AA41">
+        <v>-0.1884740848133382</v>
+      </c>
+      <c r="AB41">
+        <v>0.05930752173421039</v>
+      </c>
+      <c r="AC41">
+        <v>-0.2477816065475485</v>
+      </c>
+      <c r="AD41">
+        <v>2.86</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>2.86</v>
+      </c>
+      <c r="AG41">
+        <v>0.5</v>
+      </c>
+      <c r="AH41">
+        <v>0.2262658227848101</v>
+      </c>
+      <c r="AI41">
+        <v>0.3643312101910828</v>
+      </c>
+      <c r="AJ41">
+        <v>0.04863813229571985</v>
+      </c>
+      <c r="AK41">
+        <v>0.09107468123861566</v>
+      </c>
+      <c r="AL41">
+        <v>0.031</v>
+      </c>
+      <c r="AM41">
+        <v>0.028</v>
+      </c>
+      <c r="AN41">
+        <v>-2.831683168316832</v>
+      </c>
+      <c r="AO41">
+        <v>-33.54838709677419</v>
+      </c>
+      <c r="AP41">
+        <v>-0.495049504950495</v>
+      </c>
+      <c r="AQ41">
+        <v>-37.14285714285715</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kingkey Financial International (Holdings) Limited (SEHK:1468)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>0.115</v>
+      </c>
+      <c r="G42">
+        <v>-0.7924528301886793</v>
+      </c>
+      <c r="H42">
+        <v>-0.7924528301886793</v>
+      </c>
+      <c r="I42">
+        <v>-1.158490566037736</v>
+      </c>
+      <c r="J42">
+        <v>-1.158490566037736</v>
+      </c>
+      <c r="K42">
+        <v>-79.90000000000001</v>
+      </c>
+      <c r="L42">
+        <v>-3.015094339622642</v>
+      </c>
+      <c r="M42">
+        <v>-0</v>
+      </c>
+      <c r="N42">
+        <v>-0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>-0</v>
+      </c>
+      <c r="Q42">
+        <v>-0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>20.5</v>
+      </c>
+      <c r="V42">
+        <v>0.2100409836065574</v>
+      </c>
+      <c r="W42">
+        <v>-0.6150885296381833</v>
+      </c>
+      <c r="X42">
+        <v>0.06006364527977506</v>
+      </c>
+      <c r="Y42">
+        <v>-0.6751521749179583</v>
+      </c>
+      <c r="Z42">
+        <v>0.2389540126239856</v>
+      </c>
+      <c r="AA42">
+        <v>-0.2768259693417493</v>
+      </c>
+      <c r="AB42">
+        <v>0.06715796896627582</v>
+      </c>
+      <c r="AC42">
+        <v>-0.3439839383080251</v>
+      </c>
+      <c r="AD42">
+        <v>18.8</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>18.8</v>
+      </c>
+      <c r="AG42">
+        <v>-1.699999999999999</v>
+      </c>
+      <c r="AH42">
+        <v>0.1615120274914089</v>
+      </c>
+      <c r="AI42">
+        <v>0.2079646017699115</v>
+      </c>
+      <c r="AJ42">
+        <v>-0.01772679874869655</v>
+      </c>
+      <c r="AK42">
+        <v>-0.02432045779685264</v>
+      </c>
+      <c r="AL42">
+        <v>1.24</v>
+      </c>
+      <c r="AM42">
+        <v>0.47</v>
+      </c>
+      <c r="AN42">
+        <v>-1.027322404371585</v>
+      </c>
+      <c r="AO42">
+        <v>-24.75806451612903</v>
+      </c>
+      <c r="AP42">
+        <v>0.09289617486338794</v>
+      </c>
+      <c r="AQ42">
+        <v>-65.31914893617021</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NOIZ Group Limited (SEHK:8163)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>-0.468</v>
+      </c>
+      <c r="G43">
+        <v>-0.4577464788732395</v>
+      </c>
+      <c r="H43">
+        <v>-0.4577464788732395</v>
+      </c>
+      <c r="I43">
+        <v>-0.6126760563380282</v>
+      </c>
+      <c r="J43">
+        <v>-0.6126760563380282</v>
+      </c>
+      <c r="K43">
+        <v>-3.49</v>
+      </c>
+      <c r="L43">
+        <v>-1.22887323943662</v>
+      </c>
+      <c r="M43">
+        <v>-0</v>
+      </c>
+      <c r="N43">
+        <v>-0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>-0</v>
+      </c>
+      <c r="Q43">
+        <v>-0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="V43">
+        <v>0.07790476190476189</v>
+      </c>
+      <c r="W43">
+        <v>0.6415441176470588</v>
+      </c>
+      <c r="X43">
+        <v>0.0687381353952093</v>
+      </c>
+      <c r="Y43">
+        <v>0.5728059822518494</v>
+      </c>
+      <c r="Z43">
+        <v>0.6207650273224045</v>
+      </c>
+      <c r="AA43">
+        <v>-0.3803278688524591</v>
+      </c>
+      <c r="AB43">
+        <v>0.08669254384129682</v>
+      </c>
+      <c r="AC43">
+        <v>-0.4670204126937559</v>
+      </c>
+      <c r="AD43">
+        <v>10.9</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>10.9</v>
+      </c>
+      <c r="AG43">
+        <v>10.082</v>
+      </c>
+      <c r="AH43">
+        <v>0.5093457943925234</v>
+      </c>
+      <c r="AI43">
+        <v>2.433035714285714</v>
+      </c>
+      <c r="AJ43">
+        <v>0.4898454960645224</v>
+      </c>
+      <c r="AK43">
+        <v>2.753140360458765</v>
+      </c>
+      <c r="AL43">
+        <v>1.62</v>
+      </c>
+      <c r="AM43">
+        <v>1.62</v>
+      </c>
+      <c r="AN43">
+        <v>-8.01470588235294</v>
+      </c>
+      <c r="AO43">
+        <v>-1.074074074074074</v>
+      </c>
+      <c r="AP43">
+        <v>-7.413235294117647</v>
+      </c>
+      <c r="AQ43">
+        <v>-1.074074074074074</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>OSL Group Limited (SEHK:863)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>0.05309999999999999</v>
+      </c>
+      <c r="G44">
+        <v>-0.7952218430034129</v>
+      </c>
+      <c r="H44">
+        <v>-0.7952218430034129</v>
+      </c>
+      <c r="I44">
+        <v>-0.5836177474402731</v>
+      </c>
+      <c r="J44">
+        <v>-0.5836177474402731</v>
+      </c>
+      <c r="K44">
+        <v>-23.9</v>
+      </c>
+      <c r="L44">
+        <v>-0.8156996587030716</v>
+      </c>
+      <c r="M44">
+        <v>-0</v>
+      </c>
+      <c r="N44">
+        <v>-0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>-0</v>
+      </c>
+      <c r="Q44">
+        <v>-0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>97.8</v>
+      </c>
+      <c r="V44">
+        <v>0.1516044024182297</v>
+      </c>
+      <c r="W44">
+        <v>-0.3273972602739726</v>
+      </c>
+      <c r="X44">
+        <v>0.05814985078838189</v>
+      </c>
+      <c r="Y44">
+        <v>-0.3855471110623545</v>
+      </c>
+      <c r="Z44">
+        <v>1.180499597099114</v>
+      </c>
+      <c r="AA44">
+        <v>-0.6889605157131347</v>
+      </c>
+      <c r="AB44">
+        <v>0.05828280595349074</v>
+      </c>
+      <c r="AC44">
+        <v>-0.7472433216666254</v>
+      </c>
+      <c r="AD44">
+        <v>3.93</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>3.93</v>
+      </c>
+      <c r="AG44">
+        <v>-93.86999999999999</v>
+      </c>
+      <c r="AH44">
+        <v>0.006055190052848097</v>
+      </c>
+      <c r="AI44">
+        <v>0.0272670505793381</v>
+      </c>
+      <c r="AJ44">
+        <v>-0.1702918926763783</v>
+      </c>
+      <c r="AK44">
+        <v>-2.026116986833585</v>
+      </c>
+      <c r="AL44">
+        <v>0.432</v>
+      </c>
+      <c r="AM44">
+        <v>-1.448</v>
+      </c>
+      <c r="AN44">
+        <v>-0.2396341463414634</v>
+      </c>
+      <c r="AO44">
+        <v>-39.58333333333334</v>
+      </c>
+      <c r="AP44">
+        <v>5.723780487804878</v>
+      </c>
+      <c r="AQ44">
+        <v>11.80939226519337</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AGM Group Holdings Inc. (NasdaqCM:AGMH)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>1.276</v>
+      </c>
+      <c r="G45">
+        <v>-0.1373846153846154</v>
+      </c>
+      <c r="H45">
+        <v>-0.1373846153846154</v>
+      </c>
+      <c r="I45">
+        <v>-0.7022252790735941</v>
+      </c>
+      <c r="J45">
+        <v>-0.7022252790735941</v>
+      </c>
+      <c r="K45">
+        <v>-38.5</v>
+      </c>
+      <c r="L45">
+        <v>-0.5923076923076923</v>
+      </c>
+      <c r="M45">
+        <v>-0</v>
+      </c>
+      <c r="N45">
+        <v>-0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>-0</v>
+      </c>
+      <c r="Q45">
+        <v>-0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>1.21</v>
+      </c>
+      <c r="V45">
+        <v>0.03306010928961749</v>
+      </c>
+      <c r="W45">
+        <v>-0.8932714617169373</v>
+      </c>
+      <c r="X45">
+        <v>0.06087188581606842</v>
+      </c>
+      <c r="Y45">
+        <v>-0.9541433475330057</v>
+      </c>
+      <c r="Z45">
+        <v>1.326985153435644</v>
+      </c>
+      <c r="AA45">
+        <v>-0.931842519697861</v>
+      </c>
+      <c r="AB45">
+        <v>0.06036142448979993</v>
+      </c>
+      <c r="AC45">
+        <v>-0.992203944187661</v>
+      </c>
+      <c r="AD45">
+        <v>9.81</v>
+      </c>
+      <c r="AE45">
+        <v>0.1232156989180512</v>
+      </c>
+      <c r="AF45">
+        <v>9.933215698918051</v>
+      </c>
+      <c r="AG45">
+        <v>8.72321569891805</v>
+      </c>
+      <c r="AH45">
+        <v>0.2134650603815676</v>
+      </c>
+      <c r="AI45">
+        <v>0.6964218945151018</v>
+      </c>
+      <c r="AJ45">
+        <v>0.1924668310577594</v>
+      </c>
+      <c r="AK45">
+        <v>0.6682809738324554</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
+      </c>
+      <c r="AN45">
+        <v>-0.2174202127659574</v>
+      </c>
+      <c r="AP45">
+        <v>-0.1933336812703468</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Metalpha Technology Holding Limited (NasdaqCM:MATH)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>0.435</v>
+      </c>
+      <c r="G46">
+        <v>-0.2803571428571429</v>
+      </c>
+      <c r="H46">
+        <v>-0.2803571428571429</v>
+      </c>
+      <c r="I46">
+        <v>-0.280952380952381</v>
+      </c>
+      <c r="J46">
+        <v>-0.280952380952381</v>
+      </c>
+      <c r="K46">
+        <v>-3.68</v>
+      </c>
+      <c r="L46">
+        <v>-0.219047619047619</v>
+      </c>
+      <c r="M46">
+        <v>0.082</v>
+      </c>
+      <c r="N46">
+        <v>0.001933962264150944</v>
+      </c>
+      <c r="O46">
+        <v>-0.02228260869565217</v>
+      </c>
+      <c r="P46">
+        <v>-0</v>
+      </c>
+      <c r="Q46">
+        <v>-0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0.082</v>
+      </c>
+      <c r="T46">
+        <v>1</v>
+      </c>
+      <c r="U46">
+        <v>4.88</v>
+      </c>
+      <c r="V46">
+        <v>0.1150943396226415</v>
+      </c>
+      <c r="W46">
+        <v>-0.4279069767441861</v>
+      </c>
+      <c r="X46">
+        <v>0.05930692355612197</v>
+      </c>
+      <c r="Y46">
+        <v>-0.4872139003003081</v>
+      </c>
+      <c r="Z46">
+        <v>8.47201210287443</v>
+      </c>
+      <c r="AA46">
+        <v>-1</v>
+      </c>
+      <c r="AB46">
+        <v>0.05921913272222133</v>
+      </c>
+      <c r="AC46">
+        <v>-1.059219132722221</v>
+      </c>
+      <c r="AD46">
+        <v>5.04</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>5.04</v>
+      </c>
+      <c r="AG46">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="AH46">
+        <v>0.106239460370995</v>
+      </c>
+      <c r="AI46">
+        <v>0.2297174111212398</v>
+      </c>
+      <c r="AJ46">
+        <v>0.003759398496240605</v>
+      </c>
+      <c r="AK46">
+        <v>0.009378663540445496</v>
+      </c>
+      <c r="AL46">
+        <v>0.004</v>
+      </c>
+      <c r="AM46">
+        <v>-0.03</v>
+      </c>
+      <c r="AN46">
+        <v>-1.070063694267516</v>
+      </c>
+      <c r="AO46">
+        <v>-1180</v>
+      </c>
+      <c r="AP46">
+        <v>-0.0339702760084926</v>
+      </c>
+      <c r="AQ46">
+        <v>157.3333333333333</v>
       </c>
     </row>
   </sheetData>
